--- a/data/instruments_master.xlsx
+++ b/data/instruments_master.xlsx
@@ -23,9 +23,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -65,12 +64,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -995,7 +995,6 @@
       <c r="E2" t="n">
         <v>0.024</v>
       </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1021,7 +1020,6 @@
       <c r="E3" t="n">
         <v>0.0353</v>
       </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1047,7 +1045,6 @@
       <c r="E4" t="n">
         <v>0.026</v>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1073,7 +1070,6 @@
       <c r="E5" t="n">
         <v>0.0235</v>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1099,7 +1095,6 @@
       <c r="E6" t="n">
         <v>0.0215</v>
       </c>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1125,7 +1120,6 @@
       <c r="E7" t="n">
         <v>0.0275</v>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1151,7 +1145,6 @@
       <c r="E8" t="n">
         <v>0.025</v>
       </c>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1177,7 +1170,6 @@
       <c r="E9" t="n">
         <v>0.0253</v>
       </c>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1203,7 +1195,6 @@
       <c r="E10" t="n">
         <v>0.0255</v>
       </c>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1229,7 +1220,6 @@
       <c r="E11" t="n">
         <v>0.023</v>
       </c>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1255,7 +1245,6 @@
       <c r="E12" t="n">
         <v>0.0205</v>
       </c>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1281,7 +1270,6 @@
       <c r="E13" t="n">
         <v>0.0255</v>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1307,7 +1295,6 @@
       <c r="E14" t="n">
         <v>0.024</v>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1333,7 +1320,6 @@
       <c r="E15" t="n">
         <v>0.0258</v>
       </c>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1359,7 +1345,6 @@
       <c r="E16" t="n">
         <v>0.0216</v>
       </c>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1415,7 +1400,6 @@
       <c r="E18" t="n">
         <v>0.0219</v>
       </c>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1441,7 +1425,6 @@
       <c r="E19" t="n">
         <v>0.0217</v>
       </c>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1467,7 +1450,6 @@
       <c r="E20" t="n">
         <v>0.0214</v>
       </c>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1480,14 +1462,11 @@
           <t>BONOFIJA</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>17/10/2026</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1500,14 +1479,11 @@
           <t>BONOFIJA</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>30/05/2030</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1520,13 +1496,11 @@
           <t>BONOFIJA</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>30/05/2027</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>precio_de:TY30P</t>
@@ -1544,7 +1518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1613,6 +1587,11 @@
           <t>CER Emision</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1625,22 +1604,15 @@
           <t>LECER</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="3" t="n">
         <v>46080</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <v>46157</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>701.61402891428</v>
       </c>
@@ -1656,22 +1628,15 @@
           <t>LECER</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="3" t="n">
         <v>45989</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>46171</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>652.33524435885</v>
       </c>
@@ -1687,25 +1652,23 @@
           <t>BONCER ZC</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="3" t="n">
         <v>45323</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="3" t="n">
         <v>46203</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>200.38801458912</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>BONCERES CERO CUPON</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1718,22 +1681,15 @@
           <t>LECER</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="3" t="n">
         <v>46052</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <v>46234</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>685.55061207521</v>
       </c>
@@ -1749,22 +1705,15 @@
           <t>LECER</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="3" t="n">
         <v>46097</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="3" t="n">
         <v>46295</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>714.9848780192</v>
       </c>
@@ -1780,25 +1729,23 @@
           <t>BONCER ZC</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="3" t="n">
         <v>45596</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3" t="n">
         <v>46325</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>480.15257831965</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>BONCERES CERO CUPON</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1811,10 +1758,10 @@
           <t>BONCER</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="3" t="n">
         <v>44078</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="3" t="n">
         <v>46335</v>
       </c>
       <c r="E8" t="n">
@@ -1833,7 +1780,7 @@
           <t>amortizing</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="3" t="n">
         <v>45605</v>
       </c>
       <c r="J8" t="n">
@@ -1842,10 +1789,14 @@
       <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>22.5439510896</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>BONTES (CUPON SEMESTRAL)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1858,22 +1809,15 @@
           <t>LECER</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="3" t="n">
         <v>46006</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="3" t="n">
         <v>46356</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>659.67889566652</v>
       </c>
@@ -1889,25 +1833,23 @@
           <t>BONCER ZC</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="3" t="n">
         <v>45366</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="3" t="n">
         <v>46371</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>271.04755550913</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>BONCERES CERO CUPON</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1920,25 +1862,23 @@
           <t>BONCER ZC</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="3" t="n">
         <v>45432</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="3" t="n">
         <v>46477</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>361.31760345721</v>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>BONCERES CERO CUPON</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1951,25 +1891,23 @@
           <t>BONCER ZC</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C12" s="3" t="n">
         <v>46006</v>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="3" t="n">
         <v>46537</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>659.67889566652</v>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>BONCERES CERO CUPON</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1982,25 +1920,23 @@
           <t>BONCER ZC</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C13" s="3" t="n">
         <v>45323</v>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="3" t="n">
         <v>46568</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>200.38801458912</v>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>BONCERES CERO CUPON</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2013,25 +1949,23 @@
           <t>BONCER ZC</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C14" s="3" t="n">
         <v>45366</v>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="3" t="n">
         <v>46736</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>271.04755550913</v>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>BONCERES CERO CUPON</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2044,25 +1978,23 @@
           <t>BONCER ZC</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="C15" s="3" t="n">
         <v>45366</v>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="3" t="n">
         <v>46934</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>271.04755550913</v>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>BONCERES CERO CUPON</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2075,10 +2007,10 @@
           <t>BONCER</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="C16" s="3" t="n">
         <v>44078</v>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" s="3" t="n">
         <v>47066</v>
       </c>
       <c r="E16" t="n">
@@ -2097,7 +2029,7 @@
           <t>amortizing</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="I16" s="3" t="n">
         <v>45421</v>
       </c>
       <c r="J16" t="n">
@@ -2106,10 +2038,14 @@
       <c r="K16" t="n">
         <v>1</v>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
         <v>22.5439510896</v>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>BONTES (CUPON SEMESTRAL)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2122,10 +2058,10 @@
           <t>BONCER</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="C17" s="3" t="n">
         <v>44712</v>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" s="3" t="n">
         <v>48182</v>
       </c>
       <c r="E17" t="n">
@@ -2144,7 +2080,7 @@
           <t>amortizing</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="I17" s="3" t="n">
         <v>46537</v>
       </c>
       <c r="J17" t="n">
@@ -2153,10 +2089,14 @@
       <c r="K17" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
         <v>46.9130015738</v>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>BONTES (CUPON SEMESTRAL)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2169,10 +2109,10 @@
           <t>CON CUPON</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="C18" s="3" t="n">
         <v>37986</v>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="3" t="n">
         <v>48944</v>
       </c>
       <c r="E18" t="n">
@@ -2191,7 +2131,7 @@
           <t>amortizing</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="I18" s="3" t="n">
         <v>45473</v>
       </c>
       <c r="J18" t="n">
@@ -2200,7 +2140,6 @@
       <c r="K18" t="n">
         <v>1.269937</v>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
         <v>1.4550639398</v>
       </c>
@@ -2216,10 +2155,10 @@
           <t>STEP-UP</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n">
+      <c r="C19" s="3" t="n">
         <v>37986</v>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="D19" s="3" t="n">
         <v>50770</v>
       </c>
       <c r="E19" t="inlineStr">
@@ -2240,7 +2179,7 @@
           <t>amortizing</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="I19" s="3" t="n">
         <v>47391</v>
       </c>
       <c r="J19" t="n">
@@ -2269,10 +2208,10 @@
           <t>CON CUPON</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
+      <c r="C20" s="3" t="n">
         <v>37986</v>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="D20" s="3" t="n">
         <v>53327</v>
       </c>
       <c r="E20" t="n">
@@ -2291,7 +2230,7 @@
           <t>amortizing</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="I20" s="3" t="n">
         <v>49856</v>
       </c>
       <c r="J20" t="n">
@@ -2300,7 +2239,6 @@
       <c r="K20" t="n">
         <v>1.388593</v>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
         <v>1.4550639398</v>
       </c>
@@ -2332,19 +2270,20 @@
       <c r="F21" t="n">
         <v>0</v>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
         <v>651.89</v>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>BONCERES CERO CUPON</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2373,19 +2312,20 @@
       <c r="F22" t="n">
         <v>0</v>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
         <v>725.17</v>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>BONCERES CERO CUPON</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2414,19 +2354,20 @@
       <c r="F23" t="n">
         <v>0</v>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
         <v>730</v>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>BONCERES CERO CUPON</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2476,7 +2417,6 @@
       <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
         <v>1.455064</v>
       </c>
@@ -2736,7 +2676,6 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2759,7 +2698,6 @@
           <t>2027-02-26</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2782,7 +2720,6 @@
           <t>2028-02-25</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">

--- a/data/instruments_master.xlsx
+++ b/data/instruments_master.xlsx
@@ -23,8 +23,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,13 +65,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1518,7 +1520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2476,6 +2478,93 @@
       </c>
       <c r="M25" t="n">
         <v>1.455064</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TZXM6</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BONCER ZC</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>45412</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>46112</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>337.034067574</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>BONCERES CERO CUPON</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TZXM8</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BONCER ZC</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>46132</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>46843</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>739.387405739</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>BONCERES CERO CUPON</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TZXM9</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BONCER ZC</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>47205</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>725.875485635</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>BONCERES CERO CUPON</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/instruments_master.xlsx
+++ b/data/instruments_master.xlsx
@@ -1618,6 +1618,11 @@
       <c r="M2" t="n">
         <v>701.61402891428</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>LETRA TESORO DESCUENTO CER</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1642,6 +1647,11 @@
       <c r="M3" t="n">
         <v>652.33524435885</v>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>LETRA TESORO DESCUENTO CER</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1695,6 +1705,11 @@
       <c r="M5" t="n">
         <v>685.55061207521</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>LETRA TESORO DESCUENTO CER</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1719,6 +1734,11 @@
       <c r="M6" t="n">
         <v>714.9848780192</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>LETRA TESORO DESCUENTO CER</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1823,6 +1843,11 @@
       <c r="M9" t="n">
         <v>659.67889566652</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>LETRA TESORO DESCUENTO CER</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2145,6 +2170,11 @@
       <c r="M18" t="n">
         <v>1.4550639398</v>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>BONTE (SEMESTRAL)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2198,6 +2228,11 @@
       <c r="M19" t="n">
         <v>1.4550639398</v>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>BONTE (SEMESTRAL)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2243,6 +2278,11 @@
       </c>
       <c r="M20" t="n">
         <v>1.4550639398</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>BONTE (SEMESTRAL)</t>
+        </is>
       </c>
     </row>
     <row r="21">

--- a/data/instruments_master.xlsx
+++ b/data/instruments_master.xlsx
@@ -471,7 +471,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AL29</t>
+          <t>AL29D</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -498,7 +498,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AL30</t>
+          <t>AL30D</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -525,7 +525,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AL35</t>
+          <t>AL35D</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -552,7 +552,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AE38</t>
+          <t>AE38D</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AL41</t>
+          <t>AL41D</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GD29</t>
+          <t>GD29D</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GD30</t>
+          <t>GD30D</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GD35</t>
+          <t>GD35D</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GD38</t>
+          <t>GD38D</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GD41</t>
+          <t>GD41D</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GD46</t>
+          <t>GD46D</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BPY6</t>
+          <t>BPY6D</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BPA7</t>
+          <t>BPA7D</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BPB7</t>
+          <t>BPB7D</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BPC7</t>
+          <t>BPC7D</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BPD7</t>
+          <t>BPD7D</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BPB8</t>
+          <t>BPB8D</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">

--- a/data/instruments_master.xlsx
+++ b/data/instruments_master.xlsx
@@ -14424,7 +14424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R262"/>
+  <dimension ref="A1:R260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22305,7 +22305,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TLCLD</t>
+          <t>TLCUD</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -22330,20 +22330,20 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>AR0731472459</t>
+          <t>AR0857544677</t>
         </is>
       </c>
       <c r="G129" s="25" t="n">
-        <v>45449</v>
+        <v>46086</v>
       </c>
       <c r="H129" s="25" t="n">
-        <v>46179</v>
+        <v>47182</v>
       </c>
       <c r="I129" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="J129" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -22356,16 +22356,19 @@
         </is>
       </c>
       <c r="M129" s="25" t="n">
-        <v>46179</v>
+        <v>47182</v>
       </c>
       <c r="N129" t="n">
         <v>1</v>
       </c>
+      <c r="O129" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TLCUD</t>
+          <t>TLCDD</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -22390,20 +22393,20 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>AR0857544677</t>
+          <t>ARTECO5600E0</t>
         </is>
       </c>
       <c r="G130" s="25" t="n">
-        <v>46086</v>
+        <v>44629</v>
       </c>
       <c r="H130" s="25" t="n">
-        <v>47182</v>
+        <v>46455</v>
       </c>
       <c r="I130" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -22416,24 +22419,21 @@
         </is>
       </c>
       <c r="M130" s="25" t="n">
-        <v>47182</v>
+        <v>46455</v>
       </c>
       <c r="N130" t="n">
         <v>1</v>
       </c>
-      <c r="O130" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TLCDD</t>
+          <t>VSCQD</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Vista Energy</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -22443,7 +22443,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Telecomunicaciones</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -22453,17 +22453,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>ARTECO5600E0</t>
+          <t>AR0941463967</t>
         </is>
       </c>
       <c r="G131" s="25" t="n">
-        <v>44629</v>
+        <v>45481</v>
       </c>
       <c r="H131" s="25" t="n">
-        <v>46455</v>
+        <v>46942</v>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J131" t="n">
         <v>4</v>
@@ -22479,7 +22479,7 @@
         </is>
       </c>
       <c r="M131" s="25" t="n">
-        <v>46455</v>
+        <v>46942</v>
       </c>
       <c r="N131" t="n">
         <v>1</v>
@@ -22488,7 +22488,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>VSCQD</t>
+          <t>VSCMD</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -22513,17 +22513,17 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>AR0941463967</t>
+          <t>AROILG5600L4</t>
         </is>
       </c>
       <c r="G132" s="25" t="n">
-        <v>45481</v>
+        <v>45149</v>
       </c>
       <c r="H132" s="25" t="n">
-        <v>46942</v>
+        <v>46976</v>
       </c>
       <c r="I132" t="n">
-        <v>3</v>
+        <v>0.99</v>
       </c>
       <c r="J132" t="n">
         <v>4</v>
@@ -22539,7 +22539,7 @@
         </is>
       </c>
       <c r="M132" s="25" t="n">
-        <v>46942</v>
+        <v>46976</v>
       </c>
       <c r="N132" t="n">
         <v>1</v>
@@ -22548,7 +22548,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>VSCMD</t>
+          <t>VSCWD</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -22573,17 +22573,17 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>AROILG5600L4</t>
+          <t>AR0652555118</t>
         </is>
       </c>
       <c r="G133" s="25" t="n">
-        <v>45149</v>
+        <v>45945</v>
       </c>
       <c r="H133" s="25" t="n">
-        <v>46976</v>
+        <v>46492</v>
       </c>
       <c r="I133" t="n">
-        <v>0.99</v>
+        <v>6</v>
       </c>
       <c r="J133" t="n">
         <v>4</v>
@@ -22599,7 +22599,7 @@
         </is>
       </c>
       <c r="M133" s="25" t="n">
-        <v>46976</v>
+        <v>46492</v>
       </c>
       <c r="N133" t="n">
         <v>1</v>
@@ -22608,7 +22608,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>VSCWD</t>
+          <t>VSCOD</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -22633,20 +22633,20 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>AR0652555118</t>
+          <t>AR0399155156</t>
         </is>
       </c>
       <c r="G134" s="25" t="n">
-        <v>45945</v>
+        <v>45357</v>
       </c>
       <c r="H134" s="25" t="n">
-        <v>46492</v>
+        <v>46452</v>
       </c>
       <c r="I134" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="J134" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         </is>
       </c>
       <c r="M134" s="25" t="n">
-        <v>46492</v>
+        <v>46452</v>
       </c>
       <c r="N134" t="n">
         <v>1</v>
@@ -22668,7 +22668,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>VSCOD</t>
+          <t>VSCUD</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -22693,17 +22693,17 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>AR0399155156</t>
+          <t>AR0707929003</t>
         </is>
       </c>
       <c r="G135" s="25" t="n">
-        <v>45357</v>
+        <v>45723</v>
       </c>
       <c r="H135" s="25" t="n">
-        <v>46452</v>
+        <v>47549</v>
       </c>
       <c r="I135" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="J135" t="n">
         <v>2</v>
@@ -22719,7 +22719,7 @@
         </is>
       </c>
       <c r="M135" s="25" t="n">
-        <v>46452</v>
+        <v>47549</v>
       </c>
       <c r="N135" t="n">
         <v>1</v>
@@ -22728,7 +22728,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>VSCUD</t>
+          <t>VSCJD</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -22753,20 +22753,20 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>AR0707929003</t>
+          <t>AROILG5600I0</t>
         </is>
       </c>
       <c r="G136" s="25" t="n">
-        <v>45723</v>
+        <v>44988</v>
       </c>
       <c r="H136" s="25" t="n">
-        <v>47549</v>
+        <v>46449</v>
       </c>
       <c r="I136" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
@@ -22779,7 +22779,7 @@
         </is>
       </c>
       <c r="M136" s="25" t="n">
-        <v>47549</v>
+        <v>46449</v>
       </c>
       <c r="N136" t="n">
         <v>1</v>
@@ -22788,7 +22788,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>VSCHD</t>
+          <t>VSCRD</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -22813,20 +22813,20 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>AROILG5600G4</t>
+          <t>AR0138120560</t>
         </is>
       </c>
       <c r="G137" s="25" t="n">
-        <v>44901</v>
+        <v>45575</v>
       </c>
       <c r="H137" s="25" t="n">
-        <v>46179</v>
+        <v>48131</v>
       </c>
       <c r="I137" t="n">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="J137" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -22835,25 +22835,31 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>amortizing</t>
         </is>
       </c>
       <c r="M137" s="25" t="n">
-        <v>46179</v>
+        <v>47401</v>
       </c>
       <c r="N137" t="n">
+        <v>3</v>
+      </c>
+      <c r="O137" t="n">
         <v>1</v>
+      </c>
+      <c r="P137" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>VSCJD</t>
+          <t>YFCLD</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Vista Energy</t>
+          <t>YPF Energia Electrica SA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -22863,7 +22869,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Servicios Públicos y Generación</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -22873,24 +22879,24 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>AROILG5600I0</t>
+          <t>AR0338531962</t>
         </is>
       </c>
       <c r="G138" s="25" t="n">
-        <v>44988</v>
+        <v>45618</v>
       </c>
       <c r="H138" s="25" t="n">
-        <v>46449</v>
+        <v>47079</v>
       </c>
       <c r="I138" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="J138" t="n">
         <v>4</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>ACT/365</t>
+          <t>30/360</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -22899,7 +22905,7 @@
         </is>
       </c>
       <c r="M138" s="25" t="n">
-        <v>46449</v>
+        <v>47079</v>
       </c>
       <c r="N138" t="n">
         <v>1</v>
@@ -22908,12 +22914,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>VSCRD</t>
+          <t>YFCMD</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Vista Energy</t>
+          <t>YPF Energia Electrica SA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -22923,7 +22929,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Servicios Públicos y Generación</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -22933,48 +22939,42 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>AR0138120560</t>
+          <t>AR0975634988</t>
         </is>
       </c>
       <c r="G139" s="25" t="n">
-        <v>45575</v>
+        <v>45797</v>
       </c>
       <c r="H139" s="25" t="n">
-        <v>48131</v>
+        <v>46527</v>
       </c>
       <c r="I139" t="n">
-        <v>7.65</v>
+        <v>6.5</v>
       </c>
       <c r="J139" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>ACT/365</t>
+          <t>30/360</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>amortizing</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="M139" s="25" t="n">
-        <v>47401</v>
+        <v>46527</v>
       </c>
       <c r="N139" t="n">
-        <v>3</v>
-      </c>
-      <c r="O139" t="n">
         <v>1</v>
-      </c>
-      <c r="P139" t="n">
-        <v>33</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>YFCLD</t>
+          <t>YFCAD</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -22999,20 +22999,20 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>AR0338531962</t>
+          <t>ARYPFE5600G5</t>
         </is>
       </c>
       <c r="G140" s="25" t="n">
-        <v>45618</v>
+        <v>44595</v>
       </c>
       <c r="H140" s="25" t="n">
-        <v>47079</v>
+        <v>48247</v>
       </c>
       <c r="I140" t="n">
-        <v>6.75</v>
+        <v>5</v>
       </c>
       <c r="J140" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -23021,20 +23021,26 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>amortizing</t>
         </is>
       </c>
       <c r="M140" s="25" t="n">
-        <v>47079</v>
+        <v>46602</v>
       </c>
       <c r="N140" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="O140" t="n">
+        <v>2</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>YFCMD</t>
+          <t>YFCND</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -23059,20 +23065,20 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>AR0975634988</t>
+          <t>AR0361875989</t>
         </is>
       </c>
       <c r="G141" s="25" t="n">
-        <v>45797</v>
+        <v>45933</v>
       </c>
       <c r="H141" s="25" t="n">
-        <v>46527</v>
+        <v>46298</v>
       </c>
       <c r="I141" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="J141" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -23085,7 +23091,7 @@
         </is>
       </c>
       <c r="M141" s="25" t="n">
-        <v>46527</v>
+        <v>46298</v>
       </c>
       <c r="N141" t="n">
         <v>1</v>
@@ -23094,12 +23100,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>YFCAD</t>
+          <t>YM40D</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>YPF Energia Electrica SA</t>
+          <t>YPF SA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -23109,7 +23115,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Servicios Públicos y Generación</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -23119,53 +23125,47 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>ARYPFE5600G5</t>
+          <t>AR0963751125</t>
         </is>
       </c>
       <c r="G142" s="25" t="n">
-        <v>44595</v>
+        <v>45897</v>
       </c>
       <c r="H142" s="25" t="n">
-        <v>48247</v>
+        <v>46993</v>
       </c>
       <c r="I142" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="J142" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>30/360</t>
+          <t>ACT/365</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>amortizing</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="M142" s="25" t="n">
-        <v>46602</v>
+        <v>46993</v>
       </c>
       <c r="N142" t="n">
-        <v>10</v>
-      </c>
-      <c r="O142" t="n">
-        <v>2</v>
-      </c>
-      <c r="P142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>YFCND</t>
+          <t>YM41D</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>YPF Energia Electrica SA</t>
+          <t>YPF SA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -23175,7 +23175,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Servicios Públicos y Generación</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -23185,24 +23185,24 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>AR0361875989</t>
+          <t>AR0675705039</t>
         </is>
       </c>
       <c r="G143" s="25" t="n">
-        <v>45933</v>
+        <v>45938</v>
       </c>
       <c r="H143" s="25" t="n">
-        <v>46298</v>
+        <v>46395</v>
       </c>
       <c r="I143" t="n">
         <v>6</v>
       </c>
       <c r="J143" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>30/360</t>
+          <t>ACT/365</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -23211,7 +23211,7 @@
         </is>
       </c>
       <c r="M143" s="25" t="n">
-        <v>46298</v>
+        <v>46395</v>
       </c>
       <c r="N143" t="n">
         <v>1</v>
@@ -23220,7 +23220,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>YM40D</t>
+          <t>YMCYD</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -23245,17 +23245,17 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>AR0963751125</t>
+          <t>AR0417757066</t>
         </is>
       </c>
       <c r="G144" s="25" t="n">
-        <v>45897</v>
+        <v>45575</v>
       </c>
       <c r="H144" s="25" t="n">
-        <v>46993</v>
+        <v>47036</v>
       </c>
       <c r="I144" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="J144" t="n">
         <v>4</v>
@@ -23271,7 +23271,7 @@
         </is>
       </c>
       <c r="M144" s="25" t="n">
-        <v>46993</v>
+        <v>47036</v>
       </c>
       <c r="N144" t="n">
         <v>1</v>
@@ -23280,7 +23280,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>YM41D</t>
+          <t>YMCTD</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -23305,20 +23305,17 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>AR0675705039</t>
+          <t>AR0688075032</t>
         </is>
       </c>
       <c r="G145" s="25" t="n">
-        <v>45938</v>
+        <v>45209</v>
       </c>
       <c r="H145" s="25" t="n">
-        <v>46395</v>
+        <v>46305</v>
       </c>
       <c r="I145" t="n">
-        <v>6</v>
-      </c>
-      <c r="J145" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
@@ -23331,16 +23328,22 @@
         </is>
       </c>
       <c r="M145" s="25" t="n">
-        <v>46395</v>
+        <v>46305</v>
       </c>
       <c r="N145" t="n">
         <v>1</v>
       </c>
+      <c r="O145" t="n">
+        <v>1</v>
+      </c>
+      <c r="P145" t="n">
+        <v>17.5</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>YMCYD</t>
+          <t>YM37D</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -23365,17 +23368,17 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>AR0417757066</t>
+          <t>AR0657794191</t>
         </is>
       </c>
       <c r="G146" s="25" t="n">
-        <v>45575</v>
+        <v>45784</v>
       </c>
       <c r="H146" s="25" t="n">
-        <v>47036</v>
+        <v>46514</v>
       </c>
       <c r="I146" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="J146" t="n">
         <v>4</v>
@@ -23391,7 +23394,7 @@
         </is>
       </c>
       <c r="M146" s="25" t="n">
-        <v>47036</v>
+        <v>46514</v>
       </c>
       <c r="N146" t="n">
         <v>1</v>
@@ -23400,7 +23403,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>YMCTD</t>
+          <t>YM35D</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -23425,17 +23428,20 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>AR0688075032</t>
+          <t>AR0929824099</t>
         </is>
       </c>
       <c r="G147" s="25" t="n">
-        <v>45209</v>
+        <v>45715</v>
       </c>
       <c r="H147" s="25" t="n">
-        <v>46305</v>
+        <v>46445</v>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>6.25</v>
+      </c>
+      <c r="J147" t="n">
+        <v>4</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -23448,22 +23454,16 @@
         </is>
       </c>
       <c r="M147" s="25" t="n">
-        <v>46305</v>
+        <v>46445</v>
       </c>
       <c r="N147" t="n">
         <v>1</v>
       </c>
-      <c r="O147" t="n">
-        <v>1</v>
-      </c>
-      <c r="P147" t="n">
-        <v>17.5</v>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>YM37D</t>
+          <t>YM39D</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -23488,20 +23488,20 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>AR0657794191</t>
+          <t>AR0081455617</t>
         </is>
       </c>
       <c r="G148" s="25" t="n">
-        <v>45784</v>
+        <v>45860</v>
       </c>
       <c r="H148" s="25" t="n">
-        <v>46514</v>
+        <v>47686</v>
       </c>
       <c r="I148" t="n">
-        <v>7</v>
+        <v>8.75</v>
       </c>
       <c r="J148" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -23514,7 +23514,7 @@
         </is>
       </c>
       <c r="M148" s="25" t="n">
-        <v>46514</v>
+        <v>47686</v>
       </c>
       <c r="N148" t="n">
         <v>1</v>
@@ -23523,7 +23523,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>YM35D</t>
+          <t>YM38D</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -23548,17 +23548,17 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>AR0929824099</t>
+          <t>AR0419238511</t>
         </is>
       </c>
       <c r="G149" s="25" t="n">
-        <v>45715</v>
+        <v>45860</v>
       </c>
       <c r="H149" s="25" t="n">
-        <v>46445</v>
+        <v>46590</v>
       </c>
       <c r="I149" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="J149" t="n">
         <v>4</v>
@@ -23574,7 +23574,7 @@
         </is>
       </c>
       <c r="M149" s="25" t="n">
-        <v>46445</v>
+        <v>46590</v>
       </c>
       <c r="N149" t="n">
         <v>1</v>
@@ -23583,7 +23583,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>YM39D</t>
+          <t>YM42D</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -23608,17 +23608,17 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>AR0081455617</t>
+          <t>AR0123407162</t>
         </is>
       </c>
       <c r="G150" s="25" t="n">
-        <v>45860</v>
+        <v>45993</v>
       </c>
       <c r="H150" s="25" t="n">
-        <v>47686</v>
+        <v>47179</v>
       </c>
       <c r="I150" t="n">
-        <v>8.75</v>
+        <v>7</v>
       </c>
       <c r="J150" t="n">
         <v>2</v>
@@ -23634,7 +23634,7 @@
         </is>
       </c>
       <c r="M150" s="25" t="n">
-        <v>47686</v>
+        <v>47179</v>
       </c>
       <c r="N150" t="n">
         <v>1</v>
@@ -23643,7 +23643,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>YM38D</t>
+          <t>YMCWD</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -23668,17 +23668,17 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>AR0419238511</t>
+          <t>AR0132676112</t>
         </is>
       </c>
       <c r="G151" s="25" t="n">
-        <v>45860</v>
+        <v>45474</v>
       </c>
       <c r="H151" s="25" t="n">
-        <v>46590</v>
+        <v>46204</v>
       </c>
       <c r="I151" t="n">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="J151" t="n">
         <v>4</v>
@@ -23694,16 +23694,19 @@
         </is>
       </c>
       <c r="M151" s="25" t="n">
-        <v>46590</v>
+        <v>46204</v>
       </c>
       <c r="N151" t="n">
         <v>1</v>
       </c>
+      <c r="O151" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>YM42D</t>
+          <t>YMCRD</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -23728,20 +23731,20 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>AR0123407162</t>
+          <t>ARYPFS5601X8</t>
         </is>
       </c>
       <c r="G152" s="25" t="n">
-        <v>45993</v>
+        <v>45181</v>
       </c>
       <c r="H152" s="25" t="n">
-        <v>47179</v>
+        <v>47008</v>
       </c>
       <c r="I152" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
@@ -23754,21 +23757,24 @@
         </is>
       </c>
       <c r="M152" s="25" t="n">
-        <v>47179</v>
+        <v>47008</v>
       </c>
       <c r="N152" t="n">
         <v>1</v>
       </c>
+      <c r="O152" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>YMCWD</t>
+          <t>IRCFD</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>YPF SA</t>
+          <t>IRSA S.A</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -23778,60 +23784,63 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t xml:space="preserve">Construcción </t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>AR0132676112</t>
+          <t>USP58809BH95</t>
         </is>
       </c>
       <c r="G153" s="25" t="n">
-        <v>45474</v>
+        <v>44750</v>
       </c>
       <c r="H153" s="25" t="n">
-        <v>46204</v>
+        <v>46926</v>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>8.75</v>
       </c>
       <c r="J153" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>ACT/365</t>
+          <t>30/360</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>amortizing</t>
         </is>
       </c>
       <c r="M153" s="25" t="n">
-        <v>46204</v>
+        <v>45465</v>
       </c>
       <c r="N153" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O153" t="n">
         <v>1</v>
       </c>
+      <c r="P153" t="n">
+        <v>17.5</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>YMCRD</t>
+          <t>TLCPD</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>YPF SA</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -23841,7 +23850,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Telecomunicaciones</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -23851,50 +23860,53 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>ARYPFS5601X8</t>
+          <t>USP9028NCA74</t>
         </is>
       </c>
       <c r="G154" s="25" t="n">
-        <v>45181</v>
+        <v>45805</v>
       </c>
       <c r="H154" s="25" t="n">
-        <v>47008</v>
+        <v>48727</v>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="J154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>ACT/365</t>
+          <t>30/360</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>amortizing</t>
         </is>
       </c>
       <c r="M154" s="25" t="n">
-        <v>47008</v>
+        <v>48362</v>
       </c>
       <c r="N154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O154" t="n">
         <v>1</v>
       </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>IRCFD</t>
+          <t>TLCTD</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>IRSA S.A</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -23904,7 +23916,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construcción </t>
+          <t>Telecomunicaciones</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -23914,17 +23926,17 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>USP58809BH95</t>
+          <t>USP9028NCE96</t>
         </is>
       </c>
       <c r="G155" s="25" t="n">
-        <v>44750</v>
+        <v>46042</v>
       </c>
       <c r="H155" s="25" t="n">
-        <v>46926</v>
+        <v>49694</v>
       </c>
       <c r="I155" t="n">
-        <v>8.75</v>
+        <v>8.5</v>
       </c>
       <c r="J155" t="n">
         <v>2</v>
@@ -23940,27 +23952,27 @@
         </is>
       </c>
       <c r="M155" s="25" t="n">
-        <v>45465</v>
+        <v>49329</v>
       </c>
       <c r="N155" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O155" t="n">
         <v>1</v>
       </c>
       <c r="P155" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>TLCPD</t>
+          <t>YFCID</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>YPF Energia Electrica SA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -23970,7 +23982,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Telecomunicaciones</t>
+          <t>Servicios Públicos y Generación</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -23980,20 +23992,20 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>USP9028NCA74</t>
+          <t>AR0947502206</t>
         </is>
       </c>
       <c r="G156" s="25" t="n">
-        <v>45805</v>
+        <v>45456</v>
       </c>
       <c r="H156" s="25" t="n">
-        <v>48727</v>
+        <v>46551</v>
       </c>
       <c r="I156" t="n">
-        <v>9.25</v>
+        <v>5.9</v>
       </c>
       <c r="J156" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -24006,13 +24018,13 @@
         </is>
       </c>
       <c r="M156" s="25" t="n">
-        <v>48362</v>
+        <v>46520</v>
       </c>
       <c r="N156" t="n">
         <v>2</v>
       </c>
       <c r="O156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P156" t="n">
         <v>0</v>
@@ -24021,12 +24033,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>TLCTD</t>
+          <t>YM43D</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>YPF SA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -24036,184 +24048,108 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Telecomunicaciones</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>USP9028NCE96</t>
+          <t>AR0156884063</t>
         </is>
       </c>
       <c r="G157" s="25" t="n">
-        <v>46042</v>
+        <v>46126</v>
       </c>
       <c r="H157" s="25" t="n">
-        <v>49694</v>
+        <v>47587</v>
       </c>
       <c r="I157" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="J157" t="n">
         <v>2</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>30/360</t>
+          <t>ACT/365</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>amortizing</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="M157" s="25" t="n">
-        <v>49329</v>
+        <v>47588</v>
       </c>
       <c r="N157" t="n">
-        <v>2</v>
-      </c>
-      <c r="O157" t="n">
         <v>1</v>
       </c>
-      <c r="P157" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>YFCID</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>YPF Energia Electrica SA</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
+      <c r="A158" s="24" t="inlineStr">
+        <is>
+          <t>AERBD</t>
+        </is>
+      </c>
+      <c r="B158" s="24" t="n"/>
+      <c r="C158" s="24" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Servicios Públicos y Generación</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>AR0947502206</t>
-        </is>
-      </c>
-      <c r="G158" s="25" t="n">
-        <v>45456</v>
-      </c>
-      <c r="H158" s="25" t="n">
-        <v>46551</v>
-      </c>
-      <c r="I158" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J158" t="n">
-        <v>4</v>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>30/360</t>
-        </is>
-      </c>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>amortizing</t>
-        </is>
-      </c>
-      <c r="M158" s="25" t="n">
-        <v>46520</v>
-      </c>
-      <c r="N158" t="n">
-        <v>2</v>
-      </c>
-      <c r="O158" t="n">
-        <v>2</v>
-      </c>
-      <c r="P158" t="n">
-        <v>0</v>
-      </c>
+      <c r="D158" s="24" t="n"/>
+      <c r="E158" s="24" t="n"/>
+      <c r="F158" s="24" t="n"/>
+      <c r="G158" s="24" t="n"/>
+      <c r="H158" s="24" t="n"/>
+      <c r="I158" s="24" t="n"/>
+      <c r="J158" s="24" t="n"/>
+      <c r="K158" s="24" t="n"/>
+      <c r="L158" s="24" t="n"/>
+      <c r="M158" s="24" t="n"/>
+      <c r="N158" s="24" t="n"/>
+      <c r="O158" s="24" t="n"/>
+      <c r="P158" s="24" t="n"/>
+      <c r="Q158" s="24" t="n"/>
+      <c r="R158" s="24" t="n"/>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>YM43D</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>YPF SA</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
+      <c r="A159" s="24" t="inlineStr">
+        <is>
+          <t>AFCHD</t>
+        </is>
+      </c>
+      <c r="B159" s="24" t="n"/>
+      <c r="C159" s="24" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Petróleo y Gas</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>AR0156884063</t>
-        </is>
-      </c>
-      <c r="G159" s="25" t="n">
-        <v>46126</v>
-      </c>
-      <c r="H159" s="25" t="n">
-        <v>47587</v>
-      </c>
-      <c r="I159" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J159" t="n">
-        <v>2</v>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>ACT/365</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>bullet</t>
-        </is>
-      </c>
-      <c r="M159" s="25" t="n">
-        <v>47588</v>
-      </c>
-      <c r="N159" t="n">
-        <v>1</v>
-      </c>
+      <c r="D159" s="24" t="n"/>
+      <c r="E159" s="24" t="n"/>
+      <c r="F159" s="24" t="n"/>
+      <c r="G159" s="24" t="n"/>
+      <c r="H159" s="24" t="n"/>
+      <c r="I159" s="24" t="n"/>
+      <c r="J159" s="24" t="n"/>
+      <c r="K159" s="24" t="n"/>
+      <c r="L159" s="24" t="n"/>
+      <c r="M159" s="24" t="n"/>
+      <c r="N159" s="24" t="n"/>
+      <c r="O159" s="24" t="n"/>
+      <c r="P159" s="24" t="n"/>
+      <c r="Q159" s="24" t="n"/>
+      <c r="R159" s="24" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="24" t="inlineStr">
         <is>
-          <t>AERBD</t>
+          <t>AFCID</t>
         </is>
       </c>
       <c r="B160" s="24" t="n"/>
@@ -24241,7 +24177,7 @@
     <row r="161">
       <c r="A161" s="24" t="inlineStr">
         <is>
-          <t>AFCHD</t>
+          <t>AFCJD</t>
         </is>
       </c>
       <c r="B161" s="24" t="n"/>
@@ -24269,7 +24205,7 @@
     <row r="162">
       <c r="A162" s="24" t="inlineStr">
         <is>
-          <t>AFCID</t>
+          <t>AFCKD</t>
         </is>
       </c>
       <c r="B162" s="24" t="n"/>
@@ -24297,7 +24233,7 @@
     <row r="163">
       <c r="A163" s="24" t="inlineStr">
         <is>
-          <t>AFCJD</t>
+          <t>BACHD</t>
         </is>
       </c>
       <c r="B163" s="24" t="n"/>
@@ -24325,7 +24261,7 @@
     <row r="164">
       <c r="A164" s="24" t="inlineStr">
         <is>
-          <t>AFCKD</t>
+          <t>BF37D</t>
         </is>
       </c>
       <c r="B164" s="24" t="n"/>
@@ -24353,7 +24289,7 @@
     <row r="165">
       <c r="A165" s="24" t="inlineStr">
         <is>
-          <t>BACHD</t>
+          <t>BF40D</t>
         </is>
       </c>
       <c r="B165" s="24" t="n"/>
@@ -24381,7 +24317,7 @@
     <row r="166">
       <c r="A166" s="24" t="inlineStr">
         <is>
-          <t>BF37D</t>
+          <t>BF45D</t>
         </is>
       </c>
       <c r="B166" s="24" t="n"/>
@@ -24409,7 +24345,7 @@
     <row r="167">
       <c r="A167" s="24" t="inlineStr">
         <is>
-          <t>BF40D</t>
+          <t>BGC4D</t>
         </is>
       </c>
       <c r="B167" s="24" t="n"/>
@@ -24437,7 +24373,7 @@
     <row r="168">
       <c r="A168" s="24" t="inlineStr">
         <is>
-          <t>BF45D</t>
+          <t>BPCSD</t>
         </is>
       </c>
       <c r="B168" s="24" t="n"/>
@@ -24465,7 +24401,7 @@
     <row r="169">
       <c r="A169" s="24" t="inlineStr">
         <is>
-          <t>BGC4D</t>
+          <t>BPCUD</t>
         </is>
       </c>
       <c r="B169" s="24" t="n"/>
@@ -24493,7 +24429,7 @@
     <row r="170">
       <c r="A170" s="24" t="inlineStr">
         <is>
-          <t>BPCSD</t>
+          <t>BPCVD</t>
         </is>
       </c>
       <c r="B170" s="24" t="n"/>
@@ -24521,7 +24457,7 @@
     <row r="171">
       <c r="A171" s="24" t="inlineStr">
         <is>
-          <t>BPCUD</t>
+          <t>BVCPD</t>
         </is>
       </c>
       <c r="B171" s="24" t="n"/>
@@ -24549,7 +24485,7 @@
     <row r="172">
       <c r="A172" s="24" t="inlineStr">
         <is>
-          <t>BPCVD</t>
+          <t>CACBD</t>
         </is>
       </c>
       <c r="B172" s="24" t="n"/>
@@ -24577,7 +24513,7 @@
     <row r="173">
       <c r="A173" s="24" t="inlineStr">
         <is>
-          <t>BVCPD</t>
+          <t>CIC7D</t>
         </is>
       </c>
       <c r="B173" s="24" t="n"/>
@@ -24605,7 +24541,7 @@
     <row r="174">
       <c r="A174" s="24" t="inlineStr">
         <is>
-          <t>CACBD</t>
+          <t>CIC8D</t>
         </is>
       </c>
       <c r="B174" s="24" t="n"/>
@@ -24633,7 +24569,7 @@
     <row r="175">
       <c r="A175" s="24" t="inlineStr">
         <is>
-          <t>CIC7D</t>
+          <t>CIC9D</t>
         </is>
       </c>
       <c r="B175" s="24" t="n"/>
@@ -24661,7 +24597,7 @@
     <row r="176">
       <c r="A176" s="24" t="inlineStr">
         <is>
-          <t>CIC8D</t>
+          <t>CICBD</t>
         </is>
       </c>
       <c r="B176" s="24" t="n"/>
@@ -24689,7 +24625,7 @@
     <row r="177">
       <c r="A177" s="24" t="inlineStr">
         <is>
-          <t>CIC9D</t>
+          <t>CLI1D</t>
         </is>
       </c>
       <c r="B177" s="24" t="n"/>
@@ -24717,7 +24653,7 @@
     <row r="178">
       <c r="A178" s="24" t="inlineStr">
         <is>
-          <t>CICBD</t>
+          <t>CLSID</t>
         </is>
       </c>
       <c r="B178" s="24" t="n"/>
@@ -24745,7 +24681,7 @@
     <row r="179">
       <c r="A179" s="24" t="inlineStr">
         <is>
-          <t>CLI1D</t>
+          <t>CP37D</t>
         </is>
       </c>
       <c r="B179" s="24" t="n"/>
@@ -24773,7 +24709,7 @@
     <row r="180">
       <c r="A180" s="24" t="inlineStr">
         <is>
-          <t>CLSID</t>
+          <t>CP38D</t>
         </is>
       </c>
       <c r="B180" s="24" t="n"/>
@@ -24801,7 +24737,7 @@
     <row r="181">
       <c r="A181" s="24" t="inlineStr">
         <is>
-          <t>CP37D</t>
+          <t>CS45D</t>
         </is>
       </c>
       <c r="B181" s="24" t="n"/>
@@ -24829,7 +24765,7 @@
     <row r="182">
       <c r="A182" s="24" t="inlineStr">
         <is>
-          <t>CP38D</t>
+          <t>CS51D</t>
         </is>
       </c>
       <c r="B182" s="24" t="n"/>
@@ -24857,7 +24793,7 @@
     <row r="183">
       <c r="A183" s="24" t="inlineStr">
         <is>
-          <t>CS45D</t>
+          <t>CS52D</t>
         </is>
       </c>
       <c r="B183" s="24" t="n"/>
@@ -24885,7 +24821,7 @@
     <row r="184">
       <c r="A184" s="24" t="inlineStr">
         <is>
-          <t>CS51D</t>
+          <t>CWC6D</t>
         </is>
       </c>
       <c r="B184" s="24" t="n"/>
@@ -24913,7 +24849,7 @@
     <row r="185">
       <c r="A185" s="24" t="inlineStr">
         <is>
-          <t>CS52D</t>
+          <t>DEC2D</t>
         </is>
       </c>
       <c r="B185" s="24" t="n"/>
@@ -24941,7 +24877,7 @@
     <row r="186">
       <c r="A186" s="24" t="inlineStr">
         <is>
-          <t>CWC6D</t>
+          <t>DNCAD</t>
         </is>
       </c>
       <c r="B186" s="24" t="n"/>
@@ -24969,7 +24905,7 @@
     <row r="187">
       <c r="A187" s="24" t="inlineStr">
         <is>
-          <t>DEC2D</t>
+          <t>EAC3D</t>
         </is>
       </c>
       <c r="B187" s="24" t="n"/>
@@ -24997,7 +24933,7 @@
     <row r="188">
       <c r="A188" s="24" t="inlineStr">
         <is>
-          <t>DNCAD</t>
+          <t>FO4AD</t>
         </is>
       </c>
       <c r="B188" s="24" t="n"/>
@@ -25025,7 +24961,7 @@
     <row r="189">
       <c r="A189" s="24" t="inlineStr">
         <is>
-          <t>EAC3D</t>
+          <t>FYC1D</t>
         </is>
       </c>
       <c r="B189" s="24" t="n"/>
@@ -25053,7 +24989,7 @@
     <row r="190">
       <c r="A190" s="24" t="inlineStr">
         <is>
-          <t>FO4AD</t>
+          <t>GN43D</t>
         </is>
       </c>
       <c r="B190" s="24" t="n"/>
@@ -25081,7 +25017,7 @@
     <row r="191">
       <c r="A191" s="24" t="inlineStr">
         <is>
-          <t>FYC1D</t>
+          <t>GN47D</t>
         </is>
       </c>
       <c r="B191" s="24" t="n"/>
@@ -25109,7 +25045,7 @@
     <row r="192">
       <c r="A192" s="24" t="inlineStr">
         <is>
-          <t>GN43D</t>
+          <t>GN48D</t>
         </is>
       </c>
       <c r="B192" s="24" t="n"/>
@@ -25137,7 +25073,7 @@
     <row r="193">
       <c r="A193" s="24" t="inlineStr">
         <is>
-          <t>GN47D</t>
+          <t>GN49D</t>
         </is>
       </c>
       <c r="B193" s="24" t="n"/>
@@ -25165,7 +25101,7 @@
     <row r="194">
       <c r="A194" s="24" t="inlineStr">
         <is>
-          <t>GN48D</t>
+          <t>GOC4D</t>
         </is>
       </c>
       <c r="B194" s="24" t="n"/>
@@ -25193,7 +25129,7 @@
     <row r="195">
       <c r="A195" s="24" t="inlineStr">
         <is>
-          <t>GN49D</t>
+          <t>GYC4D</t>
         </is>
       </c>
       <c r="B195" s="24" t="n"/>
@@ -25221,7 +25157,7 @@
     <row r="196">
       <c r="A196" s="24" t="inlineStr">
         <is>
-          <t>GOC4D</t>
+          <t>GYC5D</t>
         </is>
       </c>
       <c r="B196" s="24" t="n"/>
@@ -25249,7 +25185,7 @@
     <row r="197">
       <c r="A197" s="24" t="inlineStr">
         <is>
-          <t>GYC4D</t>
+          <t>HBCAD</t>
         </is>
       </c>
       <c r="B197" s="24" t="n"/>
@@ -25277,7 +25213,7 @@
     <row r="198">
       <c r="A198" s="24" t="inlineStr">
         <is>
-          <t>GYC5D</t>
+          <t>HBCDD</t>
         </is>
       </c>
       <c r="B198" s="24" t="n"/>
@@ -25305,7 +25241,7 @@
     <row r="199">
       <c r="A199" s="24" t="inlineStr">
         <is>
-          <t>HBCAD</t>
+          <t>HJCFD</t>
         </is>
       </c>
       <c r="B199" s="24" t="n"/>
@@ -25333,7 +25269,7 @@
     <row r="200">
       <c r="A200" s="24" t="inlineStr">
         <is>
-          <t>HBCDD</t>
+          <t>HJCGD</t>
         </is>
       </c>
       <c r="B200" s="24" t="n"/>
@@ -25361,7 +25297,7 @@
     <row r="201">
       <c r="A201" s="24" t="inlineStr">
         <is>
-          <t>HJCFD</t>
+          <t>HVS1D</t>
         </is>
       </c>
       <c r="B201" s="24" t="n"/>
@@ -25389,7 +25325,7 @@
     <row r="202">
       <c r="A202" s="24" t="inlineStr">
         <is>
-          <t>HJCGD</t>
+          <t>JNC5D</t>
         </is>
       </c>
       <c r="B202" s="24" t="n"/>
@@ -25417,7 +25353,7 @@
     <row r="203">
       <c r="A203" s="24" t="inlineStr">
         <is>
-          <t>HVS1D</t>
+          <t>JNC6D</t>
         </is>
       </c>
       <c r="B203" s="24" t="n"/>
@@ -25445,7 +25381,7 @@
     <row r="204">
       <c r="A204" s="24" t="inlineStr">
         <is>
-          <t>JNC5D</t>
+          <t>LDCGD</t>
         </is>
       </c>
       <c r="B204" s="24" t="n"/>
@@ -25473,7 +25409,7 @@
     <row r="205">
       <c r="A205" s="24" t="inlineStr">
         <is>
-          <t>JNC6D</t>
+          <t>LIC6D</t>
         </is>
       </c>
       <c r="B205" s="24" t="n"/>
@@ -25501,7 +25437,7 @@
     <row r="206">
       <c r="A206" s="24" t="inlineStr">
         <is>
-          <t>LDCGD</t>
+          <t>LUC5D</t>
         </is>
       </c>
       <c r="B206" s="24" t="n"/>
@@ -25529,7 +25465,7 @@
     <row r="207">
       <c r="A207" s="24" t="inlineStr">
         <is>
-          <t>LIC6D</t>
+          <t>MCC1D</t>
         </is>
       </c>
       <c r="B207" s="24" t="n"/>
@@ -25557,7 +25493,7 @@
     <row r="208">
       <c r="A208" s="24" t="inlineStr">
         <is>
-          <t>LUC5D</t>
+          <t>MCC2D</t>
         </is>
       </c>
       <c r="B208" s="24" t="n"/>
@@ -25585,7 +25521,7 @@
     <row r="209">
       <c r="A209" s="24" t="inlineStr">
         <is>
-          <t>MCC1D</t>
+          <t>MCC3D</t>
         </is>
       </c>
       <c r="B209" s="24" t="n"/>
@@ -25613,7 +25549,7 @@
     <row r="210">
       <c r="A210" s="24" t="inlineStr">
         <is>
-          <t>MCC2D</t>
+          <t>MIC3D</t>
         </is>
       </c>
       <c r="B210" s="24" t="n"/>
@@ -25641,7 +25577,7 @@
     <row r="211">
       <c r="A211" s="24" t="inlineStr">
         <is>
-          <t>MCC3D</t>
+          <t>MIC4D</t>
         </is>
       </c>
       <c r="B211" s="24" t="n"/>
@@ -25669,7 +25605,7 @@
     <row r="212">
       <c r="A212" s="24" t="inlineStr">
         <is>
-          <t>MIC3D</t>
+          <t>MIC6D</t>
         </is>
       </c>
       <c r="B212" s="24" t="n"/>
@@ -25697,7 +25633,7 @@
     <row r="213">
       <c r="A213" s="24" t="inlineStr">
         <is>
-          <t>MIC4D</t>
+          <t>MR39D</t>
         </is>
       </c>
       <c r="B213" s="24" t="n"/>
@@ -25725,7 +25661,7 @@
     <row r="214">
       <c r="A214" s="24" t="inlineStr">
         <is>
-          <t>MIC6D</t>
+          <t>MSSED</t>
         </is>
       </c>
       <c r="B214" s="24" t="n"/>
@@ -25753,7 +25689,7 @@
     <row r="215">
       <c r="A215" s="24" t="inlineStr">
         <is>
-          <t>MR39D</t>
+          <t>MSSFD</t>
         </is>
       </c>
       <c r="B215" s="24" t="n"/>
@@ -25781,7 +25717,7 @@
     <row r="216">
       <c r="A216" s="24" t="inlineStr">
         <is>
-          <t>MSSED</t>
+          <t>MSSGD</t>
         </is>
       </c>
       <c r="B216" s="24" t="n"/>
@@ -25809,7 +25745,7 @@
     <row r="217">
       <c r="A217" s="24" t="inlineStr">
         <is>
-          <t>MSSFD</t>
+          <t>MU31D</t>
         </is>
       </c>
       <c r="B217" s="24" t="n"/>
@@ -25837,7 +25773,7 @@
     <row r="218">
       <c r="A218" s="24" t="inlineStr">
         <is>
-          <t>MSSGD</t>
+          <t>MU32D</t>
         </is>
       </c>
       <c r="B218" s="24" t="n"/>
@@ -25865,7 +25801,7 @@
     <row r="219">
       <c r="A219" s="24" t="inlineStr">
         <is>
-          <t>MU31D</t>
+          <t>NBS1D</t>
         </is>
       </c>
       <c r="B219" s="24" t="n"/>
@@ -25893,7 +25829,7 @@
     <row r="220">
       <c r="A220" s="24" t="inlineStr">
         <is>
-          <t>MU32D</t>
+          <t>NPCDD</t>
         </is>
       </c>
       <c r="B220" s="24" t="n"/>
@@ -25921,7 +25857,7 @@
     <row r="221">
       <c r="A221" s="24" t="inlineStr">
         <is>
-          <t>NBS1D</t>
+          <t>OT41D</t>
         </is>
       </c>
       <c r="B221" s="24" t="n"/>
@@ -25949,7 +25885,7 @@
     <row r="222">
       <c r="A222" s="24" t="inlineStr">
         <is>
-          <t>NPCDD</t>
+          <t>OZC3D</t>
         </is>
       </c>
       <c r="B222" s="24" t="n"/>
@@ -25977,7 +25913,7 @@
     <row r="223">
       <c r="A223" s="24" t="inlineStr">
         <is>
-          <t>OT41D</t>
+          <t>PECMD</t>
         </is>
       </c>
       <c r="B223" s="24" t="n"/>
@@ -26005,7 +25941,7 @@
     <row r="224">
       <c r="A224" s="24" t="inlineStr">
         <is>
-          <t>OZC3D</t>
+          <t>PECND</t>
         </is>
       </c>
       <c r="B224" s="24" t="n"/>
@@ -26033,7 +25969,7 @@
     <row r="225">
       <c r="A225" s="24" t="inlineStr">
         <is>
-          <t>PECMD</t>
+          <t>PFC3D</t>
         </is>
       </c>
       <c r="B225" s="24" t="n"/>
@@ -26061,7 +25997,7 @@
     <row r="226">
       <c r="A226" s="24" t="inlineStr">
         <is>
-          <t>PECND</t>
+          <t>PN34D</t>
         </is>
       </c>
       <c r="B226" s="24" t="n"/>
@@ -26089,7 +26025,7 @@
     <row r="227">
       <c r="A227" s="24" t="inlineStr">
         <is>
-          <t>PFC3D</t>
+          <t>PQCRD</t>
         </is>
       </c>
       <c r="B227" s="24" t="n"/>
@@ -26117,7 +26053,7 @@
     <row r="228">
       <c r="A228" s="24" t="inlineStr">
         <is>
-          <t>PN34D</t>
+          <t>PQCTD</t>
         </is>
       </c>
       <c r="B228" s="24" t="n"/>
@@ -26145,7 +26081,7 @@
     <row r="229">
       <c r="A229" s="24" t="inlineStr">
         <is>
-          <t>PQCRD</t>
+          <t>PZCGD</t>
         </is>
       </c>
       <c r="B229" s="24" t="n"/>
@@ -26173,7 +26109,7 @@
     <row r="230">
       <c r="A230" s="24" t="inlineStr">
         <is>
-          <t>PQCTD</t>
+          <t>RC1CD</t>
         </is>
       </c>
       <c r="B230" s="24" t="n"/>
@@ -26201,7 +26137,7 @@
     <row r="231">
       <c r="A231" s="24" t="inlineStr">
         <is>
-          <t>PZCGD</t>
+          <t>RC3CD</t>
         </is>
       </c>
       <c r="B231" s="24" t="n"/>
@@ -26229,7 +26165,7 @@
     <row r="232">
       <c r="A232" s="24" t="inlineStr">
         <is>
-          <t>RC1CD</t>
+          <t>RC5CD</t>
         </is>
       </c>
       <c r="B232" s="24" t="n"/>
@@ -26257,7 +26193,7 @@
     <row r="233">
       <c r="A233" s="24" t="inlineStr">
         <is>
-          <t>RC3CD</t>
+          <t>RZ9BD</t>
         </is>
       </c>
       <c r="B233" s="24" t="n"/>
@@ -26285,7 +26221,7 @@
     <row r="234">
       <c r="A234" s="24" t="inlineStr">
         <is>
-          <t>RC5CD</t>
+          <t>RZABD</t>
         </is>
       </c>
       <c r="B234" s="24" t="n"/>
@@ -26313,7 +26249,7 @@
     <row r="235">
       <c r="A235" s="24" t="inlineStr">
         <is>
-          <t>RZ9BD</t>
+          <t>SBC1D</t>
         </is>
       </c>
       <c r="B235" s="24" t="n"/>
@@ -26341,7 +26277,7 @@
     <row r="236">
       <c r="A236" s="24" t="inlineStr">
         <is>
-          <t>RZABD</t>
+          <t>SBC2D</t>
         </is>
       </c>
       <c r="B236" s="24" t="n"/>
@@ -26369,7 +26305,7 @@
     <row r="237">
       <c r="A237" s="24" t="inlineStr">
         <is>
-          <t>SBC1D</t>
+          <t>SIC1D</t>
         </is>
       </c>
       <c r="B237" s="24" t="n"/>
@@ -26397,7 +26333,7 @@
     <row r="238">
       <c r="A238" s="24" t="inlineStr">
         <is>
-          <t>SBC2D</t>
+          <t>SNABD</t>
         </is>
       </c>
       <c r="B238" s="24" t="n"/>
@@ -26425,7 +26361,7 @@
     <row r="239">
       <c r="A239" s="24" t="inlineStr">
         <is>
-          <t>SIC1D</t>
+          <t>SNEAD</t>
         </is>
       </c>
       <c r="B239" s="24" t="n"/>
@@ -26453,7 +26389,7 @@
     <row r="240">
       <c r="A240" s="24" t="inlineStr">
         <is>
-          <t>SNABD</t>
+          <t>SNEBD</t>
         </is>
       </c>
       <c r="B240" s="24" t="n"/>
@@ -26481,7 +26417,7 @@
     <row r="241">
       <c r="A241" s="24" t="inlineStr">
         <is>
-          <t>SNEAD</t>
+          <t>SNSBD</t>
         </is>
       </c>
       <c r="B241" s="24" t="n"/>
@@ -26509,7 +26445,7 @@
     <row r="242">
       <c r="A242" s="24" t="inlineStr">
         <is>
-          <t>SNEBD</t>
+          <t>SNSDD</t>
         </is>
       </c>
       <c r="B242" s="24" t="n"/>
@@ -26537,7 +26473,7 @@
     <row r="243">
       <c r="A243" s="24" t="inlineStr">
         <is>
-          <t>SNSBD</t>
+          <t>STCFD</t>
         </is>
       </c>
       <c r="B243" s="24" t="n"/>
@@ -26565,7 +26501,7 @@
     <row r="244">
       <c r="A244" s="24" t="inlineStr">
         <is>
-          <t>SNSDD</t>
+          <t>SXC4D</t>
         </is>
       </c>
       <c r="B244" s="24" t="n"/>
@@ -26593,7 +26529,7 @@
     <row r="245">
       <c r="A245" s="24" t="inlineStr">
         <is>
-          <t>STCFD</t>
+          <t>T641D</t>
         </is>
       </c>
       <c r="B245" s="24" t="n"/>
@@ -26621,7 +26557,7 @@
     <row r="246">
       <c r="A246" s="24" t="inlineStr">
         <is>
-          <t>SXC4D</t>
+          <t>T672D</t>
         </is>
       </c>
       <c r="B246" s="24" t="n"/>
@@ -26649,7 +26585,7 @@
     <row r="247">
       <c r="A247" s="24" t="inlineStr">
         <is>
-          <t>T641D</t>
+          <t>TLCVD</t>
         </is>
       </c>
       <c r="B247" s="24" t="n"/>
@@ -26677,7 +26613,7 @@
     <row r="248">
       <c r="A248" s="24" t="inlineStr">
         <is>
-          <t>T672D</t>
+          <t>TLCWD</t>
         </is>
       </c>
       <c r="B248" s="24" t="n"/>
@@ -26705,7 +26641,7 @@
     <row r="249">
       <c r="A249" s="24" t="inlineStr">
         <is>
-          <t>TLCVD</t>
+          <t>TTCED</t>
         </is>
       </c>
       <c r="B249" s="24" t="n"/>
@@ -26733,7 +26669,7 @@
     <row r="250">
       <c r="A250" s="24" t="inlineStr">
         <is>
-          <t>TLCWD</t>
+          <t>VBC1D</t>
         </is>
       </c>
       <c r="B250" s="24" t="n"/>
@@ -26761,7 +26697,7 @@
     <row r="251">
       <c r="A251" s="24" t="inlineStr">
         <is>
-          <t>TTCED</t>
+          <t>VBC2D</t>
         </is>
       </c>
       <c r="B251" s="24" t="n"/>
@@ -26789,7 +26725,7 @@
     <row r="252">
       <c r="A252" s="24" t="inlineStr">
         <is>
-          <t>VBC1D</t>
+          <t>VSCID</t>
         </is>
       </c>
       <c r="B252" s="24" t="n"/>
@@ -26817,7 +26753,7 @@
     <row r="253">
       <c r="A253" s="24" t="inlineStr">
         <is>
-          <t>VBC2D</t>
+          <t>VSCPD</t>
         </is>
       </c>
       <c r="B253" s="24" t="n"/>
@@ -26845,7 +26781,7 @@
     <row r="254">
       <c r="A254" s="24" t="inlineStr">
         <is>
-          <t>VSCID</t>
+          <t>VSCXD</t>
         </is>
       </c>
       <c r="B254" s="24" t="n"/>
@@ -26873,7 +26809,7 @@
     <row r="255">
       <c r="A255" s="24" t="inlineStr">
         <is>
-          <t>VSCPD</t>
+          <t>WBS1D</t>
         </is>
       </c>
       <c r="B255" s="24" t="n"/>
@@ -26901,7 +26837,7 @@
     <row r="256">
       <c r="A256" s="24" t="inlineStr">
         <is>
-          <t>VSCXD</t>
+          <t>YFCKD</t>
         </is>
       </c>
       <c r="B256" s="24" t="n"/>
@@ -26929,7 +26865,7 @@
     <row r="257">
       <c r="A257" s="24" t="inlineStr">
         <is>
-          <t>WBS1D</t>
+          <t>ZPC2D</t>
         </is>
       </c>
       <c r="B257" s="24" t="n"/>
@@ -26957,7 +26893,7 @@
     <row r="258">
       <c r="A258" s="24" t="inlineStr">
         <is>
-          <t>YFCKD</t>
+          <t>ZPC3D</t>
         </is>
       </c>
       <c r="B258" s="24" t="n"/>
@@ -26985,7 +26921,7 @@
     <row r="259">
       <c r="A259" s="24" t="inlineStr">
         <is>
-          <t>ZPC2D</t>
+          <t>PUC2D</t>
         </is>
       </c>
       <c r="B259" s="24" t="n"/>
@@ -27013,7 +26949,7 @@
     <row r="260">
       <c r="A260" s="24" t="inlineStr">
         <is>
-          <t>ZPC3D</t>
+          <t>ICC6D</t>
         </is>
       </c>
       <c r="B260" s="24" t="n"/>
@@ -27038,62 +26974,6 @@
       <c r="Q260" s="24" t="n"/>
       <c r="R260" s="24" t="n"/>
     </row>
-    <row r="261">
-      <c r="A261" s="24" t="inlineStr">
-        <is>
-          <t>PUC2D</t>
-        </is>
-      </c>
-      <c r="B261" s="24" t="n"/>
-      <c r="C261" s="24" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
-      <c r="D261" s="24" t="n"/>
-      <c r="E261" s="24" t="n"/>
-      <c r="F261" s="24" t="n"/>
-      <c r="G261" s="24" t="n"/>
-      <c r="H261" s="24" t="n"/>
-      <c r="I261" s="24" t="n"/>
-      <c r="J261" s="24" t="n"/>
-      <c r="K261" s="24" t="n"/>
-      <c r="L261" s="24" t="n"/>
-      <c r="M261" s="24" t="n"/>
-      <c r="N261" s="24" t="n"/>
-      <c r="O261" s="24" t="n"/>
-      <c r="P261" s="24" t="n"/>
-      <c r="Q261" s="24" t="n"/>
-      <c r="R261" s="24" t="n"/>
-    </row>
-    <row r="262">
-      <c r="A262" s="24" t="inlineStr">
-        <is>
-          <t>ICC6D</t>
-        </is>
-      </c>
-      <c r="B262" s="24" t="n"/>
-      <c r="C262" s="24" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
-      <c r="D262" s="24" t="n"/>
-      <c r="E262" s="24" t="n"/>
-      <c r="F262" s="24" t="n"/>
-      <c r="G262" s="24" t="n"/>
-      <c r="H262" s="24" t="n"/>
-      <c r="I262" s="24" t="n"/>
-      <c r="J262" s="24" t="n"/>
-      <c r="K262" s="24" t="n"/>
-      <c r="L262" s="24" t="n"/>
-      <c r="M262" s="24" t="n"/>
-      <c r="N262" s="24" t="n"/>
-      <c r="O262" s="24" t="n"/>
-      <c r="P262" s="24" t="n"/>
-      <c r="Q262" s="24" t="n"/>
-      <c r="R262" s="24" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/instruments_master.xlsx
+++ b/data/instruments_master.xlsx
@@ -14424,7 +14424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R260"/>
+  <dimension ref="A1:R261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26974,6 +26974,34 @@
       <c r="Q260" s="24" t="n"/>
       <c r="R260" s="24" t="n"/>
     </row>
+    <row r="261">
+      <c r="A261" s="24" t="inlineStr">
+        <is>
+          <t>MJC1D</t>
+        </is>
+      </c>
+      <c r="B261" s="24" t="n"/>
+      <c r="C261" s="24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D261" s="24" t="n"/>
+      <c r="E261" s="24" t="n"/>
+      <c r="F261" s="24" t="n"/>
+      <c r="G261" s="24" t="n"/>
+      <c r="H261" s="24" t="n"/>
+      <c r="I261" s="24" t="n"/>
+      <c r="J261" s="24" t="n"/>
+      <c r="K261" s="24" t="n"/>
+      <c r="L261" s="24" t="n"/>
+      <c r="M261" s="24" t="n"/>
+      <c r="N261" s="24" t="n"/>
+      <c r="O261" s="24" t="n"/>
+      <c r="P261" s="24" t="n"/>
+      <c r="Q261" s="24" t="n"/>
+      <c r="R261" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/instruments_master.xlsx
+++ b/data/instruments_master.xlsx
@@ -2071,7 +2071,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2572,32 +2572,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="18.75" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>S12J6</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>LECAP</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="F20" s="3" t="n"/>
-    </row>
+    <row r="20" ht="18.75" customHeight="1"/>
     <row r="21" ht="18.75" customHeight="1"/>
     <row r="22" ht="18.75" customHeight="1"/>
     <row r="23" ht="18.75" customHeight="1"/>
@@ -14424,7 +14399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R261"/>
+  <dimension ref="A1:R263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15092,7 +15067,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IRCLD</t>
+          <t>IRCND</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -15116,13 +15091,13 @@
         </is>
       </c>
       <c r="G11" s="25" t="n">
-        <v>45453</v>
+        <v>45588</v>
       </c>
       <c r="H11" s="25" t="n">
-        <v>46183</v>
+        <v>46683</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
@@ -15138,7 +15113,7 @@
         </is>
       </c>
       <c r="M11" s="25" t="n">
-        <v>46183</v>
+        <v>46683</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
@@ -15147,18 +15122,18 @@
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IRCND</t>
+          <t>OT42D</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IRSA S.A</t>
+          <t>Oiltanking Ebytem SA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -15168,7 +15143,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construcción </t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -15177,16 +15152,16 @@
         </is>
       </c>
       <c r="G12" s="25" t="n">
-        <v>45588</v>
+        <v>45674</v>
       </c>
       <c r="H12" s="25" t="n">
-        <v>46683</v>
+        <v>47500</v>
       </c>
       <c r="I12" t="n">
-        <v>5.75</v>
+        <v>8</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -15199,22 +15174,16 @@
         </is>
       </c>
       <c r="M12" s="25" t="n">
-        <v>46683</v>
+        <v>47500</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
       </c>
-      <c r="O12" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OT42D</t>
+          <t>OTS2D</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -15238,13 +15207,13 @@
         </is>
       </c>
       <c r="G13" s="25" t="n">
-        <v>45674</v>
+        <v>45406</v>
       </c>
       <c r="H13" s="25" t="n">
-        <v>47500</v>
+        <v>46501</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J13" t="n">
         <v>4</v>
@@ -15260,7 +15229,7 @@
         </is>
       </c>
       <c r="M13" s="25" t="n">
-        <v>47500</v>
+        <v>46501</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
@@ -15269,7 +15238,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OTS2D</t>
+          <t>OTS3D</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -15293,10 +15262,10 @@
         </is>
       </c>
       <c r="G14" s="25" t="n">
-        <v>45406</v>
+        <v>45597</v>
       </c>
       <c r="H14" s="25" t="n">
-        <v>46501</v>
+        <v>47058</v>
       </c>
       <c r="I14" t="n">
         <v>7</v>
@@ -15315,7 +15284,7 @@
         </is>
       </c>
       <c r="M14" s="25" t="n">
-        <v>46501</v>
+        <v>47058</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
@@ -15324,12 +15293,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OTS3D</t>
+          <t>YFCGD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Oiltanking Ebytem SA</t>
+          <t>YPF Energia Electrica SA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -15339,7 +15308,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Servicios Públicos y Generación</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -15348,13 +15317,13 @@
         </is>
       </c>
       <c r="G15" s="25" t="n">
-        <v>45597</v>
+        <v>45349</v>
       </c>
       <c r="H15" s="25" t="n">
-        <v>47058</v>
+        <v>46445</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
@@ -15370,7 +15339,7 @@
         </is>
       </c>
       <c r="M15" s="25" t="n">
-        <v>47058</v>
+        <v>46445</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
@@ -15379,7 +15348,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>YFCGD</t>
+          <t>YFCOD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -15403,20 +15372,20 @@
         </is>
       </c>
       <c r="G16" s="25" t="n">
-        <v>45349</v>
+        <v>46006</v>
       </c>
       <c r="H16" s="25" t="n">
-        <v>46445</v>
+        <v>47102</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="J16" t="n">
         <v>4</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>ACT/365</t>
+          <t>30/360</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -15425,7 +15394,7 @@
         </is>
       </c>
       <c r="M16" s="25" t="n">
-        <v>46445</v>
+        <v>47102</v>
       </c>
       <c r="N16" t="n">
         <v>1</v>
@@ -15434,12 +15403,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>YFCOD</t>
+          <t>YMCZD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>YPF Energia Electrica SA</t>
+          <t>YPF SA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -15449,7 +15418,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Servicios Públicos y Generación</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -15458,20 +15427,20 @@
         </is>
       </c>
       <c r="G17" s="25" t="n">
-        <v>46006</v>
+        <v>45575</v>
       </c>
       <c r="H17" s="25" t="n">
-        <v>47102</v>
+        <v>47036</v>
       </c>
       <c r="I17" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>30/360</t>
+          <t>ACT/365</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -15480,7 +15449,7 @@
         </is>
       </c>
       <c r="M17" s="25" t="n">
-        <v>47102</v>
+        <v>47036</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
@@ -15489,12 +15458,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>YMCZD</t>
+          <t>PNDCD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>YPF SA</t>
+          <t>Pan American Energy SL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -15509,47 +15478,58 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>USE7S78BAB82</t>
         </is>
       </c>
       <c r="G18" s="25" t="n">
-        <v>45575</v>
+        <v>44316</v>
       </c>
       <c r="H18" s="25" t="n">
-        <v>47036</v>
+        <v>46507</v>
       </c>
       <c r="I18" t="n">
-        <v>7</v>
+        <v>9.125</v>
       </c>
       <c r="J18" t="n">
         <v>2</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>ACT/365</t>
+          <t>30/360</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>amortizing</t>
         </is>
       </c>
       <c r="M18" s="25" t="n">
-        <v>47036</v>
+        <v>45777</v>
       </c>
       <c r="N18" t="n">
+        <v>5</v>
+      </c>
+      <c r="O18" t="n">
         <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PNDCD</t>
+          <t>CAC5D</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pan American Energy SL</t>
+          <t>Capex SA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -15569,17 +15549,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>USE7S78BAB82</t>
+          <t>USP20058AE63</t>
         </is>
       </c>
       <c r="G19" s="25" t="n">
-        <v>44316</v>
+        <v>45163</v>
       </c>
       <c r="H19" s="25" t="n">
-        <v>46507</v>
+        <v>46990</v>
       </c>
       <c r="I19" t="n">
-        <v>9.125</v>
+        <v>9.25</v>
       </c>
       <c r="J19" t="n">
         <v>2</v>
@@ -15595,13 +15575,13 @@
         </is>
       </c>
       <c r="M19" s="25" t="n">
-        <v>45777</v>
+        <v>45713</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -15610,12 +15590,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CAC5D</t>
+          <t>YMCID</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capex SA</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -15635,17 +15615,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>USP20058AE63</t>
+          <t>USP989MJBS99</t>
         </is>
       </c>
       <c r="G20" s="25" t="n">
-        <v>45163</v>
+        <v>44239</v>
       </c>
       <c r="H20" s="25" t="n">
-        <v>46990</v>
+        <v>47299</v>
       </c>
       <c r="I20" t="n">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="J20" t="n">
         <v>2</v>
@@ -15661,10 +15641,10 @@
         </is>
       </c>
       <c r="M20" s="25" t="n">
-        <v>45713</v>
+        <v>46203</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
@@ -15676,12 +15656,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>YMCID</t>
+          <t>BYCHD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>Banco de Galicia y Buenos Aires SAU</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -15691,7 +15671,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Sector Financiero</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -15701,17 +15681,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>USP989MJBS99</t>
+          <t>USP0R66CAB48</t>
         </is>
       </c>
       <c r="G21" s="25" t="n">
-        <v>44239</v>
+        <v>45575</v>
       </c>
       <c r="H21" s="25" t="n">
-        <v>47299</v>
+        <v>47036</v>
       </c>
       <c r="I21" t="n">
-        <v>9</v>
+        <v>7.75</v>
       </c>
       <c r="J21" t="n">
         <v>2</v>
@@ -15723,31 +15703,25 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>amortizing</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="M21" s="25" t="n">
-        <v>46203</v>
+        <v>47036</v>
       </c>
       <c r="N21" t="n">
-        <v>7</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BYCHD</t>
+          <t>BACGD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Banco de Galicia y Buenos Aires SAU</t>
+          <t>Banco Macro S.A.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -15767,17 +15741,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>USP0R66CAB48</t>
+          <t>USP1047VAL10</t>
         </is>
       </c>
       <c r="G22" s="25" t="n">
-        <v>45575</v>
+        <v>45831</v>
       </c>
       <c r="H22" s="25" t="n">
-        <v>47036</v>
+        <v>47292</v>
       </c>
       <c r="I22" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="J22" t="n">
         <v>2</v>
@@ -15792,22 +15766,27 @@
           <t>bullet</t>
         </is>
       </c>
-      <c r="M22" s="25" t="n">
-        <v>47036</v>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>25/6/2029</t>
+        </is>
       </c>
       <c r="N22" t="n">
         <v>1</v>
       </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BACGD</t>
+          <t>DNC7D</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Banco Macro S.A.</t>
+          <t>EDENOR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -15817,7 +15796,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sector Financiero</t>
+          <t>Servicios Públicos y Generación</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -15827,17 +15806,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>USP1047VAL10</t>
+          <t>USP3710FAU86</t>
         </is>
       </c>
       <c r="G23" s="25" t="n">
-        <v>45831</v>
+        <v>45589</v>
       </c>
       <c r="H23" s="25" t="n">
-        <v>47292</v>
+        <v>47780</v>
       </c>
       <c r="I23" t="n">
-        <v>8</v>
+        <v>9.75</v>
       </c>
       <c r="J23" t="n">
         <v>2</v>
@@ -15849,30 +15828,31 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>bullet</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>25/6/2029</t>
-        </is>
+          <t>amortizing</t>
+        </is>
+      </c>
+      <c r="M23" s="25" t="n">
+        <v>47050</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
       </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DNC7D</t>
+          <t>YMCXD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EDENOR</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -15882,7 +15862,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Servicios Públicos y Generación</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -15892,17 +15872,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>USP3710FAU86</t>
+          <t>USP989MJBV29</t>
         </is>
       </c>
       <c r="G24" s="25" t="n">
-        <v>45589</v>
+        <v>45546</v>
       </c>
       <c r="H24" s="25" t="n">
-        <v>47780</v>
+        <v>48102</v>
       </c>
       <c r="I24" t="n">
-        <v>9.75</v>
+        <v>8.75</v>
       </c>
       <c r="J24" t="n">
         <v>2</v>
@@ -15918,7 +15898,7 @@
         </is>
       </c>
       <c r="M24" s="25" t="n">
-        <v>47050</v>
+        <v>47372</v>
       </c>
       <c r="N24" t="n">
         <v>3</v>
@@ -15927,18 +15907,18 @@
         <v>1</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>YMCXD</t>
+          <t>PLC5D</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>Pluspetrol S.A.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -15958,17 +15938,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>USP989MJBV29</t>
+          <t>USP7924AAC29</t>
         </is>
       </c>
       <c r="G25" s="25" t="n">
-        <v>45546</v>
+        <v>45979</v>
       </c>
       <c r="H25" s="25" t="n">
-        <v>48102</v>
+        <v>47986</v>
       </c>
       <c r="I25" t="n">
-        <v>8.75</v>
+        <v>8.125</v>
       </c>
       <c r="J25" t="n">
         <v>2</v>
@@ -15980,31 +15960,25 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>amortizing</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="M25" s="25" t="n">
-        <v>47372</v>
+        <v>47987</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
-      </c>
-      <c r="O25" t="n">
         <v>1</v>
-      </c>
-      <c r="P25" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PLC5D</t>
+          <t>YFCJD</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pluspetrol S.A.</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -16024,17 +15998,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>USP7924AAC29</t>
+          <t>USP9897PAS31</t>
         </is>
       </c>
       <c r="G26" s="25" t="n">
-        <v>45979</v>
+        <v>45581</v>
       </c>
       <c r="H26" s="25" t="n">
-        <v>47986</v>
+        <v>48503</v>
       </c>
       <c r="I26" t="n">
-        <v>8.125</v>
+        <v>7.875</v>
       </c>
       <c r="J26" t="n">
         <v>2</v>
@@ -16046,25 +16020,31 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>amortizing</t>
         </is>
       </c>
       <c r="M26" s="25" t="n">
-        <v>47987</v>
+        <v>47772</v>
       </c>
       <c r="N26" t="n">
+        <v>3</v>
+      </c>
+      <c r="O26" t="n">
         <v>1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>YFCJD</t>
+          <t>TTCAD</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>Tecpetrol S.A.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -16084,17 +16064,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>USP9897PAS31</t>
+          <t>USP90187AR99</t>
         </is>
       </c>
       <c r="G27" s="25" t="n">
-        <v>45581</v>
+        <v>45679</v>
       </c>
       <c r="H27" s="25" t="n">
-        <v>48503</v>
+        <v>48601</v>
       </c>
       <c r="I27" t="n">
-        <v>7.875</v>
+        <v>7.625</v>
       </c>
       <c r="J27" t="n">
         <v>2</v>
@@ -16110,7 +16090,7 @@
         </is>
       </c>
       <c r="M27" s="25" t="n">
-        <v>47772</v>
+        <v>47870</v>
       </c>
       <c r="N27" t="n">
         <v>3</v>
@@ -16125,12 +16105,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TTCAD</t>
+          <t>VSCVD</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tecpetrol S.A.</t>
+          <t>Vista Energy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -16150,17 +16130,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>USP90187AR99</t>
+          <t>USP9659RAB44</t>
         </is>
       </c>
       <c r="G28" s="25" t="n">
-        <v>45679</v>
+        <v>45818</v>
       </c>
       <c r="H28" s="25" t="n">
-        <v>48601</v>
+        <v>48740</v>
       </c>
       <c r="I28" t="n">
-        <v>7.625</v>
+        <v>8.5</v>
       </c>
       <c r="J28" t="n">
         <v>2</v>
@@ -16176,7 +16156,7 @@
         </is>
       </c>
       <c r="M28" s="25" t="n">
-        <v>47870</v>
+        <v>48009</v>
       </c>
       <c r="N28" t="n">
         <v>3</v>
@@ -16191,12 +16171,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>VSCVD</t>
+          <t>YM34D</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vista Energy</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -16216,17 +16196,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>USP9659RAB44</t>
+          <t>USP989MJBY67</t>
         </is>
       </c>
       <c r="G29" s="25" t="n">
-        <v>45818</v>
+        <v>45674</v>
       </c>
       <c r="H29" s="25" t="n">
-        <v>48740</v>
+        <v>48961</v>
       </c>
       <c r="I29" t="n">
-        <v>8.5</v>
+        <v>8.25</v>
       </c>
       <c r="J29" t="n">
         <v>2</v>
@@ -16242,7 +16222,7 @@
         </is>
       </c>
       <c r="M29" s="25" t="n">
-        <v>48009</v>
+        <v>48232</v>
       </c>
       <c r="N29" t="n">
         <v>3</v>
@@ -16251,18 +16231,18 @@
         <v>1</v>
       </c>
       <c r="P29" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>YM34D</t>
+          <t>MGCOD</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>Pampa Energía S.A.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -16272,7 +16252,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Servicios Públicos y Generación</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -16282,17 +16262,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>USP989MJBY67</t>
+          <t>USP7464EAT30</t>
         </is>
       </c>
       <c r="G30" s="25" t="n">
-        <v>45674</v>
+        <v>45642</v>
       </c>
       <c r="H30" s="25" t="n">
-        <v>48961</v>
+        <v>49294</v>
       </c>
       <c r="I30" t="n">
-        <v>8.25</v>
+        <v>7.875</v>
       </c>
       <c r="J30" t="n">
         <v>2</v>
@@ -16304,31 +16284,28 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>amortizing</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="M30" s="25" t="n">
-        <v>48232</v>
+        <v>49296</v>
       </c>
       <c r="N30" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" t="n">
         <v>3</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1</v>
-      </c>
-      <c r="P30" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MGCOD</t>
+          <t>TSC4D</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pampa Energía S.A.</t>
+          <t>Transportadora de Gas del Sur S.A. (TGS)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -16348,17 +16325,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>USP7464EAT30</t>
+          <t>USP9308RBB89</t>
         </is>
       </c>
       <c r="G31" s="25" t="n">
-        <v>45642</v>
+        <v>45981</v>
       </c>
       <c r="H31" s="25" t="n">
-        <v>49294</v>
+        <v>49633</v>
       </c>
       <c r="I31" t="n">
-        <v>7.875</v>
+        <v>7.75</v>
       </c>
       <c r="J31" t="n">
         <v>2</v>
@@ -16374,24 +16351,21 @@
         </is>
       </c>
       <c r="M31" s="25" t="n">
-        <v>49296</v>
+        <v>49633</v>
       </c>
       <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="O31" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TSC4D</t>
+          <t>MGCRD</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Transportadora de Gas del Sur S.A. (TGS)</t>
+          <t>Pampa Energía S.A.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -16411,14 +16385,14 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>USP9308RBB89</t>
+          <t>USP7464EAY25</t>
         </is>
       </c>
       <c r="G32" s="25" t="n">
-        <v>45981</v>
+        <v>45975</v>
       </c>
       <c r="H32" s="25" t="n">
-        <v>49633</v>
+        <v>50358</v>
       </c>
       <c r="I32" t="n">
         <v>7.75</v>
@@ -16437,7 +16411,7 @@
         </is>
       </c>
       <c r="M32" s="25" t="n">
-        <v>49633</v>
+        <v>50358</v>
       </c>
       <c r="N32" t="n">
         <v>1</v>
@@ -16446,12 +16420,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MGCRD</t>
+          <t>MTCGD</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pampa Energía S.A.</t>
+          <t>Mastellone Hnos. S.A.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -16461,7 +16435,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Servicios Públicos y Generación</t>
+          <t>Consumo Masivo y Agro</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -16471,20 +16445,20 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>USP7464EAY25</t>
+          <t>USP6460MAK01</t>
         </is>
       </c>
       <c r="G33" s="25" t="n">
-        <v>45975</v>
+        <v>44377</v>
       </c>
       <c r="H33" s="25" t="n">
-        <v>50358</v>
+        <v>46203</v>
       </c>
       <c r="I33" t="n">
-        <v>7.75</v>
+        <v>10.95</v>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -16497,7 +16471,7 @@
         </is>
       </c>
       <c r="M33" s="25" t="n">
-        <v>50358</v>
+        <v>46203</v>
       </c>
       <c r="N33" t="n">
         <v>1</v>
@@ -16506,12 +16480,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MTCGD</t>
+          <t>YCAMD</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mastellone Hnos. S.A.</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -16521,7 +16495,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Consumo Masivo y Agro</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -16531,20 +16505,20 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>USP6460MAK01</t>
+          <t>USP989MJBL47</t>
         </is>
       </c>
       <c r="G34" s="25" t="n">
-        <v>44377</v>
+        <v>42937</v>
       </c>
       <c r="H34" s="25" t="n">
-        <v>46203</v>
+        <v>46589</v>
       </c>
       <c r="I34" t="n">
-        <v>10.95</v>
+        <v>6.95</v>
       </c>
       <c r="J34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -16557,21 +16531,27 @@
         </is>
       </c>
       <c r="M34" s="25" t="n">
-        <v>46203</v>
+        <v>46589</v>
       </c>
       <c r="N34" t="n">
         <v>1</v>
       </c>
+      <c r="O34" t="n">
+        <v>3</v>
+      </c>
+      <c r="P34" t="n">
+        <v>8.33</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>YCAMD</t>
+          <t>RUCDD</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>MSU Energy S.A.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -16581,7 +16561,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Servicios Públicos y Generación</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -16591,17 +16571,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>USP989MJBL47</t>
+          <t>USP7000QAJ96</t>
         </is>
       </c>
       <c r="G35" s="25" t="n">
-        <v>42937</v>
+        <v>45631</v>
       </c>
       <c r="H35" s="25" t="n">
-        <v>46589</v>
+        <v>47822</v>
       </c>
       <c r="I35" t="n">
-        <v>6.95</v>
+        <v>9.75</v>
       </c>
       <c r="J35" t="n">
         <v>2</v>
@@ -16613,31 +16593,31 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>amortizing</t>
         </is>
       </c>
       <c r="M35" s="25" t="n">
-        <v>46589</v>
+        <v>47092</v>
       </c>
       <c r="N35" t="n">
+        <v>3</v>
+      </c>
+      <c r="O35" t="n">
         <v>1</v>
       </c>
-      <c r="O35" t="n">
-        <v>3</v>
-      </c>
       <c r="P35" t="n">
-        <v>8.33</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RUCDD</t>
+          <t>TLCMD</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MSU Energy S.A.</t>
+          <t>Telecom Argentina S.A.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -16647,7 +16627,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Servicios Públicos y Generación</t>
+          <t>Telecomunicaciones</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -16657,17 +16637,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>USP7000QAJ96</t>
+          <t>USP9028NBT74</t>
         </is>
       </c>
       <c r="G36" s="25" t="n">
-        <v>45631</v>
+        <v>45491</v>
       </c>
       <c r="H36" s="25" t="n">
-        <v>47822</v>
+        <v>48047</v>
       </c>
       <c r="I36" t="n">
-        <v>9.75</v>
+        <v>9.5</v>
       </c>
       <c r="J36" t="n">
         <v>2</v>
@@ -16683,7 +16663,7 @@
         </is>
       </c>
       <c r="M36" s="25" t="n">
-        <v>47092</v>
+        <v>47317</v>
       </c>
       <c r="N36" t="n">
         <v>3</v>
@@ -16692,18 +16672,18 @@
         <v>1</v>
       </c>
       <c r="P36" t="n">
-        <v>17.5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TLCMD</t>
+          <t>TTCDD</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Telecom Argentina S.A.</t>
+          <t>Tecpetrol S.A.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -16713,7 +16693,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Telecomunicaciones</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -16723,17 +16703,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>USP9028NBT74</t>
+          <t>USP90187AT55</t>
         </is>
       </c>
       <c r="G37" s="25" t="n">
-        <v>45491</v>
+        <v>45964</v>
       </c>
       <c r="H37" s="25" t="n">
-        <v>48047</v>
+        <v>47790</v>
       </c>
       <c r="I37" t="n">
-        <v>9.5</v>
+        <v>7.625</v>
       </c>
       <c r="J37" t="n">
         <v>2</v>
@@ -16745,31 +16725,25 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>amortizing</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="M37" s="25" t="n">
-        <v>47317</v>
+        <v>47790</v>
       </c>
       <c r="N37" t="n">
-        <v>3</v>
-      </c>
-      <c r="O37" t="n">
         <v>1</v>
-      </c>
-      <c r="P37" t="n">
-        <v>33</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TTCDD</t>
+          <t>PNXCD</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tecpetrol S.A.</t>
+          <t>Pan American Energy SL</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -16789,17 +16763,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>USP90187AT55</t>
+          <t>USE7S78BAC65</t>
         </is>
       </c>
       <c r="G38" s="25" t="n">
-        <v>45964</v>
+        <v>45412</v>
       </c>
       <c r="H38" s="25" t="n">
-        <v>47790</v>
+        <v>48334</v>
       </c>
       <c r="I38" t="n">
-        <v>7.625</v>
+        <v>8.5</v>
       </c>
       <c r="J38" t="n">
         <v>2</v>
@@ -16811,25 +16785,31 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>amortizing</t>
         </is>
       </c>
       <c r="M38" s="25" t="n">
-        <v>47790</v>
+        <v>47603</v>
       </c>
       <c r="N38" t="n">
+        <v>3</v>
+      </c>
+      <c r="O38" t="n">
         <v>1</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PNXCD</t>
+          <t>TSC3D</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pan American Energy SL</t>
+          <t>Transportadora de Gas del Sur S.A. (TGS)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -16839,7 +16819,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Servicios Públicos y Generación</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -16849,14 +16829,14 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>USE7S78BAC65</t>
+          <t>USP9308RBA07</t>
         </is>
       </c>
       <c r="G39" s="25" t="n">
-        <v>45412</v>
+        <v>45497</v>
       </c>
       <c r="H39" s="25" t="n">
-        <v>48334</v>
+        <v>48053</v>
       </c>
       <c r="I39" t="n">
         <v>8.5</v>
@@ -16871,31 +16851,25 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>amortizing</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="M39" s="25" t="n">
-        <v>47603</v>
+        <v>48053</v>
       </c>
       <c r="N39" t="n">
         <v>3</v>
       </c>
-      <c r="O39" t="n">
-        <v>1</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TSC3D</t>
+          <t>MGCMD</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Transportadora de Gas del Sur S.A. (TGS)</t>
+          <t>Pampa Energía S.A.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -16915,17 +16889,17 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>USP9308RBA07</t>
+          <t>USP7464EAS56</t>
         </is>
       </c>
       <c r="G40" s="25" t="n">
-        <v>45497</v>
+        <v>45545</v>
       </c>
       <c r="H40" s="25" t="n">
-        <v>48053</v>
+        <v>48101</v>
       </c>
       <c r="I40" t="n">
-        <v>8.5</v>
+        <v>7.95</v>
       </c>
       <c r="J40" t="n">
         <v>2</v>
@@ -16941,21 +16915,21 @@
         </is>
       </c>
       <c r="M40" s="25" t="n">
-        <v>48053</v>
+        <v>48101</v>
       </c>
       <c r="N40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MGCMD</t>
+          <t>PLC4D</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pampa Energía S.A.</t>
+          <t>Pluspetrol S.A.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -16965,7 +16939,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Servicios Públicos y Generación</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -16975,17 +16949,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>USP7464EAS56</t>
+          <t>USP7924AAA62</t>
         </is>
       </c>
       <c r="G41" s="25" t="n">
-        <v>45545</v>
+        <v>45807</v>
       </c>
       <c r="H41" s="25" t="n">
-        <v>48101</v>
+        <v>48364</v>
       </c>
       <c r="I41" t="n">
-        <v>7.95</v>
+        <v>8.5</v>
       </c>
       <c r="J41" t="n">
         <v>2</v>
@@ -17001,7 +16975,7 @@
         </is>
       </c>
       <c r="M41" s="25" t="n">
-        <v>48101</v>
+        <v>48364</v>
       </c>
       <c r="N41" t="n">
         <v>1</v>
@@ -17010,12 +16984,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PLC4D</t>
+          <t>YMCJD</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pluspetrol S.A.</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -17035,17 +17009,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>USP7924AAA62</t>
+          <t>USP989MJBT72</t>
         </is>
       </c>
       <c r="G42" s="25" t="n">
-        <v>45807</v>
+        <v>44239</v>
       </c>
       <c r="H42" s="25" t="n">
-        <v>48364</v>
+        <v>48852</v>
       </c>
       <c r="I42" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="J42" t="n">
         <v>2</v>
@@ -17057,25 +17031,31 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>amortizing</t>
         </is>
       </c>
       <c r="M42" s="25" t="n">
-        <v>48364</v>
+        <v>47756</v>
       </c>
       <c r="N42" t="n">
+        <v>4</v>
+      </c>
+      <c r="O42" t="n">
         <v>1</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>YMCJD</t>
+          <t>IRCPD</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>IRSA Inversiones y Representaciones S.A.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -17085,7 +17065,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Bienes Raíces</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -17095,17 +17075,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>USP989MJBT72</t>
+          <t>USP58809BU07</t>
         </is>
       </c>
       <c r="G43" s="25" t="n">
-        <v>44239</v>
+        <v>45747</v>
       </c>
       <c r="H43" s="25" t="n">
-        <v>48852</v>
+        <v>49399</v>
       </c>
       <c r="I43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J43" t="n">
         <v>2</v>
@@ -17121,27 +17101,27 @@
         </is>
       </c>
       <c r="M43" s="25" t="n">
-        <v>47756</v>
+        <v>48669</v>
       </c>
       <c r="N43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IRCPD</t>
+          <t>VSCTD</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IRSA Inversiones y Representaciones S.A.</t>
+          <t>Vista Energy</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -17151,7 +17131,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Bienes Raíces</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -17161,17 +17141,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>USP58809BU07</t>
+          <t>USP9659RAA60</t>
         </is>
       </c>
       <c r="G44" s="25" t="n">
-        <v>45747</v>
+        <v>45636</v>
       </c>
       <c r="H44" s="25" t="n">
-        <v>49399</v>
+        <v>49653</v>
       </c>
       <c r="I44" t="n">
-        <v>8</v>
+        <v>7.625</v>
       </c>
       <c r="J44" t="n">
         <v>2</v>
@@ -17187,7 +17167,7 @@
         </is>
       </c>
       <c r="M44" s="25" t="n">
-        <v>48669</v>
+        <v>48923</v>
       </c>
       <c r="N44" t="n">
         <v>3</v>
@@ -17202,12 +17182,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>VSCTD</t>
+          <t>PN43D</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vista Energy</t>
+          <t>Pan American Energy SL</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -17227,17 +17207,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>USP9659RAA60</t>
+          <t>USE7S78BAD49</t>
         </is>
       </c>
       <c r="G45" s="25" t="n">
-        <v>45636</v>
+        <v>46037</v>
       </c>
       <c r="H45" s="25" t="n">
-        <v>49653</v>
+        <v>50055</v>
       </c>
       <c r="I45" t="n">
-        <v>7.625</v>
+        <v>7.75</v>
       </c>
       <c r="J45" t="n">
         <v>2</v>
@@ -17249,31 +17229,25 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>amortizing</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="M45" s="25" t="n">
-        <v>48923</v>
+        <v>49324</v>
       </c>
       <c r="N45" t="n">
         <v>3</v>
       </c>
-      <c r="O45" t="n">
-        <v>1</v>
-      </c>
-      <c r="P45" t="n">
-        <v>33</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PN43D</t>
+          <t>AER5D</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pan American Energy SL</t>
+          <t>Aeropuertos Argentina 2000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -17283,57 +17257,63 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura y Transporte</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>USE7S78BAD49</t>
+          <t>ARAEAR560090</t>
         </is>
       </c>
       <c r="G46" s="25" t="n">
-        <v>46037</v>
+        <v>44613</v>
       </c>
       <c r="H46" s="25" t="n">
-        <v>50055</v>
+        <v>48265</v>
       </c>
       <c r="I46" t="n">
-        <v>7.75</v>
+        <v>5.5</v>
       </c>
       <c r="J46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>30/360</t>
+          <t>ACT/365</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>amortizing</t>
         </is>
       </c>
       <c r="M46" s="25" t="n">
-        <v>49324</v>
+        <v>46528</v>
       </c>
       <c r="N46" t="n">
+        <v>20</v>
+      </c>
+      <c r="O46" t="n">
         <v>3</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AER5D</t>
+          <t>LMS8D</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Aeropuertos Argentina 2000</t>
+          <t>Aluar</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -17343,7 +17323,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Infraestructura y Transporte</t>
+          <t>Bienes Raíces</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -17353,48 +17333,42 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ARAEAR560090</t>
+          <t>AR0787528089</t>
         </is>
       </c>
       <c r="G47" s="25" t="n">
-        <v>44613</v>
+        <v>45372</v>
       </c>
       <c r="H47" s="25" t="n">
-        <v>48265</v>
+        <v>46467</v>
       </c>
       <c r="I47" t="n">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="J47" t="n">
         <v>4</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>ACT/365</t>
+          <t>actual/360</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>amortizing</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="M47" s="25" t="n">
-        <v>46528</v>
+        <v>46468</v>
       </c>
       <c r="N47" t="n">
-        <v>20</v>
-      </c>
-      <c r="O47" t="n">
-        <v>3</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>LMS9D</t>
+          <t>LMS6D</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -17419,24 +17393,24 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AR0226237573</t>
+          <t>ARALUA560047</t>
         </is>
       </c>
       <c r="G48" s="25" t="n">
-        <v>45456</v>
+        <v>45043</v>
       </c>
       <c r="H48" s="25" t="n">
-        <v>46186</v>
+        <v>46870</v>
       </c>
       <c r="I48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
         <v>4</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>30/360</t>
+          <t>ACT/365</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -17445,7 +17419,7 @@
         </is>
       </c>
       <c r="M48" s="25" t="n">
-        <v>46186</v>
+        <v>46870</v>
       </c>
       <c r="N48" t="n">
         <v>1</v>
@@ -17454,7 +17428,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LMS8D</t>
+          <t>LMS7D</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -17479,47 +17453,53 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AR0787528089</t>
+          <t>AR0183513875</t>
         </is>
       </c>
       <c r="G49" s="25" t="n">
-        <v>45372</v>
+        <v>45211</v>
       </c>
       <c r="H49" s="25" t="n">
-        <v>46467</v>
+        <v>47038</v>
       </c>
       <c r="I49" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="J49" t="n">
         <v>4</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>actual/360</t>
+          <t>30/360</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>amortizing</t>
         </is>
       </c>
       <c r="M49" s="25" t="n">
-        <v>46468</v>
+        <v>46034</v>
       </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="O49" t="n">
+        <v>3</v>
+      </c>
+      <c r="P49" t="n">
+        <v>8.33</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LMS6D</t>
+          <t>RCCRD</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Aluar</t>
+          <t>Arcor</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -17529,7 +17509,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Bienes Raíces</t>
+          <t>Consumo Masivo y Agro</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -17539,20 +17519,20 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ARALUA560047</t>
+          <t>AR0016944933</t>
         </is>
       </c>
       <c r="G50" s="25" t="n">
-        <v>45043</v>
+        <v>45786</v>
       </c>
       <c r="H50" s="25" t="n">
-        <v>46870</v>
+        <v>46516</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="J50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -17565,21 +17545,27 @@
         </is>
       </c>
       <c r="M50" s="25" t="n">
-        <v>46870</v>
+        <v>46516</v>
       </c>
       <c r="N50" t="n">
         <v>1</v>
       </c>
+      <c r="O50" t="n">
+        <v>2</v>
+      </c>
+      <c r="P50" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LMS7D</t>
+          <t>RC2CD</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Aluar</t>
+          <t>Arcor</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -17589,7 +17575,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Bienes Raíces</t>
+          <t>Consumo Masivo y Agro</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -17599,53 +17585,47 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AR0183513875</t>
+          <t>AR0004792187</t>
         </is>
       </c>
       <c r="G51" s="25" t="n">
-        <v>45211</v>
+        <v>45936</v>
       </c>
       <c r="H51" s="25" t="n">
-        <v>47038</v>
+        <v>46301</v>
       </c>
       <c r="I51" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="J51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>30/360</t>
+          <t>ACT/365</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>amortizing</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="M51" s="25" t="n">
-        <v>46034</v>
+        <v>46301</v>
       </c>
       <c r="N51" t="n">
-        <v>12</v>
-      </c>
-      <c r="O51" t="n">
-        <v>3</v>
-      </c>
-      <c r="P51" t="n">
-        <v>8.33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>RCCRD</t>
+          <t>BF39D</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Arcor</t>
+          <t>Banco BBVA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -17655,7 +17635,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Consumo Masivo y Agro</t>
+          <t>Sector Financiero</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -17665,17 +17645,17 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AR0016944933</t>
+          <t>AR0914780439</t>
         </is>
       </c>
       <c r="G52" s="25" t="n">
-        <v>45786</v>
+        <v>45996</v>
       </c>
       <c r="H52" s="25" t="n">
-        <v>46516</v>
+        <v>46361</v>
       </c>
       <c r="I52" t="n">
-        <v>6.75</v>
+        <v>5.75</v>
       </c>
       <c r="J52" t="n">
         <v>2</v>
@@ -17691,27 +17671,21 @@
         </is>
       </c>
       <c r="M52" s="25" t="n">
-        <v>46516</v>
+        <v>46361</v>
       </c>
       <c r="N52" t="n">
         <v>1</v>
       </c>
-      <c r="O52" t="n">
-        <v>2</v>
-      </c>
-      <c r="P52" t="n">
-        <v>11</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>RC2CD</t>
+          <t>BYCXD</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Arcor</t>
+          <t>Banco Galicia</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -17721,7 +17695,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Consumo Masivo y Agro</t>
+          <t>Sector Financiero</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -17731,17 +17705,17 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AR0004792187</t>
+          <t>AR0185542955</t>
         </is>
       </c>
       <c r="G53" s="25" t="n">
-        <v>45936</v>
+        <v>46013</v>
       </c>
       <c r="H53" s="25" t="n">
-        <v>46301</v>
+        <v>46386</v>
       </c>
       <c r="I53" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="J53" t="n">
         <v>2</v>
@@ -17757,7 +17731,7 @@
         </is>
       </c>
       <c r="M53" s="25" t="n">
-        <v>46301</v>
+        <v>46386</v>
       </c>
       <c r="N53" t="n">
         <v>1</v>
@@ -17766,12 +17740,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BF39D</t>
+          <t>BYCVD</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Banco BBVA</t>
+          <t>Banco Galicia</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -17791,17 +17765,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AR0914780439</t>
+          <t>AR0422946126</t>
         </is>
       </c>
       <c r="G54" s="25" t="n">
-        <v>45996</v>
+        <v>45883</v>
       </c>
       <c r="H54" s="25" t="n">
-        <v>46361</v>
+        <v>46265</v>
       </c>
       <c r="I54" t="n">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="J54" t="n">
         <v>2</v>
@@ -17817,7 +17791,7 @@
         </is>
       </c>
       <c r="M54" s="25" t="n">
-        <v>46361</v>
+        <v>46265</v>
       </c>
       <c r="N54" t="n">
         <v>1</v>
@@ -17826,7 +17800,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BYCXD</t>
+          <t>BYCWD</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -17851,17 +17825,17 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>AR0185542955</t>
+          <t>AR0098652693</t>
         </is>
       </c>
       <c r="G55" s="25" t="n">
-        <v>46013</v>
+        <v>45975</v>
       </c>
       <c r="H55" s="25" t="n">
-        <v>46386</v>
+        <v>46356</v>
       </c>
       <c r="I55" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="J55" t="n">
         <v>2</v>
@@ -17877,7 +17851,7 @@
         </is>
       </c>
       <c r="M55" s="25" t="n">
-        <v>46386</v>
+        <v>46356</v>
       </c>
       <c r="N55" t="n">
         <v>1</v>
@@ -17886,12 +17860,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BYCVD</t>
+          <t>ZZC1D</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Banco Galicia</t>
+          <t>Camuzzi Gas Pampeana</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -17901,7 +17875,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sector Financiero</t>
+          <t>Servicios Públicos y Generación</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -17911,17 +17885,17 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AR0422946126</t>
+          <t>AR0352269929</t>
         </is>
       </c>
       <c r="G56" s="25" t="n">
-        <v>45883</v>
+        <v>45709</v>
       </c>
       <c r="H56" s="25" t="n">
-        <v>46265</v>
+        <v>46439</v>
       </c>
       <c r="I56" t="n">
-        <v>6.25</v>
+        <v>7.95</v>
       </c>
       <c r="J56" t="n">
         <v>2</v>
@@ -17937,7 +17911,7 @@
         </is>
       </c>
       <c r="M56" s="25" t="n">
-        <v>46265</v>
+        <v>46439</v>
       </c>
       <c r="N56" t="n">
         <v>1</v>
@@ -17946,12 +17920,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BYCWD</t>
+          <t>CACAD</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Banco Galicia</t>
+          <t>Capex SA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -17961,7 +17935,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Sector Financiero</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -17971,20 +17945,20 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AR0098652693</t>
+          <t>AR0669378199</t>
         </is>
       </c>
       <c r="G57" s="25" t="n">
-        <v>45975</v>
+        <v>45478</v>
       </c>
       <c r="H57" s="25" t="n">
-        <v>46356</v>
+        <v>46573</v>
       </c>
       <c r="I57" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -17997,7 +17971,7 @@
         </is>
       </c>
       <c r="M57" s="25" t="n">
-        <v>46356</v>
+        <v>46573</v>
       </c>
       <c r="N57" t="n">
         <v>1</v>
@@ -18006,12 +17980,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ZZC1D</t>
+          <t>CACDD</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Camuzzi Gas Pampeana</t>
+          <t>Capex SA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -18021,7 +17995,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Servicios Públicos y Generación</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -18031,17 +18005,17 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AR0352269929</t>
+          <t>AR0629138345</t>
         </is>
       </c>
       <c r="G58" s="25" t="n">
-        <v>45709</v>
+        <v>45995</v>
       </c>
       <c r="H58" s="25" t="n">
-        <v>46439</v>
+        <v>47273</v>
       </c>
       <c r="I58" t="n">
-        <v>7.95</v>
+        <v>8.25</v>
       </c>
       <c r="J58" t="n">
         <v>2</v>
@@ -18057,7 +18031,7 @@
         </is>
       </c>
       <c r="M58" s="25" t="n">
-        <v>46439</v>
+        <v>47273</v>
       </c>
       <c r="N58" t="n">
         <v>1</v>
@@ -18066,12 +18040,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CACAD</t>
+          <t>NPCCD</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capex SA</t>
+          <t>Central Puerto SA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -18081,7 +18055,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Servicios Públicos y Generación</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -18091,20 +18065,20 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AR0669378199</t>
+          <t>AR0630055561</t>
         </is>
       </c>
       <c r="G59" s="25" t="n">
-        <v>45478</v>
+        <v>45894</v>
       </c>
       <c r="H59" s="25" t="n">
-        <v>46573</v>
+        <v>47355</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -18117,7 +18091,7 @@
         </is>
       </c>
       <c r="M59" s="25" t="n">
-        <v>46573</v>
+        <v>47355</v>
       </c>
       <c r="N59" t="n">
         <v>1</v>
@@ -18126,12 +18100,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CACDD</t>
+          <t>CICAD</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Capex SA</t>
+          <t>CNH</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -18141,7 +18115,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura y Transporte</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -18151,17 +18125,17 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AR0629138345</t>
+          <t>AR0027069092</t>
         </is>
       </c>
       <c r="G60" s="25" t="n">
-        <v>45995</v>
+        <v>45994</v>
       </c>
       <c r="H60" s="25" t="n">
-        <v>47273</v>
+        <v>46907</v>
       </c>
       <c r="I60" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="J60" t="n">
         <v>2</v>
@@ -18177,7 +18151,7 @@
         </is>
       </c>
       <c r="M60" s="25" t="n">
-        <v>47273</v>
+        <v>46907</v>
       </c>
       <c r="N60" t="n">
         <v>1</v>
@@ -18186,12 +18160,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NPCCD</t>
+          <t>CP40D</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Central Puerto SA</t>
+          <t>CGC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -18201,7 +18175,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Servicios Públicos y Generación</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -18211,20 +18185,20 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AR0630055561</t>
+          <t>AR0360181769</t>
         </is>
       </c>
       <c r="G61" s="25" t="n">
-        <v>45894</v>
+        <v>46090</v>
       </c>
       <c r="H61" s="25" t="n">
-        <v>47355</v>
+        <v>46821</v>
       </c>
       <c r="I61" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="J61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -18237,7 +18211,7 @@
         </is>
       </c>
       <c r="M61" s="25" t="n">
-        <v>47355</v>
+        <v>46821</v>
       </c>
       <c r="N61" t="n">
         <v>1</v>
@@ -18246,12 +18220,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CICAD</t>
+          <t>CP36D</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CNH</t>
+          <t>CGC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -18261,7 +18235,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Infraestructura y Transporte</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -18271,17 +18245,17 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AR0027069092</t>
+          <t>AR0015464982</t>
         </is>
       </c>
       <c r="G62" s="25" t="n">
-        <v>45994</v>
+        <v>45575</v>
       </c>
       <c r="H62" s="25" t="n">
-        <v>46907</v>
+        <v>46670</v>
       </c>
       <c r="I62" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="J62" t="n">
         <v>2</v>
@@ -18297,7 +18271,7 @@
         </is>
       </c>
       <c r="M62" s="25" t="n">
-        <v>46907</v>
+        <v>46670</v>
       </c>
       <c r="N62" t="n">
         <v>1</v>
@@ -18306,7 +18280,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CP31D</t>
+          <t>CP27D</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -18331,20 +18305,20 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ARCGCO5600W3</t>
+          <t>ARCGCO5600S1</t>
         </is>
       </c>
       <c r="G63" s="25" t="n">
-        <v>45086</v>
+        <v>44719</v>
       </c>
       <c r="H63" s="25" t="n">
-        <v>46182</v>
+        <v>47276</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -18353,20 +18327,26 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>amortizing</t>
         </is>
       </c>
       <c r="M63" s="25" t="n">
-        <v>46182</v>
+        <v>46180</v>
       </c>
       <c r="N63" t="n">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="O63" t="n">
+        <v>2</v>
+      </c>
+      <c r="P63" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CP40D</t>
+          <t>CP39D</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -18391,17 +18371,17 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AR0360181769</t>
+          <t>AR0100497988</t>
         </is>
       </c>
       <c r="G64" s="25" t="n">
-        <v>46090</v>
+        <v>46020</v>
       </c>
       <c r="H64" s="25" t="n">
-        <v>46821</v>
+        <v>46475</v>
       </c>
       <c r="I64" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="J64" t="n">
         <v>4</v>
@@ -18417,7 +18397,7 @@
         </is>
       </c>
       <c r="M64" s="25" t="n">
-        <v>46821</v>
+        <v>46475</v>
       </c>
       <c r="N64" t="n">
         <v>1</v>
@@ -18426,7 +18406,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CP36D</t>
+          <t>CP28D</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -18451,20 +18431,20 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AR0015464982</t>
+          <t>ARCGCO5600T9</t>
         </is>
       </c>
       <c r="G65" s="25" t="n">
-        <v>45575</v>
+        <v>44811</v>
       </c>
       <c r="H65" s="25" t="n">
-        <v>46670</v>
+        <v>46272</v>
       </c>
       <c r="I65" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -18473,25 +18453,31 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>amortizing</t>
         </is>
       </c>
       <c r="M65" s="25" t="n">
-        <v>46670</v>
+        <v>46088</v>
       </c>
       <c r="N65" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="O65" t="n">
+        <v>3</v>
+      </c>
+      <c r="P65" t="n">
+        <v>33.33</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CP27D</t>
+          <t>EMC1D</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CGC</t>
+          <t>Compania Mega SA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -18511,17 +18497,17 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>ARCGCO5600S1</t>
+          <t>AR0339892116</t>
         </is>
       </c>
       <c r="G66" s="25" t="n">
-        <v>44719</v>
+        <v>45842</v>
       </c>
       <c r="H66" s="25" t="n">
-        <v>47276</v>
+        <v>46572</v>
       </c>
       <c r="I66" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="J66" t="n">
         <v>2</v>
@@ -18533,31 +18519,25 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>amortizing</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="M66" s="25" t="n">
-        <v>46180</v>
+        <v>46572</v>
       </c>
       <c r="N66" t="n">
-        <v>9</v>
-      </c>
-      <c r="O66" t="n">
-        <v>2</v>
-      </c>
-      <c r="P66" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CP39D</t>
+          <t>CS47D</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CGC</t>
+          <t>Cresud</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -18567,7 +18547,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Consumo Masivo y Agro</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -18577,20 +18557,20 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AR0100497988</t>
+          <t>AR0892513117</t>
         </is>
       </c>
       <c r="G67" s="25" t="n">
-        <v>46020</v>
+        <v>45611</v>
       </c>
       <c r="H67" s="25" t="n">
-        <v>46475</v>
+        <v>47072</v>
       </c>
       <c r="I67" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -18603,7 +18583,7 @@
         </is>
       </c>
       <c r="M67" s="25" t="n">
-        <v>46475</v>
+        <v>47072</v>
       </c>
       <c r="N67" t="n">
         <v>1</v>
@@ -18612,12 +18592,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CP28D</t>
+          <t>CS50D</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CGC</t>
+          <t>Cresud</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -18627,7 +18607,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Consumo Masivo y Agro</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -18637,20 +18617,20 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ARCGCO5600T9</t>
+          <t>AR0394353335</t>
         </is>
       </c>
       <c r="G68" s="25" t="n">
-        <v>44811</v>
+        <v>46001</v>
       </c>
       <c r="H68" s="25" t="n">
-        <v>46272</v>
+        <v>47187</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -18659,31 +18639,25 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>amortizing</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="M68" s="25" t="n">
-        <v>46088</v>
+        <v>47187</v>
       </c>
       <c r="N68" t="n">
-        <v>3</v>
-      </c>
-      <c r="O68" t="n">
-        <v>3</v>
-      </c>
-      <c r="P68" t="n">
-        <v>33.33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EMC1D</t>
+          <t>DNC8D</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Compania Mega SA</t>
+          <t>Empresa Distribuidora y Comercializadora Norte SA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -18693,7 +18667,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Servicios Públicos y Generación</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -18703,17 +18677,17 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AR0339892116</t>
+          <t>AR0787561361</t>
         </is>
       </c>
       <c r="G69" s="25" t="n">
-        <v>45842</v>
+        <v>45876</v>
       </c>
       <c r="H69" s="25" t="n">
-        <v>46572</v>
+        <v>46241</v>
       </c>
       <c r="I69" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="J69" t="n">
         <v>2</v>
@@ -18729,7 +18703,7 @@
         </is>
       </c>
       <c r="M69" s="25" t="n">
-        <v>46572</v>
+        <v>46241</v>
       </c>
       <c r="N69" t="n">
         <v>1</v>
@@ -18738,12 +18712,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CS47D</t>
+          <t>DNC5D</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cresud</t>
+          <t>Empresa Distribuidora y Comercializadora Norte SA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -18753,7 +18727,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Consumo Masivo y Agro</t>
+          <t>Servicios Públicos y Generación</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -18763,17 +18737,17 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>AR0892513117</t>
+          <t>AR0674196495</t>
         </is>
       </c>
       <c r="G70" s="25" t="n">
-        <v>45611</v>
+        <v>45509</v>
       </c>
       <c r="H70" s="25" t="n">
-        <v>47072</v>
+        <v>46970</v>
       </c>
       <c r="I70" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="J70" t="n">
         <v>2</v>
@@ -18789,7 +18763,7 @@
         </is>
       </c>
       <c r="M70" s="25" t="n">
-        <v>47072</v>
+        <v>46970</v>
       </c>
       <c r="N70" t="n">
         <v>1</v>
@@ -18798,12 +18772,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CS50D</t>
+          <t>DNC3D</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cresud</t>
+          <t>Empresa Distribuidora y Comercializadora Norte SA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -18813,7 +18787,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Consumo Masivo y Agro</t>
+          <t>Servicios Públicos y Generación</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -18823,17 +18797,17 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>AR0394353335</t>
+          <t>AR0140482933</t>
         </is>
       </c>
       <c r="G71" s="25" t="n">
-        <v>46001</v>
+        <v>45358</v>
       </c>
       <c r="H71" s="25" t="n">
-        <v>47187</v>
+        <v>46348</v>
       </c>
       <c r="I71" t="n">
-        <v>7.25</v>
+        <v>9.75</v>
       </c>
       <c r="J71" t="n">
         <v>2</v>
@@ -18849,7 +18823,7 @@
         </is>
       </c>
       <c r="M71" s="25" t="n">
-        <v>47187</v>
+        <v>46348</v>
       </c>
       <c r="N71" t="n">
         <v>1</v>
@@ -18858,12 +18832,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DNC8D</t>
+          <t>GN36D</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Empresa Distribuidora y Comercializadora Norte SA</t>
+          <t>Genneia SA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -18883,20 +18857,20 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AR0787561361</t>
+          <t>AREMGA5600O4</t>
         </is>
       </c>
       <c r="G72" s="25" t="n">
-        <v>45876</v>
+        <v>44553</v>
       </c>
       <c r="H72" s="25" t="n">
-        <v>46241</v>
+        <v>48205</v>
       </c>
       <c r="I72" t="n">
-        <v>8.5</v>
+        <v>5.65</v>
       </c>
       <c r="J72" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -18909,7 +18883,7 @@
         </is>
       </c>
       <c r="M72" s="25" t="n">
-        <v>46241</v>
+        <v>48205</v>
       </c>
       <c r="N72" t="n">
         <v>1</v>
@@ -18918,12 +18892,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DNC5D</t>
+          <t>GN46D</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Empresa Distribuidora y Comercializadora Norte SA</t>
+          <t>Genneia SA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -18943,20 +18917,20 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>AR0674196495</t>
+          <t>AR0086415137</t>
         </is>
       </c>
       <c r="G73" s="25" t="n">
-        <v>45509</v>
+        <v>45470</v>
       </c>
       <c r="H73" s="25" t="n">
-        <v>46970</v>
+        <v>46200</v>
       </c>
       <c r="I73" t="n">
-        <v>9.5</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -18969,7 +18943,7 @@
         </is>
       </c>
       <c r="M73" s="25" t="n">
-        <v>46970</v>
+        <v>46200</v>
       </c>
       <c r="N73" t="n">
         <v>1</v>
@@ -18978,12 +18952,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DNC3D</t>
+          <t>GN38D</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Empresa Distribuidora y Comercializadora Norte SA</t>
+          <t>Genneia SA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -19003,20 +18977,20 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>AR0140482933</t>
+          <t>AREMGA5600Q9</t>
         </is>
       </c>
       <c r="G74" s="25" t="n">
-        <v>45358</v>
+        <v>44967</v>
       </c>
       <c r="H74" s="25" t="n">
-        <v>46348</v>
+        <v>48620</v>
       </c>
       <c r="I74" t="n">
-        <v>9.75</v>
+        <v>4.5</v>
       </c>
       <c r="J74" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -19029,7 +19003,7 @@
         </is>
       </c>
       <c r="M74" s="25" t="n">
-        <v>46348</v>
+        <v>48620</v>
       </c>
       <c r="N74" t="n">
         <v>1</v>
@@ -19038,12 +19012,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>GN36D</t>
+          <t>DMC7D</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Genneia SA</t>
+          <t>Impsa SA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -19053,7 +19027,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Servicios Públicos y Generación</t>
+          <t>Infraestructura y Transporte</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -19063,20 +19037,20 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>AREMGA5600O4</t>
+          <t>ARIPSA5600A2</t>
         </is>
       </c>
       <c r="G75" s="25" t="n">
-        <v>44553</v>
+        <v>44537</v>
       </c>
       <c r="H75" s="25" t="n">
-        <v>48205</v>
+        <v>50039</v>
       </c>
       <c r="I75" t="n">
-        <v>5.65</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -19089,7 +19063,7 @@
         </is>
       </c>
       <c r="M75" s="25" t="n">
-        <v>48205</v>
+        <v>50039</v>
       </c>
       <c r="N75" t="n">
         <v>1</v>
@@ -19098,12 +19072,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GN46D</t>
+          <t>IRCOD</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Genneia SA</t>
+          <t>IRSA Inversiones y Representaciones SA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -19113,7 +19087,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Servicios Públicos y Generación</t>
+          <t>Bienes Raíces</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -19123,21 +19097,21 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AR0086415137</t>
+          <t>AR0084572384</t>
         </is>
       </c>
       <c r="G76" s="25" t="n">
-        <v>45470</v>
+        <v>45588</v>
       </c>
       <c r="H76" s="25" t="n">
-        <v>46200</v>
+        <v>47414</v>
       </c>
       <c r="I76" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="J76" t="n">
         <v>2</v>
       </c>
-      <c r="J76" t="n">
-        <v>4</v>
-      </c>
       <c r="K76" t="inlineStr">
         <is>
           <t>ACT/365</t>
@@ -19149,7 +19123,7 @@
         </is>
       </c>
       <c r="M76" s="25" t="n">
-        <v>46200</v>
+        <v>47414</v>
       </c>
       <c r="N76" t="n">
         <v>1</v>
@@ -19158,12 +19132,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GN38D</t>
+          <t>HJCHD</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Genneia SA</t>
+          <t>John Deere Credit</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -19173,7 +19147,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Servicios Públicos y Generación</t>
+          <t>Sector Financiero</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -19183,20 +19157,20 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>AREMGA5600Q9</t>
+          <t>AR0262204990</t>
         </is>
       </c>
       <c r="G77" s="25" t="n">
-        <v>44967</v>
+        <v>45674</v>
       </c>
       <c r="H77" s="25" t="n">
-        <v>48620</v>
+        <v>46769</v>
       </c>
       <c r="I77" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="J77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -19209,7 +19183,7 @@
         </is>
       </c>
       <c r="M77" s="25" t="n">
-        <v>48620</v>
+        <v>46769</v>
       </c>
       <c r="N77" t="n">
         <v>1</v>
@@ -19218,12 +19192,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DMC7D</t>
+          <t>HJCJD</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Impsa SA</t>
+          <t>John Deere Credit</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -19233,7 +19207,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Infraestructura y Transporte</t>
+          <t>Sector Financiero</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -19243,17 +19217,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ARIPSA5600A2</t>
+          <t>AR0924785071</t>
         </is>
       </c>
       <c r="G78" s="25" t="n">
-        <v>44537</v>
+        <v>45863</v>
       </c>
       <c r="H78" s="25" t="n">
-        <v>50039</v>
+        <v>46593</v>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="J78" t="n">
         <v>2</v>
@@ -19269,7 +19243,7 @@
         </is>
       </c>
       <c r="M78" s="25" t="n">
-        <v>50039</v>
+        <v>46593</v>
       </c>
       <c r="N78" t="n">
         <v>1</v>
@@ -19278,12 +19252,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>IRCOD</t>
+          <t>HJCID</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>IRSA Inversiones y Representaciones SA</t>
+          <t>John Deere Credit</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -19293,7 +19267,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Bienes Raíces</t>
+          <t>Sector Financiero</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -19303,17 +19277,17 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>AR0084572384</t>
+          <t>AR0861451372</t>
         </is>
       </c>
       <c r="G79" s="25" t="n">
-        <v>45588</v>
+        <v>45804</v>
       </c>
       <c r="H79" s="25" t="n">
-        <v>47414</v>
+        <v>46534</v>
       </c>
       <c r="I79" t="n">
-        <v>7.25</v>
+        <v>7.5</v>
       </c>
       <c r="J79" t="n">
         <v>2</v>
@@ -19329,7 +19303,7 @@
         </is>
       </c>
       <c r="M79" s="25" t="n">
-        <v>47414</v>
+        <v>46534</v>
       </c>
       <c r="N79" t="n">
         <v>1</v>
@@ -19338,7 +19312,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HJCHD</t>
+          <t>HJCKD</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -19363,17 +19337,17 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>AR0262204990</t>
+          <t>AR0021407595</t>
         </is>
       </c>
       <c r="G80" s="25" t="n">
-        <v>45674</v>
+        <v>46038</v>
       </c>
       <c r="H80" s="25" t="n">
-        <v>46769</v>
+        <v>47134</v>
       </c>
       <c r="I80" t="n">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="J80" t="n">
         <v>2</v>
@@ -19389,7 +19363,7 @@
         </is>
       </c>
       <c r="M80" s="25" t="n">
-        <v>46769</v>
+        <v>47134</v>
       </c>
       <c r="N80" t="n">
         <v>1</v>
@@ -19398,12 +19372,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HJCJD</t>
+          <t>LOC6D</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>John Deere Credit</t>
+          <t>Loma Negra</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -19413,7 +19387,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Sector Financiero</t>
+          <t>Bienes Raíces</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -19423,17 +19397,17 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AR0924785071</t>
+          <t>AR0204516451</t>
         </is>
       </c>
       <c r="G81" s="25" t="n">
-        <v>45863</v>
+        <v>46045</v>
       </c>
       <c r="H81" s="25" t="n">
-        <v>46593</v>
+        <v>47141</v>
       </c>
       <c r="I81" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="J81" t="n">
         <v>2</v>
@@ -19449,7 +19423,7 @@
         </is>
       </c>
       <c r="M81" s="25" t="n">
-        <v>46593</v>
+        <v>47141</v>
       </c>
       <c r="N81" t="n">
         <v>1</v>
@@ -19458,12 +19432,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>HJCID</t>
+          <t>LOC5D</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>John Deere Credit</t>
+          <t>Loma Negra</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -19473,7 +19447,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Sector Financiero</t>
+          <t>Bienes Raíces</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -19483,17 +19457,17 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AR0861451372</t>
+          <t>AR0579536985</t>
         </is>
       </c>
       <c r="G82" s="25" t="n">
-        <v>45804</v>
+        <v>45862</v>
       </c>
       <c r="H82" s="25" t="n">
-        <v>46534</v>
+        <v>46592</v>
       </c>
       <c r="I82" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J82" t="n">
         <v>2</v>
@@ -19509,7 +19483,7 @@
         </is>
       </c>
       <c r="M82" s="25" t="n">
-        <v>46534</v>
+        <v>46592</v>
       </c>
       <c r="N82" t="n">
         <v>1</v>
@@ -19518,12 +19492,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>HJCKD</t>
+          <t>LUC3D</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>John Deere Credit</t>
+          <t>Luz De Tres Picos SA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -19533,7 +19507,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Sector Financiero</t>
+          <t>Servicios Públicos y Generación</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -19543,20 +19517,20 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AR0021407595</t>
+          <t>ARLUZT560039</t>
         </is>
       </c>
       <c r="G83" s="25" t="n">
-        <v>46038</v>
+        <v>44686</v>
       </c>
       <c r="H83" s="25" t="n">
-        <v>47134</v>
+        <v>48339</v>
       </c>
       <c r="I83" t="n">
-        <v>7.75</v>
+        <v>5.05</v>
       </c>
       <c r="J83" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -19569,7 +19543,7 @@
         </is>
       </c>
       <c r="M83" s="25" t="n">
-        <v>47134</v>
+        <v>48339</v>
       </c>
       <c r="N83" t="n">
         <v>1</v>
@@ -19578,12 +19552,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>LOC6D</t>
+          <t>LUC4D</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Loma Negra</t>
+          <t>Luz De Tres Picos SA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -19593,7 +19567,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Bienes Raíces</t>
+          <t>Servicios Públicos y Generación</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -19603,20 +19577,17 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>AR0204516451</t>
+          <t>ARLUZT560047</t>
         </is>
       </c>
       <c r="G84" s="25" t="n">
-        <v>46045</v>
+        <v>44833</v>
       </c>
       <c r="H84" s="25" t="n">
-        <v>47141</v>
+        <v>46294</v>
       </c>
       <c r="I84" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -19629,7 +19600,7 @@
         </is>
       </c>
       <c r="M84" s="25" t="n">
-        <v>47141</v>
+        <v>46294</v>
       </c>
       <c r="N84" t="n">
         <v>1</v>
@@ -19638,12 +19609,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>LOC5D</t>
+          <t>XMC1D</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Loma Negra</t>
+          <t>Minera Exar SA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -19653,7 +19624,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Bienes Raíces</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -19663,14 +19634,14 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AR0579536985</t>
+          <t>AR0778941762</t>
         </is>
       </c>
       <c r="G85" s="25" t="n">
-        <v>45862</v>
+        <v>45607</v>
       </c>
       <c r="H85" s="25" t="n">
-        <v>46592</v>
+        <v>46702</v>
       </c>
       <c r="I85" t="n">
         <v>8</v>
@@ -19689,7 +19660,7 @@
         </is>
       </c>
       <c r="M85" s="25" t="n">
-        <v>46592</v>
+        <v>46702</v>
       </c>
       <c r="N85" t="n">
         <v>1</v>
@@ -19698,12 +19669,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LUC3D</t>
+          <t>RUCED</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Luz De Tres Picos SA</t>
+          <t>MSU Energy SA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -19723,17 +19694,17 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>ARLUZT560039</t>
+          <t>AR0207865277</t>
         </is>
       </c>
       <c r="G86" s="25" t="n">
-        <v>44686</v>
+        <v>46062</v>
       </c>
       <c r="H86" s="25" t="n">
-        <v>48339</v>
+        <v>46690</v>
       </c>
       <c r="I86" t="n">
-        <v>5.05</v>
+        <v>7.5</v>
       </c>
       <c r="J86" t="n">
         <v>4</v>
@@ -19749,7 +19720,7 @@
         </is>
       </c>
       <c r="M86" s="25" t="n">
-        <v>48339</v>
+        <v>46690</v>
       </c>
       <c r="N86" t="n">
         <v>1</v>
@@ -19758,12 +19729,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>LUC4D</t>
+          <t>EAC2D</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Luz De Tres Picos SA</t>
+          <t>MSU Green Energy SAU</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -19783,17 +19754,20 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ARLUZT560047</t>
+          <t>AR0047526246</t>
         </is>
       </c>
       <c r="G87" s="25" t="n">
-        <v>44833</v>
+        <v>45211</v>
       </c>
       <c r="H87" s="25" t="n">
-        <v>46294</v>
+        <v>48864</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>4.5</v>
+      </c>
+      <c r="J87" t="n">
+        <v>4</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -19806,7 +19780,7 @@
         </is>
       </c>
       <c r="M87" s="25" t="n">
-        <v>46294</v>
+        <v>48864</v>
       </c>
       <c r="N87" t="n">
         <v>1</v>
@@ -19815,12 +19789,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>XMC1D</t>
+          <t>MSSDD</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Minera Exar SA</t>
+          <t>MSU SA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -19830,7 +19804,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Consumo Masivo y Agro</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -19840,20 +19814,20 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AR0778941762</t>
+          <t>ARLEDE5600E6</t>
         </is>
       </c>
       <c r="G88" s="25" t="n">
-        <v>45607</v>
+        <v>44879</v>
       </c>
       <c r="H88" s="25" t="n">
-        <v>46702</v>
+        <v>48532</v>
       </c>
       <c r="I88" t="n">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="J88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -19866,7 +19840,7 @@
         </is>
       </c>
       <c r="M88" s="25" t="n">
-        <v>46702</v>
+        <v>48532</v>
       </c>
       <c r="N88" t="n">
         <v>1</v>
@@ -19875,12 +19849,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>RUCED</t>
+          <t>OTS5D</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MSU Energy SA</t>
+          <t>Oiltanking Ebytem SA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -19890,7 +19864,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Servicios Públicos y Generación</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -19900,20 +19874,20 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>AR0207865277</t>
+          <t>AR0034370418</t>
         </is>
       </c>
       <c r="G89" s="25" t="n">
-        <v>46062</v>
+        <v>45953</v>
       </c>
       <c r="H89" s="25" t="n">
-        <v>46690</v>
+        <v>46318</v>
       </c>
       <c r="I89" t="n">
-        <v>7.5</v>
+        <v>6.69</v>
       </c>
       <c r="J89" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -19926,21 +19900,24 @@
         </is>
       </c>
       <c r="M89" s="25" t="n">
-        <v>46690</v>
+        <v>46318</v>
       </c>
       <c r="N89" t="n">
         <v>1</v>
       </c>
+      <c r="O89" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EAC2D</t>
+          <t>OTS6D</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MSU Green Energy SAU</t>
+          <t>Oiltanking Ebytem SA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -19950,7 +19927,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Servicios Públicos y Generación</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -19960,20 +19937,20 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AR0047526246</t>
+          <t>AR0110435994</t>
         </is>
       </c>
       <c r="G90" s="25" t="n">
-        <v>45211</v>
+        <v>46051</v>
       </c>
       <c r="H90" s="25" t="n">
-        <v>48864</v>
+        <v>47328</v>
       </c>
       <c r="I90" t="n">
-        <v>4.5</v>
+        <v>6.74</v>
       </c>
       <c r="J90" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -19986,7 +19963,7 @@
         </is>
       </c>
       <c r="M90" s="25" t="n">
-        <v>48864</v>
+        <v>47328</v>
       </c>
       <c r="N90" t="n">
         <v>1</v>
@@ -19995,12 +19972,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MSSDD</t>
+          <t>OLC5D</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MSU SA</t>
+          <t>Oleoductos del Valle SA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -20010,7 +19987,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Consumo Masivo y Agro</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -20020,20 +19997,20 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ARLEDE5600E6</t>
+          <t>AR0467419146</t>
         </is>
       </c>
       <c r="G91" s="25" t="n">
-        <v>44879</v>
+        <v>45820</v>
       </c>
       <c r="H91" s="25" t="n">
-        <v>48532</v>
+        <v>46916</v>
       </c>
       <c r="I91" t="n">
-        <v>4.9</v>
+        <v>7.89</v>
       </c>
       <c r="J91" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -20046,7 +20023,7 @@
         </is>
       </c>
       <c r="M91" s="25" t="n">
-        <v>48532</v>
+        <v>46916</v>
       </c>
       <c r="N91" t="n">
         <v>1</v>
@@ -20055,12 +20032,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>OTS5D</t>
+          <t>OLC3D</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Oiltanking Ebytem SA</t>
+          <t>Oleoductos del Valle SA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -20080,20 +20057,17 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>AR0034370418</t>
+          <t>AROLDV560039</t>
         </is>
       </c>
       <c r="G92" s="25" t="n">
-        <v>45953</v>
+        <v>45117</v>
       </c>
       <c r="H92" s="25" t="n">
-        <v>46318</v>
+        <v>46578</v>
       </c>
       <c r="I92" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="J92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -20106,7 +20080,7 @@
         </is>
       </c>
       <c r="M92" s="25" t="n">
-        <v>46318</v>
+        <v>46578</v>
       </c>
       <c r="N92" t="n">
         <v>1</v>
@@ -20118,12 +20092,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>OTS6D</t>
+          <t>OLC7D</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Oiltanking Ebytem SA</t>
+          <t>Oleoductos del Valle SA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -20143,17 +20117,17 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>AR0110435994</t>
+          <t>AR0888142434</t>
         </is>
       </c>
       <c r="G93" s="25" t="n">
-        <v>46051</v>
+        <v>46076</v>
       </c>
       <c r="H93" s="25" t="n">
-        <v>47328</v>
+        <v>47537</v>
       </c>
       <c r="I93" t="n">
-        <v>6.74</v>
+        <v>6.9</v>
       </c>
       <c r="J93" t="n">
         <v>2</v>
@@ -20169,7 +20143,7 @@
         </is>
       </c>
       <c r="M93" s="25" t="n">
-        <v>47328</v>
+        <v>47537</v>
       </c>
       <c r="N93" t="n">
         <v>1</v>
@@ -20178,7 +20152,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>OLC4D</t>
+          <t>OLC6D</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -20203,20 +20177,20 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>AR0909041870</t>
+          <t>AR0828163235</t>
         </is>
       </c>
       <c r="G94" s="25" t="n">
-        <v>45457</v>
+        <v>45996</v>
       </c>
       <c r="H94" s="25" t="n">
-        <v>46187</v>
+        <v>47274</v>
       </c>
       <c r="I94" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="J94" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -20229,7 +20203,7 @@
         </is>
       </c>
       <c r="M94" s="25" t="n">
-        <v>46187</v>
+        <v>47274</v>
       </c>
       <c r="N94" t="n">
         <v>1</v>
@@ -20238,12 +20212,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>OLC5D</t>
+          <t>MGCND</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Oleoductos del Valle SA</t>
+          <t>Pampa Energia SA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -20253,7 +20227,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Servicios Públicos y Generación</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -20263,17 +20237,17 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>AR0467419146</t>
+          <t>AR0765746752</t>
         </is>
       </c>
       <c r="G95" s="25" t="n">
-        <v>45820</v>
+        <v>45569</v>
       </c>
       <c r="H95" s="25" t="n">
-        <v>46916</v>
+        <v>47030</v>
       </c>
       <c r="I95" t="n">
-        <v>7.89</v>
+        <v>5.75</v>
       </c>
       <c r="J95" t="n">
         <v>2</v>
@@ -20289,7 +20263,7 @@
         </is>
       </c>
       <c r="M95" s="25" t="n">
-        <v>46916</v>
+        <v>47030</v>
       </c>
       <c r="N95" t="n">
         <v>1</v>
@@ -20298,12 +20272,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>OLC3D</t>
+          <t>MGCED</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Oleoductos del Valle SA</t>
+          <t>Pampa Energia SA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -20313,7 +20287,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Servicios Públicos y Generación</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -20323,14 +20297,14 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>AROLDV560039</t>
+          <t>ARPAMP5600G7</t>
         </is>
       </c>
       <c r="G96" s="25" t="n">
-        <v>45117</v>
+        <v>44914</v>
       </c>
       <c r="H96" s="25" t="n">
-        <v>46578</v>
+        <v>46740</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
@@ -20346,24 +20320,27 @@
         </is>
       </c>
       <c r="M96" s="25" t="n">
-        <v>46578</v>
+        <v>46740</v>
       </c>
       <c r="N96" t="n">
         <v>1</v>
       </c>
       <c r="O96" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="P96" t="n">
+        <v>33.33</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>OLC7D</t>
+          <t>MGCQD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Oleoductos del Valle SA</t>
+          <t>Pampa Energia SA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -20373,7 +20350,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Servicios Públicos y Generación</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -20383,17 +20360,17 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>AR0888142434</t>
+          <t>AR0519406398</t>
         </is>
       </c>
       <c r="G97" s="25" t="n">
-        <v>46076</v>
+        <v>45875</v>
       </c>
       <c r="H97" s="25" t="n">
-        <v>47537</v>
+        <v>46971</v>
       </c>
       <c r="I97" t="n">
-        <v>6.9</v>
+        <v>7.25</v>
       </c>
       <c r="J97" t="n">
         <v>2</v>
@@ -20409,7 +20386,7 @@
         </is>
       </c>
       <c r="M97" s="25" t="n">
-        <v>47537</v>
+        <v>46971</v>
       </c>
       <c r="N97" t="n">
         <v>1</v>
@@ -20418,12 +20395,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>OLC6D</t>
+          <t>MGCTD</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Oleoductos del Valle SA</t>
+          <t>Pampa Energia SA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -20433,7 +20410,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Servicios Públicos y Generación</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -20443,17 +20420,17 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>AR0828163235</t>
+          <t>AR0145481872</t>
         </is>
       </c>
       <c r="G98" s="25" t="n">
-        <v>45996</v>
+        <v>46113</v>
       </c>
       <c r="H98" s="25" t="n">
-        <v>47274</v>
+        <v>47209</v>
       </c>
       <c r="I98" t="n">
-        <v>7.5</v>
+        <v>5.49</v>
       </c>
       <c r="J98" t="n">
         <v>2</v>
@@ -20469,7 +20446,7 @@
         </is>
       </c>
       <c r="M98" s="25" t="n">
-        <v>47274</v>
+        <v>47209</v>
       </c>
       <c r="N98" t="n">
         <v>1</v>
@@ -20478,12 +20455,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MGCND</t>
+          <t>PN38D</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Pampa Energia SA</t>
+          <t>Pan American Energy SL</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -20493,7 +20470,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Servicios Públicos y Generación</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -20503,17 +20480,17 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>AR0765746752</t>
+          <t>AR0554009248</t>
         </is>
       </c>
       <c r="G99" s="25" t="n">
-        <v>45569</v>
+        <v>45699</v>
       </c>
       <c r="H99" s="25" t="n">
-        <v>47030</v>
+        <v>46610</v>
       </c>
       <c r="I99" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="J99" t="n">
         <v>2</v>
@@ -20529,7 +20506,7 @@
         </is>
       </c>
       <c r="M99" s="25" t="n">
-        <v>47030</v>
+        <v>46610</v>
       </c>
       <c r="N99" t="n">
         <v>1</v>
@@ -20538,12 +20515,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MGCED</t>
+          <t>PNRCD</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Pampa Energia SA</t>
+          <t>Pan American Energy SL</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -20553,7 +20530,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Servicios Públicos y Generación</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -20563,17 +20540,20 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ARPAMP5600G7</t>
+          <t>ARAXIO5600X7</t>
         </is>
       </c>
       <c r="G100" s="25" t="n">
-        <v>44914</v>
+        <v>45145</v>
       </c>
       <c r="H100" s="25" t="n">
-        <v>46740</v>
+        <v>46972</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J100" t="n">
+        <v>4</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -20586,27 +20566,21 @@
         </is>
       </c>
       <c r="M100" s="25" t="n">
-        <v>46740</v>
+        <v>46972</v>
       </c>
       <c r="N100" t="n">
         <v>1</v>
       </c>
-      <c r="O100" t="n">
-        <v>1</v>
-      </c>
-      <c r="P100" t="n">
-        <v>33.33</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MGCQD</t>
+          <t>PN35D</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Pampa Energia SA</t>
+          <t>Pan American Energy SL</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -20616,7 +20590,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Servicios Públicos y Generación</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -20626,17 +20600,17 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>AR0519406398</t>
+          <t>AR0623274765</t>
         </is>
       </c>
       <c r="G101" s="25" t="n">
-        <v>45875</v>
+        <v>45562</v>
       </c>
       <c r="H101" s="25" t="n">
-        <v>46971</v>
+        <v>47388</v>
       </c>
       <c r="I101" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="J101" t="n">
         <v>2</v>
@@ -20652,7 +20626,7 @@
         </is>
       </c>
       <c r="M101" s="25" t="n">
-        <v>46971</v>
+        <v>47388</v>
       </c>
       <c r="N101" t="n">
         <v>1</v>
@@ -20661,12 +20635,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MGCTD</t>
+          <t>PN40D</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Pampa Energia SA</t>
+          <t>Pan American Energy SL</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -20676,7 +20650,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Servicios Públicos y Generación</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -20686,20 +20660,20 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>AR0145481872</t>
+          <t>AR0351070781</t>
         </is>
       </c>
       <c r="G102" s="25" t="n">
-        <v>46113</v>
+        <v>45758</v>
       </c>
       <c r="H102" s="25" t="n">
-        <v>47209</v>
+        <v>46306</v>
       </c>
       <c r="I102" t="n">
-        <v>5.49</v>
+        <v>2</v>
       </c>
       <c r="J102" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -20712,16 +20686,19 @@
         </is>
       </c>
       <c r="M102" s="25" t="n">
-        <v>47209</v>
+        <v>46306</v>
       </c>
       <c r="N102" t="n">
         <v>1</v>
       </c>
+      <c r="O102" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PN38D</t>
+          <t>PN42D</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -20746,17 +20723,17 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>AR0554009248</t>
+          <t>AR0081130814</t>
         </is>
       </c>
       <c r="G103" s="25" t="n">
-        <v>45699</v>
+        <v>45947</v>
       </c>
       <c r="H103" s="25" t="n">
-        <v>46610</v>
+        <v>46494</v>
       </c>
       <c r="I103" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="J103" t="n">
         <v>2</v>
@@ -20772,7 +20749,7 @@
         </is>
       </c>
       <c r="M103" s="25" t="n">
-        <v>46610</v>
+        <v>46494</v>
       </c>
       <c r="N103" t="n">
         <v>1</v>
@@ -20781,7 +20758,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PNRCD</t>
+          <t>PN37D</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -20806,20 +20783,20 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>ARAXIO5600X7</t>
+          <t>AR0098578880</t>
         </is>
       </c>
       <c r="G104" s="25" t="n">
-        <v>45145</v>
+        <v>45609</v>
       </c>
       <c r="H104" s="25" t="n">
-        <v>46972</v>
+        <v>47070</v>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>6.25</v>
       </c>
       <c r="J104" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -20832,7 +20809,7 @@
         </is>
       </c>
       <c r="M104" s="25" t="n">
-        <v>46972</v>
+        <v>47070</v>
       </c>
       <c r="N104" t="n">
         <v>1</v>
@@ -20841,7 +20818,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PN35D</t>
+          <t>PNZCD</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -20866,20 +20843,20 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>AR0623274765</t>
+          <t>AR0614200928</t>
         </is>
       </c>
       <c r="G105" s="25" t="n">
-        <v>45562</v>
+        <v>45477</v>
       </c>
       <c r="H105" s="25" t="n">
-        <v>47388</v>
+        <v>46572</v>
       </c>
       <c r="I105" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -20892,7 +20869,7 @@
         </is>
       </c>
       <c r="M105" s="25" t="n">
-        <v>47388</v>
+        <v>46572</v>
       </c>
       <c r="N105" t="n">
         <v>1</v>
@@ -20901,7 +20878,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PN40D</t>
+          <t>PN36D</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -20926,21 +20903,21 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>AR0351070781</t>
+          <t>AR0677571967</t>
         </is>
       </c>
       <c r="G106" s="25" t="n">
-        <v>45758</v>
+        <v>45609</v>
       </c>
       <c r="H106" s="25" t="n">
-        <v>46306</v>
+        <v>48165</v>
       </c>
       <c r="I106" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="J106" t="n">
         <v>2</v>
       </c>
-      <c r="J106" t="n">
-        <v>4</v>
-      </c>
       <c r="K106" t="inlineStr">
         <is>
           <t>ACT/365</t>
@@ -20952,19 +20929,16 @@
         </is>
       </c>
       <c r="M106" s="25" t="n">
-        <v>46306</v>
+        <v>48165</v>
       </c>
       <c r="N106" t="n">
         <v>1</v>
       </c>
-      <c r="O106" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PN42D</t>
+          <t>PN41D</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -20989,17 +20963,17 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>AR0081130814</t>
+          <t>AR0299198264</t>
         </is>
       </c>
       <c r="G107" s="25" t="n">
-        <v>45947</v>
+        <v>45896</v>
       </c>
       <c r="H107" s="25" t="n">
-        <v>46494</v>
+        <v>47357</v>
       </c>
       <c r="I107" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="J107" t="n">
         <v>2</v>
@@ -21015,7 +20989,7 @@
         </is>
       </c>
       <c r="M107" s="25" t="n">
-        <v>46494</v>
+        <v>47357</v>
       </c>
       <c r="N107" t="n">
         <v>1</v>
@@ -21024,12 +20998,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PN37D</t>
+          <t>PQCOD</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Pan American Energy SL</t>
+          <t>Petroquimica Comodoro Rivadavia SA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -21049,20 +21023,20 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>AR0098578880</t>
+          <t>ARPETQ5600N8</t>
         </is>
       </c>
       <c r="G108" s="25" t="n">
-        <v>45609</v>
+        <v>45191</v>
       </c>
       <c r="H108" s="25" t="n">
-        <v>47070</v>
+        <v>46652</v>
       </c>
       <c r="I108" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -21075,7 +21049,7 @@
         </is>
       </c>
       <c r="M108" s="25" t="n">
-        <v>47070</v>
+        <v>46652</v>
       </c>
       <c r="N108" t="n">
         <v>1</v>
@@ -21084,12 +21058,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>PNZCD</t>
+          <t>PQCSD</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Pan American Energy SL</t>
+          <t>Petroquimica Comodoro Rivadavia SA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -21109,20 +21083,20 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>AR0614200928</t>
+          <t>AR0309447628</t>
         </is>
       </c>
       <c r="G109" s="25" t="n">
-        <v>45477</v>
+        <v>45705</v>
       </c>
       <c r="H109" s="25" t="n">
-        <v>46572</v>
+        <v>47896</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J109" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -21135,7 +21109,7 @@
         </is>
       </c>
       <c r="M109" s="25" t="n">
-        <v>46572</v>
+        <v>47896</v>
       </c>
       <c r="N109" t="n">
         <v>1</v>
@@ -21144,12 +21118,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>PN36D</t>
+          <t>PQCKD</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Pan American Energy SL</t>
+          <t>Petroquimica Comodoro Rivadavia SA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -21169,47 +21143,53 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>AR0677571967</t>
+          <t>ARPETQ5600H0</t>
         </is>
       </c>
       <c r="G110" s="25" t="n">
-        <v>45609</v>
+        <v>44902</v>
       </c>
       <c r="H110" s="25" t="n">
-        <v>48165</v>
+        <v>46363</v>
       </c>
       <c r="I110" t="n">
-        <v>7.25</v>
+        <v>0.5</v>
       </c>
       <c r="J110" t="n">
+        <v>4</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>ACT/365</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>amortizing</t>
+        </is>
+      </c>
+      <c r="M110" s="25" t="n">
+        <v>45998</v>
+      </c>
+      <c r="N110" t="n">
         <v>2</v>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>ACT/365</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>bullet</t>
-        </is>
-      </c>
-      <c r="M110" s="25" t="n">
-        <v>48165</v>
-      </c>
-      <c r="N110" t="n">
+      <c r="O110" t="n">
         <v>1</v>
+      </c>
+      <c r="P110" t="n">
+        <v>33.33</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>PN41D</t>
+          <t>PLC1D</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Pan American Energy SL</t>
+          <t>Pluspetrol SA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -21229,17 +21209,17 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>AR0299198264</t>
+          <t>AR0502588418</t>
         </is>
       </c>
       <c r="G111" s="25" t="n">
-        <v>45896</v>
+        <v>45684</v>
       </c>
       <c r="H111" s="25" t="n">
-        <v>47357</v>
+        <v>46779</v>
       </c>
       <c r="I111" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="J111" t="n">
         <v>2</v>
@@ -21255,7 +21235,7 @@
         </is>
       </c>
       <c r="M111" s="25" t="n">
-        <v>47357</v>
+        <v>46779</v>
       </c>
       <c r="N111" t="n">
         <v>1</v>
@@ -21264,12 +21244,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PQCOD</t>
+          <t>PLC3D</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Petroquimica Comodoro Rivadavia SA</t>
+          <t>Pluspetrol SA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -21289,20 +21269,20 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>ARPETQ5600N8</t>
+          <t>AR0808016403</t>
         </is>
       </c>
       <c r="G112" s="25" t="n">
-        <v>45191</v>
+        <v>45777</v>
       </c>
       <c r="H112" s="25" t="n">
-        <v>46652</v>
+        <v>46873</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="J112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -21315,7 +21295,7 @@
         </is>
       </c>
       <c r="M112" s="25" t="n">
-        <v>46652</v>
+        <v>46873</v>
       </c>
       <c r="N112" t="n">
         <v>1</v>
@@ -21324,12 +21304,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PQCSD</t>
+          <t>PLC2D</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Petroquimica Comodoro Rivadavia SA</t>
+          <t>Pluspetrol SA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -21349,17 +21329,17 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>AR0309447628</t>
+          <t>AR0036431960</t>
         </is>
       </c>
       <c r="G113" s="25" t="n">
-        <v>45705</v>
+        <v>45684</v>
       </c>
       <c r="H113" s="25" t="n">
-        <v>47896</v>
+        <v>47510</v>
       </c>
       <c r="I113" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="J113" t="n">
         <v>2</v>
@@ -21375,7 +21355,7 @@
         </is>
       </c>
       <c r="M113" s="25" t="n">
-        <v>47896</v>
+        <v>47510</v>
       </c>
       <c r="N113" t="n">
         <v>1</v>
@@ -21384,12 +21364,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>PQCKD</t>
+          <t>PLC6D</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Petroquimica Comodoro Rivadavia SA</t>
+          <t>Pluspetrol SA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -21409,20 +21389,20 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>ARPETQ5600H0</t>
+          <t>AR0559091100</t>
         </is>
       </c>
       <c r="G114" s="25" t="n">
-        <v>44902</v>
+        <v>46080</v>
       </c>
       <c r="H114" s="25" t="n">
-        <v>46363</v>
+        <v>47176</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5</v>
+        <v>6.5</v>
       </c>
       <c r="J114" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -21431,31 +21411,25 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>amortizing</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="M114" s="25" t="n">
-        <v>45998</v>
+        <v>47176</v>
       </c>
       <c r="N114" t="n">
-        <v>2</v>
-      </c>
-      <c r="O114" t="n">
         <v>1</v>
-      </c>
-      <c r="P114" t="n">
-        <v>33.33</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>PLC1D</t>
+          <t>PFC2D</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Pluspetrol SA</t>
+          <t>Profertil SA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -21465,7 +21439,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Consumo Masivo y Agro</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -21475,17 +21449,17 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>AR0502588418</t>
+          <t>AR0416362439</t>
         </is>
       </c>
       <c r="G115" s="25" t="n">
-        <v>45684</v>
+        <v>45852</v>
       </c>
       <c r="H115" s="25" t="n">
-        <v>46779</v>
+        <v>46582</v>
       </c>
       <c r="I115" t="n">
-        <v>6</v>
+        <v>7.25</v>
       </c>
       <c r="J115" t="n">
         <v>2</v>
@@ -21501,7 +21475,7 @@
         </is>
       </c>
       <c r="M115" s="25" t="n">
-        <v>46779</v>
+        <v>46582</v>
       </c>
       <c r="N115" t="n">
         <v>1</v>
@@ -21510,12 +21484,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>PLC3D</t>
+          <t>SPC2D</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Pluspetrol SA</t>
+          <t>SCC Power San Pedro SA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -21525,7 +21499,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Servicios Públicos y Generación</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -21535,20 +21509,20 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>AR0808016403</t>
+          <t>ARSPIE560029</t>
         </is>
       </c>
       <c r="G116" s="25" t="n">
-        <v>45777</v>
+        <v>44739</v>
       </c>
       <c r="H116" s="25" t="n">
-        <v>46873</v>
+        <v>48392</v>
       </c>
       <c r="I116" t="n">
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
       <c r="J116" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -21557,25 +21531,31 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>amortizing</t>
         </is>
       </c>
       <c r="M116" s="25" t="n">
-        <v>46873</v>
+        <v>46292</v>
       </c>
       <c r="N116" t="n">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="O116" t="n">
+        <v>3</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>PLC2D</t>
+          <t>T662D</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Pluspetrol SA</t>
+          <t>Tarjeta Naranja SAU</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -21585,7 +21565,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Sector Financiero</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -21595,20 +21575,20 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>AR0036431960</t>
+          <t>AR0124318731</t>
         </is>
       </c>
       <c r="G117" s="25" t="n">
-        <v>45684</v>
+        <v>45987</v>
       </c>
       <c r="H117" s="25" t="n">
-        <v>47510</v>
+        <v>46265</v>
       </c>
       <c r="I117" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="J117" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -21621,7 +21601,7 @@
         </is>
       </c>
       <c r="M117" s="25" t="n">
-        <v>47510</v>
+        <v>46265</v>
       </c>
       <c r="N117" t="n">
         <v>1</v>
@@ -21630,12 +21610,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>PLC6D</t>
+          <t>TTC8D</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Pluspetrol SA</t>
+          <t>Tecpetrol SA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -21655,17 +21635,17 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>AR0559091100</t>
+          <t>AR0166027471</t>
         </is>
       </c>
       <c r="G118" s="25" t="n">
-        <v>46080</v>
+        <v>45589</v>
       </c>
       <c r="H118" s="25" t="n">
-        <v>47176</v>
+        <v>46684</v>
       </c>
       <c r="I118" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="J118" t="n">
         <v>2</v>
@@ -21681,7 +21661,7 @@
         </is>
       </c>
       <c r="M118" s="25" t="n">
-        <v>47176</v>
+        <v>46684</v>
       </c>
       <c r="N118" t="n">
         <v>1</v>
@@ -21690,12 +21670,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>PFC2D</t>
+          <t>TTC9D</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Profertil SA</t>
+          <t>Tecpetrol SA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -21705,7 +21685,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Consumo Masivo y Agro</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -21715,17 +21695,17 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>AR0416362439</t>
+          <t>AR0482976963</t>
         </is>
       </c>
       <c r="G119" s="25" t="n">
-        <v>45852</v>
+        <v>45589</v>
       </c>
       <c r="H119" s="25" t="n">
-        <v>46582</v>
+        <v>47415</v>
       </c>
       <c r="I119" t="n">
-        <v>7.25</v>
+        <v>6.8</v>
       </c>
       <c r="J119" t="n">
         <v>2</v>
@@ -21741,7 +21721,7 @@
         </is>
       </c>
       <c r="M119" s="25" t="n">
-        <v>46582</v>
+        <v>47415</v>
       </c>
       <c r="N119" t="n">
         <v>1</v>
@@ -21750,12 +21730,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SPC2D</t>
+          <t>TTCBD</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SCC Power San Pedro SA</t>
+          <t>Tecpetrol SA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -21765,7 +21745,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Servicios Públicos y Generación</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -21775,20 +21755,20 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>ARSPIE560029</t>
+          <t>AR0152326457</t>
         </is>
       </c>
       <c r="G120" s="25" t="n">
-        <v>44739</v>
+        <v>45946</v>
       </c>
       <c r="H120" s="25" t="n">
-        <v>48392</v>
+        <v>46676</v>
       </c>
       <c r="I120" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="J120" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -21797,31 +21777,28 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>amortizing</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="M120" s="25" t="n">
-        <v>46292</v>
+        <v>46676</v>
       </c>
       <c r="N120" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="O120" t="n">
-        <v>3</v>
-      </c>
-      <c r="P120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>T662D</t>
+          <t>TLCQD</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Tarjeta Naranja SAU</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -21831,7 +21808,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Sector Financiero</t>
+          <t>Telecomunicaciones</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -21841,17 +21818,17 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>AR0124318731</t>
+          <t>AR0006792755</t>
         </is>
       </c>
       <c r="G121" s="25" t="n">
-        <v>45987</v>
+        <v>45840</v>
       </c>
       <c r="H121" s="25" t="n">
-        <v>46265</v>
+        <v>46570</v>
       </c>
       <c r="I121" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="J121" t="n">
         <v>4</v>
@@ -21867,7 +21844,7 @@
         </is>
       </c>
       <c r="M121" s="25" t="n">
-        <v>46265</v>
+        <v>46570</v>
       </c>
       <c r="N121" t="n">
         <v>1</v>
@@ -21876,12 +21853,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>TTC8D</t>
+          <t>TLCFD</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Tecpetrol SA</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -21891,7 +21868,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Telecomunicaciones</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -21901,20 +21878,20 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>AR0166027471</t>
+          <t>ARTECO5600G5</t>
         </is>
       </c>
       <c r="G122" s="25" t="n">
-        <v>45589</v>
+        <v>44967</v>
       </c>
       <c r="H122" s="25" t="n">
-        <v>46684</v>
+        <v>46793</v>
       </c>
       <c r="I122" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -21927,7 +21904,7 @@
         </is>
       </c>
       <c r="M122" s="25" t="n">
-        <v>46684</v>
+        <v>46793</v>
       </c>
       <c r="N122" t="n">
         <v>1</v>
@@ -21936,12 +21913,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>TTC9D</t>
+          <t>TLCKD</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Tecpetrol SA</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -21951,7 +21928,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Telecomunicaciones</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -21961,20 +21938,20 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>AR0482976963</t>
+          <t>AR0849737462</t>
         </is>
       </c>
       <c r="G123" s="25" t="n">
-        <v>45589</v>
+        <v>45247</v>
       </c>
       <c r="H123" s="25" t="n">
-        <v>47415</v>
+        <v>46343</v>
       </c>
       <c r="I123" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -21987,21 +21964,27 @@
         </is>
       </c>
       <c r="M123" s="25" t="n">
-        <v>47415</v>
+        <v>46343</v>
       </c>
       <c r="N123" t="n">
         <v>1</v>
       </c>
+      <c r="O123" t="n">
+        <v>1</v>
+      </c>
+      <c r="P123" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>TTCBD</t>
+          <t>TLCOD</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Tecpetrol SA</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -22011,7 +21994,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Telecomunicaciones</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -22021,17 +22004,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>AR0152326457</t>
+          <t>AR0241562484</t>
         </is>
       </c>
       <c r="G124" s="25" t="n">
-        <v>45946</v>
+        <v>45624</v>
       </c>
       <c r="H124" s="25" t="n">
-        <v>46676</v>
+        <v>47085</v>
       </c>
       <c r="I124" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="J124" t="n">
         <v>2</v>
@@ -22047,19 +22030,16 @@
         </is>
       </c>
       <c r="M124" s="25" t="n">
-        <v>46676</v>
+        <v>47085</v>
       </c>
       <c r="N124" t="n">
         <v>1</v>
       </c>
-      <c r="O124" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>TLCQD</t>
+          <t>TLCUD</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -22084,20 +22064,20 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>AR0006792755</t>
+          <t>AR0857544677</t>
         </is>
       </c>
       <c r="G125" s="25" t="n">
-        <v>45840</v>
+        <v>46086</v>
       </c>
       <c r="H125" s="25" t="n">
-        <v>46570</v>
+        <v>47182</v>
       </c>
       <c r="I125" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="J125" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -22110,16 +22090,19 @@
         </is>
       </c>
       <c r="M125" s="25" t="n">
-        <v>46570</v>
+        <v>47182</v>
       </c>
       <c r="N125" t="n">
         <v>1</v>
       </c>
+      <c r="O125" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>TLCFD</t>
+          <t>TLCDD</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -22144,14 +22127,14 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>ARTECO5600G5</t>
+          <t>ARTECO5600E0</t>
         </is>
       </c>
       <c r="G126" s="25" t="n">
-        <v>44967</v>
+        <v>44629</v>
       </c>
       <c r="H126" s="25" t="n">
-        <v>46793</v>
+        <v>46455</v>
       </c>
       <c r="I126" t="n">
         <v>1</v>
@@ -22170,7 +22153,7 @@
         </is>
       </c>
       <c r="M126" s="25" t="n">
-        <v>46793</v>
+        <v>46455</v>
       </c>
       <c r="N126" t="n">
         <v>1</v>
@@ -22179,12 +22162,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>TLCKD</t>
+          <t>VSCQD</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Vista Energy</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -22194,7 +22177,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Telecomunicaciones</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -22204,17 +22187,17 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>AR0849737462</t>
+          <t>AR0941463967</t>
         </is>
       </c>
       <c r="G127" s="25" t="n">
-        <v>45247</v>
+        <v>45481</v>
       </c>
       <c r="H127" s="25" t="n">
-        <v>46343</v>
+        <v>46942</v>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J127" t="n">
         <v>4</v>
@@ -22230,27 +22213,21 @@
         </is>
       </c>
       <c r="M127" s="25" t="n">
-        <v>46343</v>
+        <v>46942</v>
       </c>
       <c r="N127" t="n">
         <v>1</v>
       </c>
-      <c r="O127" t="n">
-        <v>1</v>
-      </c>
-      <c r="P127" t="n">
-        <v>33</v>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>TLCOD</t>
+          <t>VSCMD</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Vista Energy</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -22260,7 +22237,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Telecomunicaciones</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -22270,20 +22247,20 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>AR0241562484</t>
+          <t>AROILG5600L4</t>
         </is>
       </c>
       <c r="G128" s="25" t="n">
-        <v>45624</v>
+        <v>45149</v>
       </c>
       <c r="H128" s="25" t="n">
-        <v>47085</v>
+        <v>46976</v>
       </c>
       <c r="I128" t="n">
-        <v>7</v>
+        <v>0.99</v>
       </c>
       <c r="J128" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -22296,7 +22273,7 @@
         </is>
       </c>
       <c r="M128" s="25" t="n">
-        <v>47085</v>
+        <v>46976</v>
       </c>
       <c r="N128" t="n">
         <v>1</v>
@@ -22305,12 +22282,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TLCUD</t>
+          <t>VSCWD</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Vista Energy</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -22320,7 +22297,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Telecomunicaciones</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -22330,20 +22307,20 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>AR0857544677</t>
+          <t>AR0652555118</t>
         </is>
       </c>
       <c r="G129" s="25" t="n">
-        <v>46086</v>
+        <v>45945</v>
       </c>
       <c r="H129" s="25" t="n">
-        <v>47182</v>
+        <v>46492</v>
       </c>
       <c r="I129" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="J129" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -22356,24 +22333,21 @@
         </is>
       </c>
       <c r="M129" s="25" t="n">
-        <v>47182</v>
+        <v>46492</v>
       </c>
       <c r="N129" t="n">
         <v>1</v>
       </c>
-      <c r="O129" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TLCDD</t>
+          <t>VSCOD</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Vista Energy</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -22383,7 +22357,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Telecomunicaciones</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -22393,20 +22367,20 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>ARTECO5600E0</t>
+          <t>AR0399155156</t>
         </is>
       </c>
       <c r="G130" s="25" t="n">
-        <v>44629</v>
+        <v>45357</v>
       </c>
       <c r="H130" s="25" t="n">
-        <v>46455</v>
+        <v>46452</v>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="J130" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -22419,7 +22393,7 @@
         </is>
       </c>
       <c r="M130" s="25" t="n">
-        <v>46455</v>
+        <v>46452</v>
       </c>
       <c r="N130" t="n">
         <v>1</v>
@@ -22428,7 +22402,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>VSCQD</t>
+          <t>VSCUD</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -22453,20 +22427,20 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>AR0941463967</t>
+          <t>AR0707929003</t>
         </is>
       </c>
       <c r="G131" s="25" t="n">
-        <v>45481</v>
+        <v>45723</v>
       </c>
       <c r="H131" s="25" t="n">
-        <v>46942</v>
+        <v>47549</v>
       </c>
       <c r="I131" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="J131" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -22479,7 +22453,7 @@
         </is>
       </c>
       <c r="M131" s="25" t="n">
-        <v>46942</v>
+        <v>47549</v>
       </c>
       <c r="N131" t="n">
         <v>1</v>
@@ -22488,7 +22462,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>VSCMD</t>
+          <t>VSCJD</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -22513,17 +22487,17 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>AROILG5600L4</t>
+          <t>AROILG5600I0</t>
         </is>
       </c>
       <c r="G132" s="25" t="n">
-        <v>45149</v>
+        <v>44988</v>
       </c>
       <c r="H132" s="25" t="n">
-        <v>46976</v>
+        <v>46449</v>
       </c>
       <c r="I132" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="J132" t="n">
         <v>4</v>
@@ -22539,7 +22513,7 @@
         </is>
       </c>
       <c r="M132" s="25" t="n">
-        <v>46976</v>
+        <v>46449</v>
       </c>
       <c r="N132" t="n">
         <v>1</v>
@@ -22548,7 +22522,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>VSCWD</t>
+          <t>VSCRD</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -22573,20 +22547,20 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>AR0652555118</t>
+          <t>AR0138120560</t>
         </is>
       </c>
       <c r="G133" s="25" t="n">
-        <v>45945</v>
+        <v>45575</v>
       </c>
       <c r="H133" s="25" t="n">
-        <v>46492</v>
+        <v>48131</v>
       </c>
       <c r="I133" t="n">
-        <v>6</v>
+        <v>7.65</v>
       </c>
       <c r="J133" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -22595,25 +22569,31 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>amortizing</t>
         </is>
       </c>
       <c r="M133" s="25" t="n">
-        <v>46492</v>
+        <v>47401</v>
       </c>
       <c r="N133" t="n">
+        <v>3</v>
+      </c>
+      <c r="O133" t="n">
         <v>1</v>
+      </c>
+      <c r="P133" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>VSCOD</t>
+          <t>YFCLD</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Vista Energy</t>
+          <t>YPF Energia Electrica SA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -22623,7 +22603,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Servicios Públicos y Generación</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -22633,24 +22613,24 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>AR0399155156</t>
+          <t>AR0338531962</t>
         </is>
       </c>
       <c r="G134" s="25" t="n">
-        <v>45357</v>
+        <v>45618</v>
       </c>
       <c r="H134" s="25" t="n">
-        <v>46452</v>
+        <v>47079</v>
       </c>
       <c r="I134" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="J134" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>ACT/365</t>
+          <t>30/360</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -22659,7 +22639,7 @@
         </is>
       </c>
       <c r="M134" s="25" t="n">
-        <v>46452</v>
+        <v>47079</v>
       </c>
       <c r="N134" t="n">
         <v>1</v>
@@ -22668,12 +22648,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>VSCUD</t>
+          <t>YFCMD</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Vista Energy</t>
+          <t>YPF Energia Electrica SA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -22683,7 +22663,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Servicios Públicos y Generación</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -22693,24 +22673,24 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>AR0707929003</t>
+          <t>AR0975634988</t>
         </is>
       </c>
       <c r="G135" s="25" t="n">
-        <v>45723</v>
+        <v>45797</v>
       </c>
       <c r="H135" s="25" t="n">
-        <v>47549</v>
+        <v>46527</v>
       </c>
       <c r="I135" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="J135" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>ACT/365</t>
+          <t>30/360</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -22719,7 +22699,7 @@
         </is>
       </c>
       <c r="M135" s="25" t="n">
-        <v>47549</v>
+        <v>46527</v>
       </c>
       <c r="N135" t="n">
         <v>1</v>
@@ -22728,12 +22708,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>VSCJD</t>
+          <t>YFCAD</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Vista Energy</t>
+          <t>YPF Energia Electrica SA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -22743,7 +22723,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Servicios Públicos y Generación</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -22753,47 +22733,53 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>AROILG5600I0</t>
+          <t>ARYPFE5600G5</t>
         </is>
       </c>
       <c r="G136" s="25" t="n">
-        <v>44988</v>
+        <v>44595</v>
       </c>
       <c r="H136" s="25" t="n">
-        <v>46449</v>
+        <v>48247</v>
       </c>
       <c r="I136" t="n">
+        <v>5</v>
+      </c>
+      <c r="J136" t="n">
+        <v>2</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>30/360</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>amortizing</t>
+        </is>
+      </c>
+      <c r="M136" s="25" t="n">
+        <v>46602</v>
+      </c>
+      <c r="N136" t="n">
+        <v>10</v>
+      </c>
+      <c r="O136" t="n">
+        <v>2</v>
+      </c>
+      <c r="P136" t="n">
         <v>0</v>
-      </c>
-      <c r="J136" t="n">
-        <v>4</v>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>ACT/365</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>bullet</t>
-        </is>
-      </c>
-      <c r="M136" s="25" t="n">
-        <v>46449</v>
-      </c>
-      <c r="N136" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>VSCRD</t>
+          <t>YFCND</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Vista Energy</t>
+          <t>YPF Energia Electrica SA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -22803,7 +22789,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Servicios Públicos y Generación</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -22813,53 +22799,47 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>AR0138120560</t>
+          <t>AR0361875989</t>
         </is>
       </c>
       <c r="G137" s="25" t="n">
-        <v>45575</v>
+        <v>45933</v>
       </c>
       <c r="H137" s="25" t="n">
-        <v>48131</v>
+        <v>46298</v>
       </c>
       <c r="I137" t="n">
-        <v>7.65</v>
+        <v>6</v>
       </c>
       <c r="J137" t="n">
         <v>2</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>ACT/365</t>
+          <t>30/360</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>amortizing</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="M137" s="25" t="n">
-        <v>47401</v>
+        <v>46298</v>
       </c>
       <c r="N137" t="n">
-        <v>3</v>
-      </c>
-      <c r="O137" t="n">
         <v>1</v>
-      </c>
-      <c r="P137" t="n">
-        <v>33</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>YFCLD</t>
+          <t>YM40D</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>YPF Energia Electrica SA</t>
+          <t>YPF SA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -22869,7 +22849,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Servicios Públicos y Generación</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -22879,24 +22859,24 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>AR0338531962</t>
+          <t>AR0963751125</t>
         </is>
       </c>
       <c r="G138" s="25" t="n">
-        <v>45618</v>
+        <v>45897</v>
       </c>
       <c r="H138" s="25" t="n">
-        <v>47079</v>
+        <v>46993</v>
       </c>
       <c r="I138" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="J138" t="n">
         <v>4</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>30/360</t>
+          <t>ACT/365</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -22905,7 +22885,7 @@
         </is>
       </c>
       <c r="M138" s="25" t="n">
-        <v>47079</v>
+        <v>46993</v>
       </c>
       <c r="N138" t="n">
         <v>1</v>
@@ -22914,12 +22894,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>YFCMD</t>
+          <t>YM41D</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>YPF Energia Electrica SA</t>
+          <t>YPF SA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -22929,7 +22909,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Servicios Públicos y Generación</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -22939,24 +22919,24 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>AR0975634988</t>
+          <t>AR0675705039</t>
         </is>
       </c>
       <c r="G139" s="25" t="n">
-        <v>45797</v>
+        <v>45938</v>
       </c>
       <c r="H139" s="25" t="n">
-        <v>46527</v>
+        <v>46395</v>
       </c>
       <c r="I139" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="J139" t="n">
         <v>4</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>30/360</t>
+          <t>ACT/365</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -22965,7 +22945,7 @@
         </is>
       </c>
       <c r="M139" s="25" t="n">
-        <v>46527</v>
+        <v>46395</v>
       </c>
       <c r="N139" t="n">
         <v>1</v>
@@ -22974,12 +22954,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>YFCAD</t>
+          <t>YMCYD</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>YPF Energia Electrica SA</t>
+          <t>YPF SA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -22989,7 +22969,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Servicios Públicos y Generación</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -22999,53 +22979,47 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>ARYPFE5600G5</t>
+          <t>AR0417757066</t>
         </is>
       </c>
       <c r="G140" s="25" t="n">
-        <v>44595</v>
+        <v>45575</v>
       </c>
       <c r="H140" s="25" t="n">
-        <v>48247</v>
+        <v>47036</v>
       </c>
       <c r="I140" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="J140" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>30/360</t>
+          <t>ACT/365</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>amortizing</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="M140" s="25" t="n">
-        <v>46602</v>
+        <v>47036</v>
       </c>
       <c r="N140" t="n">
-        <v>10</v>
-      </c>
-      <c r="O140" t="n">
-        <v>2</v>
-      </c>
-      <c r="P140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>YFCND</t>
+          <t>YMCTD</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>YPF Energia Electrica SA</t>
+          <t>YPF SA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -23055,7 +23029,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Servicios Públicos y Generación</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -23065,24 +23039,21 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>AR0361875989</t>
+          <t>AR0688075032</t>
         </is>
       </c>
       <c r="G141" s="25" t="n">
-        <v>45933</v>
+        <v>45209</v>
       </c>
       <c r="H141" s="25" t="n">
-        <v>46298</v>
+        <v>46305</v>
       </c>
       <c r="I141" t="n">
-        <v>6</v>
-      </c>
-      <c r="J141" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>30/360</t>
+          <t>ACT/365</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -23091,16 +23062,22 @@
         </is>
       </c>
       <c r="M141" s="25" t="n">
-        <v>46298</v>
+        <v>46305</v>
       </c>
       <c r="N141" t="n">
         <v>1</v>
       </c>
+      <c r="O141" t="n">
+        <v>1</v>
+      </c>
+      <c r="P141" t="n">
+        <v>17.5</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>YM40D</t>
+          <t>YM37D</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -23125,17 +23102,17 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>AR0963751125</t>
+          <t>AR0657794191</t>
         </is>
       </c>
       <c r="G142" s="25" t="n">
-        <v>45897</v>
+        <v>45784</v>
       </c>
       <c r="H142" s="25" t="n">
-        <v>46993</v>
+        <v>46514</v>
       </c>
       <c r="I142" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="J142" t="n">
         <v>4</v>
@@ -23151,7 +23128,7 @@
         </is>
       </c>
       <c r="M142" s="25" t="n">
-        <v>46993</v>
+        <v>46514</v>
       </c>
       <c r="N142" t="n">
         <v>1</v>
@@ -23160,7 +23137,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>YM41D</t>
+          <t>YM35D</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -23185,17 +23162,17 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>AR0675705039</t>
+          <t>AR0929824099</t>
         </is>
       </c>
       <c r="G143" s="25" t="n">
-        <v>45938</v>
+        <v>45715</v>
       </c>
       <c r="H143" s="25" t="n">
-        <v>46395</v>
+        <v>46445</v>
       </c>
       <c r="I143" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="J143" t="n">
         <v>4</v>
@@ -23211,7 +23188,7 @@
         </is>
       </c>
       <c r="M143" s="25" t="n">
-        <v>46395</v>
+        <v>46445</v>
       </c>
       <c r="N143" t="n">
         <v>1</v>
@@ -23220,7 +23197,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>YMCYD</t>
+          <t>YM39D</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -23245,20 +23222,20 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>AR0417757066</t>
+          <t>AR0081455617</t>
         </is>
       </c>
       <c r="G144" s="25" t="n">
-        <v>45575</v>
+        <v>45860</v>
       </c>
       <c r="H144" s="25" t="n">
-        <v>47036</v>
+        <v>47686</v>
       </c>
       <c r="I144" t="n">
-        <v>6.5</v>
+        <v>8.75</v>
       </c>
       <c r="J144" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -23271,7 +23248,7 @@
         </is>
       </c>
       <c r="M144" s="25" t="n">
-        <v>47036</v>
+        <v>47686</v>
       </c>
       <c r="N144" t="n">
         <v>1</v>
@@ -23280,7 +23257,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>YMCTD</t>
+          <t>YM38D</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -23305,17 +23282,20 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>AR0688075032</t>
+          <t>AR0419238511</t>
         </is>
       </c>
       <c r="G145" s="25" t="n">
-        <v>45209</v>
+        <v>45860</v>
       </c>
       <c r="H145" s="25" t="n">
-        <v>46305</v>
+        <v>46590</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>7.5</v>
+      </c>
+      <c r="J145" t="n">
+        <v>4</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
@@ -23328,22 +23308,16 @@
         </is>
       </c>
       <c r="M145" s="25" t="n">
-        <v>46305</v>
+        <v>46590</v>
       </c>
       <c r="N145" t="n">
         <v>1</v>
       </c>
-      <c r="O145" t="n">
-        <v>1</v>
-      </c>
-      <c r="P145" t="n">
-        <v>17.5</v>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>YM37D</t>
+          <t>YM42D</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -23368,20 +23342,20 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>AR0657794191</t>
+          <t>AR0123407162</t>
         </is>
       </c>
       <c r="G146" s="25" t="n">
-        <v>45784</v>
+        <v>45993</v>
       </c>
       <c r="H146" s="25" t="n">
-        <v>46514</v>
+        <v>47179</v>
       </c>
       <c r="I146" t="n">
         <v>7</v>
       </c>
       <c r="J146" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -23394,7 +23368,7 @@
         </is>
       </c>
       <c r="M146" s="25" t="n">
-        <v>46514</v>
+        <v>47179</v>
       </c>
       <c r="N146" t="n">
         <v>1</v>
@@ -23403,7 +23377,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>YM35D</t>
+          <t>YMCWD</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -23428,17 +23402,17 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>AR0929824099</t>
+          <t>AR0132676112</t>
         </is>
       </c>
       <c r="G147" s="25" t="n">
-        <v>45715</v>
+        <v>45474</v>
       </c>
       <c r="H147" s="25" t="n">
-        <v>46445</v>
+        <v>46204</v>
       </c>
       <c r="I147" t="n">
-        <v>6.25</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
         <v>4</v>
@@ -23454,16 +23428,19 @@
         </is>
       </c>
       <c r="M147" s="25" t="n">
-        <v>46445</v>
+        <v>46204</v>
       </c>
       <c r="N147" t="n">
         <v>1</v>
       </c>
+      <c r="O147" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>YM39D</t>
+          <t>YMCRD</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -23488,20 +23465,20 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>AR0081455617</t>
+          <t>ARYPFS5601X8</t>
         </is>
       </c>
       <c r="G148" s="25" t="n">
-        <v>45860</v>
+        <v>45181</v>
       </c>
       <c r="H148" s="25" t="n">
-        <v>47686</v>
+        <v>47008</v>
       </c>
       <c r="I148" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="J148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -23514,21 +23491,24 @@
         </is>
       </c>
       <c r="M148" s="25" t="n">
-        <v>47686</v>
+        <v>47008</v>
       </c>
       <c r="N148" t="n">
         <v>1</v>
       </c>
+      <c r="O148" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>YM38D</t>
+          <t>IRCFD</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>YPF SA</t>
+          <t>IRSA S.A</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -23538,57 +23518,63 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t xml:space="preserve">Construcción </t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>AR0419238511</t>
+          <t>USP58809BH95</t>
         </is>
       </c>
       <c r="G149" s="25" t="n">
-        <v>45860</v>
+        <v>44750</v>
       </c>
       <c r="H149" s="25" t="n">
-        <v>46590</v>
+        <v>46926</v>
       </c>
       <c r="I149" t="n">
-        <v>7.5</v>
+        <v>8.75</v>
       </c>
       <c r="J149" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>ACT/365</t>
+          <t>30/360</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>amortizing</t>
         </is>
       </c>
       <c r="M149" s="25" t="n">
-        <v>46590</v>
+        <v>45465</v>
       </c>
       <c r="N149" t="n">
+        <v>5</v>
+      </c>
+      <c r="O149" t="n">
         <v>1</v>
+      </c>
+      <c r="P149" t="n">
+        <v>17.5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>YM42D</t>
+          <t>TLCPD</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>YPF SA</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -23598,7 +23584,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Telecomunicaciones</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -23608,47 +23594,53 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>AR0123407162</t>
+          <t>USP9028NCA74</t>
         </is>
       </c>
       <c r="G150" s="25" t="n">
-        <v>45993</v>
+        <v>45805</v>
       </c>
       <c r="H150" s="25" t="n">
-        <v>47179</v>
+        <v>48727</v>
       </c>
       <c r="I150" t="n">
-        <v>7</v>
+        <v>9.25</v>
       </c>
       <c r="J150" t="n">
         <v>2</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>ACT/365</t>
+          <t>30/360</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>amortizing</t>
         </is>
       </c>
       <c r="M150" s="25" t="n">
-        <v>47179</v>
+        <v>48362</v>
       </c>
       <c r="N150" t="n">
+        <v>2</v>
+      </c>
+      <c r="O150" t="n">
         <v>1</v>
+      </c>
+      <c r="P150" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>YMCWD</t>
+          <t>TLCTD</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>YPF SA</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -23658,60 +23650,63 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Telecomunicaciones</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>AR0132676112</t>
+          <t>USP9028NCE96</t>
         </is>
       </c>
       <c r="G151" s="25" t="n">
-        <v>45474</v>
+        <v>46042</v>
       </c>
       <c r="H151" s="25" t="n">
-        <v>46204</v>
+        <v>49694</v>
       </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="J151" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>ACT/365</t>
+          <t>30/360</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>bullet</t>
+          <t>amortizing</t>
         </is>
       </c>
       <c r="M151" s="25" t="n">
-        <v>46204</v>
+        <v>49329</v>
       </c>
       <c r="N151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O151" t="n">
         <v>1</v>
       </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>YMCRD</t>
+          <t>YFCID</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>YPF SA</t>
+          <t>YPF Energia Electrica SA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -23721,7 +23716,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Servicios Públicos y Generación</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -23731,50 +23726,53 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>ARYPFS5601X8</t>
+          <t>AR0947502206</t>
         </is>
       </c>
       <c r="G152" s="25" t="n">
-        <v>45181</v>
+        <v>45456</v>
       </c>
       <c r="H152" s="25" t="n">
-        <v>47008</v>
+        <v>46551</v>
       </c>
       <c r="I152" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J152" t="n">
+        <v>4</v>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>30/360</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>amortizing</t>
+        </is>
+      </c>
+      <c r="M152" s="25" t="n">
+        <v>46520</v>
+      </c>
+      <c r="N152" t="n">
+        <v>2</v>
+      </c>
+      <c r="O152" t="n">
+        <v>2</v>
+      </c>
+      <c r="P152" t="n">
         <v>0</v>
-      </c>
-      <c r="J152" t="n">
-        <v>1</v>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>ACT/365</t>
-        </is>
-      </c>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>bullet</t>
-        </is>
-      </c>
-      <c r="M152" s="25" t="n">
-        <v>47008</v>
-      </c>
-      <c r="N152" t="n">
-        <v>1</v>
-      </c>
-      <c r="O152" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>IRCFD</t>
+          <t>YM43D</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>IRSA S.A</t>
+          <t>YPF SA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -23784,316 +23782,164 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construcción </t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>USP58809BH95</t>
+          <t>AR0156884063</t>
         </is>
       </c>
       <c r="G153" s="25" t="n">
-        <v>44750</v>
+        <v>46126</v>
       </c>
       <c r="H153" s="25" t="n">
-        <v>46926</v>
+        <v>47587</v>
       </c>
       <c r="I153" t="n">
-        <v>8.75</v>
+        <v>5.5</v>
       </c>
       <c r="J153" t="n">
         <v>2</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>30/360</t>
+          <t>ACT/365</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>amortizing</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="M153" s="25" t="n">
-        <v>45465</v>
+        <v>47588</v>
       </c>
       <c r="N153" t="n">
-        <v>5</v>
-      </c>
-      <c r="O153" t="n">
         <v>1</v>
       </c>
-      <c r="P153" t="n">
-        <v>17.5</v>
-      </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>TLCPD</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Telecom</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
+      <c r="A154" s="24" t="inlineStr">
+        <is>
+          <t>AERBD</t>
+        </is>
+      </c>
+      <c r="B154" s="24" t="n"/>
+      <c r="C154" s="24" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Telecomunicaciones</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>USP9028NCA74</t>
-        </is>
-      </c>
-      <c r="G154" s="25" t="n">
-        <v>45805</v>
-      </c>
-      <c r="H154" s="25" t="n">
-        <v>48727</v>
-      </c>
-      <c r="I154" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="J154" t="n">
-        <v>2</v>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>30/360</t>
-        </is>
-      </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>amortizing</t>
-        </is>
-      </c>
-      <c r="M154" s="25" t="n">
-        <v>48362</v>
-      </c>
-      <c r="N154" t="n">
-        <v>2</v>
-      </c>
-      <c r="O154" t="n">
-        <v>1</v>
-      </c>
-      <c r="P154" t="n">
-        <v>0</v>
-      </c>
+      <c r="D154" s="24" t="n"/>
+      <c r="E154" s="24" t="n"/>
+      <c r="F154" s="24" t="n"/>
+      <c r="G154" s="24" t="n"/>
+      <c r="H154" s="24" t="n"/>
+      <c r="I154" s="24" t="n"/>
+      <c r="J154" s="24" t="n"/>
+      <c r="K154" s="24" t="n"/>
+      <c r="L154" s="24" t="n"/>
+      <c r="M154" s="24" t="n"/>
+      <c r="N154" s="24" t="n"/>
+      <c r="O154" s="24" t="n"/>
+      <c r="P154" s="24" t="n"/>
+      <c r="Q154" s="24" t="n"/>
+      <c r="R154" s="24" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>TLCTD</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Telecom</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
+      <c r="A155" s="24" t="inlineStr">
+        <is>
+          <t>AFCHD</t>
+        </is>
+      </c>
+      <c r="B155" s="24" t="n"/>
+      <c r="C155" s="24" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Telecomunicaciones</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>USP9028NCE96</t>
-        </is>
-      </c>
-      <c r="G155" s="25" t="n">
-        <v>46042</v>
-      </c>
-      <c r="H155" s="25" t="n">
-        <v>49694</v>
-      </c>
-      <c r="I155" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J155" t="n">
-        <v>2</v>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>30/360</t>
-        </is>
-      </c>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>amortizing</t>
-        </is>
-      </c>
-      <c r="M155" s="25" t="n">
-        <v>49329</v>
-      </c>
-      <c r="N155" t="n">
-        <v>2</v>
-      </c>
-      <c r="O155" t="n">
-        <v>1</v>
-      </c>
-      <c r="P155" t="n">
-        <v>0</v>
-      </c>
+      <c r="D155" s="24" t="n"/>
+      <c r="E155" s="24" t="n"/>
+      <c r="F155" s="24" t="n"/>
+      <c r="G155" s="24" t="n"/>
+      <c r="H155" s="24" t="n"/>
+      <c r="I155" s="24" t="n"/>
+      <c r="J155" s="24" t="n"/>
+      <c r="K155" s="24" t="n"/>
+      <c r="L155" s="24" t="n"/>
+      <c r="M155" s="24" t="n"/>
+      <c r="N155" s="24" t="n"/>
+      <c r="O155" s="24" t="n"/>
+      <c r="P155" s="24" t="n"/>
+      <c r="Q155" s="24" t="n"/>
+      <c r="R155" s="24" t="n"/>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>YFCID</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>YPF Energia Electrica SA</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
+      <c r="A156" s="24" t="inlineStr">
+        <is>
+          <t>AFCID</t>
+        </is>
+      </c>
+      <c r="B156" s="24" t="n"/>
+      <c r="C156" s="24" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Servicios Públicos y Generación</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>AR0947502206</t>
-        </is>
-      </c>
-      <c r="G156" s="25" t="n">
-        <v>45456</v>
-      </c>
-      <c r="H156" s="25" t="n">
-        <v>46551</v>
-      </c>
-      <c r="I156" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J156" t="n">
-        <v>4</v>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>30/360</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>amortizing</t>
-        </is>
-      </c>
-      <c r="M156" s="25" t="n">
-        <v>46520</v>
-      </c>
-      <c r="N156" t="n">
-        <v>2</v>
-      </c>
-      <c r="O156" t="n">
-        <v>2</v>
-      </c>
-      <c r="P156" t="n">
-        <v>0</v>
-      </c>
+      <c r="D156" s="24" t="n"/>
+      <c r="E156" s="24" t="n"/>
+      <c r="F156" s="24" t="n"/>
+      <c r="G156" s="24" t="n"/>
+      <c r="H156" s="24" t="n"/>
+      <c r="I156" s="24" t="n"/>
+      <c r="J156" s="24" t="n"/>
+      <c r="K156" s="24" t="n"/>
+      <c r="L156" s="24" t="n"/>
+      <c r="M156" s="24" t="n"/>
+      <c r="N156" s="24" t="n"/>
+      <c r="O156" s="24" t="n"/>
+      <c r="P156" s="24" t="n"/>
+      <c r="Q156" s="24" t="n"/>
+      <c r="R156" s="24" t="n"/>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>YM43D</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>YPF SA</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
+      <c r="A157" s="24" t="inlineStr">
+        <is>
+          <t>AFCJD</t>
+        </is>
+      </c>
+      <c r="B157" s="24" t="n"/>
+      <c r="C157" s="24" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Petróleo y Gas</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>AR0156884063</t>
-        </is>
-      </c>
-      <c r="G157" s="25" t="n">
-        <v>46126</v>
-      </c>
-      <c r="H157" s="25" t="n">
-        <v>47587</v>
-      </c>
-      <c r="I157" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J157" t="n">
-        <v>2</v>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>ACT/365</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>bullet</t>
-        </is>
-      </c>
-      <c r="M157" s="25" t="n">
-        <v>47588</v>
-      </c>
-      <c r="N157" t="n">
-        <v>1</v>
-      </c>
+      <c r="D157" s="24" t="n"/>
+      <c r="E157" s="24" t="n"/>
+      <c r="F157" s="24" t="n"/>
+      <c r="G157" s="24" t="n"/>
+      <c r="H157" s="24" t="n"/>
+      <c r="I157" s="24" t="n"/>
+      <c r="J157" s="24" t="n"/>
+      <c r="K157" s="24" t="n"/>
+      <c r="L157" s="24" t="n"/>
+      <c r="M157" s="24" t="n"/>
+      <c r="N157" s="24" t="n"/>
+      <c r="O157" s="24" t="n"/>
+      <c r="P157" s="24" t="n"/>
+      <c r="Q157" s="24" t="n"/>
+      <c r="R157" s="24" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="24" t="inlineStr">
         <is>
-          <t>AERBD</t>
+          <t>AFCKD</t>
         </is>
       </c>
       <c r="B158" s="24" t="n"/>
@@ -24121,7 +23967,7 @@
     <row r="159">
       <c r="A159" s="24" t="inlineStr">
         <is>
-          <t>AFCHD</t>
+          <t>BACHD</t>
         </is>
       </c>
       <c r="B159" s="24" t="n"/>
@@ -24149,7 +23995,7 @@
     <row r="160">
       <c r="A160" s="24" t="inlineStr">
         <is>
-          <t>AFCID</t>
+          <t>BF37D</t>
         </is>
       </c>
       <c r="B160" s="24" t="n"/>
@@ -24177,7 +24023,7 @@
     <row r="161">
       <c r="A161" s="24" t="inlineStr">
         <is>
-          <t>AFCJD</t>
+          <t>BF40D</t>
         </is>
       </c>
       <c r="B161" s="24" t="n"/>
@@ -24205,7 +24051,7 @@
     <row r="162">
       <c r="A162" s="24" t="inlineStr">
         <is>
-          <t>AFCKD</t>
+          <t>BF45D</t>
         </is>
       </c>
       <c r="B162" s="24" t="n"/>
@@ -24233,7 +24079,7 @@
     <row r="163">
       <c r="A163" s="24" t="inlineStr">
         <is>
-          <t>BACHD</t>
+          <t>BGC4D</t>
         </is>
       </c>
       <c r="B163" s="24" t="n"/>
@@ -24261,7 +24107,7 @@
     <row r="164">
       <c r="A164" s="24" t="inlineStr">
         <is>
-          <t>BF37D</t>
+          <t>BPCSD</t>
         </is>
       </c>
       <c r="B164" s="24" t="n"/>
@@ -24289,7 +24135,7 @@
     <row r="165">
       <c r="A165" s="24" t="inlineStr">
         <is>
-          <t>BF40D</t>
+          <t>BPCUD</t>
         </is>
       </c>
       <c r="B165" s="24" t="n"/>
@@ -24317,7 +24163,7 @@
     <row r="166">
       <c r="A166" s="24" t="inlineStr">
         <is>
-          <t>BF45D</t>
+          <t>BPCVD</t>
         </is>
       </c>
       <c r="B166" s="24" t="n"/>
@@ -24345,7 +24191,7 @@
     <row r="167">
       <c r="A167" s="24" t="inlineStr">
         <is>
-          <t>BGC4D</t>
+          <t>BVCPD</t>
         </is>
       </c>
       <c r="B167" s="24" t="n"/>
@@ -24373,7 +24219,7 @@
     <row r="168">
       <c r="A168" s="24" t="inlineStr">
         <is>
-          <t>BPCSD</t>
+          <t>CACBD</t>
         </is>
       </c>
       <c r="B168" s="24" t="n"/>
@@ -24401,7 +24247,7 @@
     <row r="169">
       <c r="A169" s="24" t="inlineStr">
         <is>
-          <t>BPCUD</t>
+          <t>CIC7D</t>
         </is>
       </c>
       <c r="B169" s="24" t="n"/>
@@ -24429,7 +24275,7 @@
     <row r="170">
       <c r="A170" s="24" t="inlineStr">
         <is>
-          <t>BPCVD</t>
+          <t>CIC8D</t>
         </is>
       </c>
       <c r="B170" s="24" t="n"/>
@@ -24457,7 +24303,7 @@
     <row r="171">
       <c r="A171" s="24" t="inlineStr">
         <is>
-          <t>BVCPD</t>
+          <t>CIC9D</t>
         </is>
       </c>
       <c r="B171" s="24" t="n"/>
@@ -24485,7 +24331,7 @@
     <row r="172">
       <c r="A172" s="24" t="inlineStr">
         <is>
-          <t>CACBD</t>
+          <t>CICBD</t>
         </is>
       </c>
       <c r="B172" s="24" t="n"/>
@@ -24513,7 +24359,7 @@
     <row r="173">
       <c r="A173" s="24" t="inlineStr">
         <is>
-          <t>CIC7D</t>
+          <t>CLI1D</t>
         </is>
       </c>
       <c r="B173" s="24" t="n"/>
@@ -24541,7 +24387,7 @@
     <row r="174">
       <c r="A174" s="24" t="inlineStr">
         <is>
-          <t>CIC8D</t>
+          <t>CLSID</t>
         </is>
       </c>
       <c r="B174" s="24" t="n"/>
@@ -24569,7 +24415,7 @@
     <row r="175">
       <c r="A175" s="24" t="inlineStr">
         <is>
-          <t>CIC9D</t>
+          <t>CP37D</t>
         </is>
       </c>
       <c r="B175" s="24" t="n"/>
@@ -24597,7 +24443,7 @@
     <row r="176">
       <c r="A176" s="24" t="inlineStr">
         <is>
-          <t>CICBD</t>
+          <t>CP38D</t>
         </is>
       </c>
       <c r="B176" s="24" t="n"/>
@@ -24625,7 +24471,7 @@
     <row r="177">
       <c r="A177" s="24" t="inlineStr">
         <is>
-          <t>CLI1D</t>
+          <t>CS45D</t>
         </is>
       </c>
       <c r="B177" s="24" t="n"/>
@@ -24653,7 +24499,7 @@
     <row r="178">
       <c r="A178" s="24" t="inlineStr">
         <is>
-          <t>CLSID</t>
+          <t>CS51D</t>
         </is>
       </c>
       <c r="B178" s="24" t="n"/>
@@ -24681,7 +24527,7 @@
     <row r="179">
       <c r="A179" s="24" t="inlineStr">
         <is>
-          <t>CP37D</t>
+          <t>CS52D</t>
         </is>
       </c>
       <c r="B179" s="24" t="n"/>
@@ -24709,7 +24555,7 @@
     <row r="180">
       <c r="A180" s="24" t="inlineStr">
         <is>
-          <t>CP38D</t>
+          <t>CWC6D</t>
         </is>
       </c>
       <c r="B180" s="24" t="n"/>
@@ -24737,7 +24583,7 @@
     <row r="181">
       <c r="A181" s="24" t="inlineStr">
         <is>
-          <t>CS45D</t>
+          <t>DEC2D</t>
         </is>
       </c>
       <c r="B181" s="24" t="n"/>
@@ -24765,7 +24611,7 @@
     <row r="182">
       <c r="A182" s="24" t="inlineStr">
         <is>
-          <t>CS51D</t>
+          <t>DNCAD</t>
         </is>
       </c>
       <c r="B182" s="24" t="n"/>
@@ -24793,7 +24639,7 @@
     <row r="183">
       <c r="A183" s="24" t="inlineStr">
         <is>
-          <t>CS52D</t>
+          <t>EAC3D</t>
         </is>
       </c>
       <c r="B183" s="24" t="n"/>
@@ -24821,7 +24667,7 @@
     <row r="184">
       <c r="A184" s="24" t="inlineStr">
         <is>
-          <t>CWC6D</t>
+          <t>FO4AD</t>
         </is>
       </c>
       <c r="B184" s="24" t="n"/>
@@ -24849,7 +24695,7 @@
     <row r="185">
       <c r="A185" s="24" t="inlineStr">
         <is>
-          <t>DEC2D</t>
+          <t>FYC1D</t>
         </is>
       </c>
       <c r="B185" s="24" t="n"/>
@@ -24877,7 +24723,7 @@
     <row r="186">
       <c r="A186" s="24" t="inlineStr">
         <is>
-          <t>DNCAD</t>
+          <t>GN43D</t>
         </is>
       </c>
       <c r="B186" s="24" t="n"/>
@@ -24905,7 +24751,7 @@
     <row r="187">
       <c r="A187" s="24" t="inlineStr">
         <is>
-          <t>EAC3D</t>
+          <t>GN47D</t>
         </is>
       </c>
       <c r="B187" s="24" t="n"/>
@@ -24933,7 +24779,7 @@
     <row r="188">
       <c r="A188" s="24" t="inlineStr">
         <is>
-          <t>FO4AD</t>
+          <t>GN48D</t>
         </is>
       </c>
       <c r="B188" s="24" t="n"/>
@@ -24961,7 +24807,7 @@
     <row r="189">
       <c r="A189" s="24" t="inlineStr">
         <is>
-          <t>FYC1D</t>
+          <t>GN49D</t>
         </is>
       </c>
       <c r="B189" s="24" t="n"/>
@@ -24989,7 +24835,7 @@
     <row r="190">
       <c r="A190" s="24" t="inlineStr">
         <is>
-          <t>GN43D</t>
+          <t>GOC4D</t>
         </is>
       </c>
       <c r="B190" s="24" t="n"/>
@@ -25017,7 +24863,7 @@
     <row r="191">
       <c r="A191" s="24" t="inlineStr">
         <is>
-          <t>GN47D</t>
+          <t>GYC4D</t>
         </is>
       </c>
       <c r="B191" s="24" t="n"/>
@@ -25045,7 +24891,7 @@
     <row r="192">
       <c r="A192" s="24" t="inlineStr">
         <is>
-          <t>GN48D</t>
+          <t>GYC5D</t>
         </is>
       </c>
       <c r="B192" s="24" t="n"/>
@@ -25073,7 +24919,7 @@
     <row r="193">
       <c r="A193" s="24" t="inlineStr">
         <is>
-          <t>GN49D</t>
+          <t>HBCAD</t>
         </is>
       </c>
       <c r="B193" s="24" t="n"/>
@@ -25101,7 +24947,7 @@
     <row r="194">
       <c r="A194" s="24" t="inlineStr">
         <is>
-          <t>GOC4D</t>
+          <t>HBCDD</t>
         </is>
       </c>
       <c r="B194" s="24" t="n"/>
@@ -25129,7 +24975,7 @@
     <row r="195">
       <c r="A195" s="24" t="inlineStr">
         <is>
-          <t>GYC4D</t>
+          <t>HJCFD</t>
         </is>
       </c>
       <c r="B195" s="24" t="n"/>
@@ -25157,7 +25003,7 @@
     <row r="196">
       <c r="A196" s="24" t="inlineStr">
         <is>
-          <t>GYC5D</t>
+          <t>HJCGD</t>
         </is>
       </c>
       <c r="B196" s="24" t="n"/>
@@ -25185,7 +25031,7 @@
     <row r="197">
       <c r="A197" s="24" t="inlineStr">
         <is>
-          <t>HBCAD</t>
+          <t>HVS1D</t>
         </is>
       </c>
       <c r="B197" s="24" t="n"/>
@@ -25213,7 +25059,7 @@
     <row r="198">
       <c r="A198" s="24" t="inlineStr">
         <is>
-          <t>HBCDD</t>
+          <t>JNC5D</t>
         </is>
       </c>
       <c r="B198" s="24" t="n"/>
@@ -25241,7 +25087,7 @@
     <row r="199">
       <c r="A199" s="24" t="inlineStr">
         <is>
-          <t>HJCFD</t>
+          <t>JNC6D</t>
         </is>
       </c>
       <c r="B199" s="24" t="n"/>
@@ -25269,7 +25115,7 @@
     <row r="200">
       <c r="A200" s="24" t="inlineStr">
         <is>
-          <t>HJCGD</t>
+          <t>LDCGD</t>
         </is>
       </c>
       <c r="B200" s="24" t="n"/>
@@ -25297,7 +25143,7 @@
     <row r="201">
       <c r="A201" s="24" t="inlineStr">
         <is>
-          <t>HVS1D</t>
+          <t>LIC6D</t>
         </is>
       </c>
       <c r="B201" s="24" t="n"/>
@@ -25325,7 +25171,7 @@
     <row r="202">
       <c r="A202" s="24" t="inlineStr">
         <is>
-          <t>JNC5D</t>
+          <t>LUC5D</t>
         </is>
       </c>
       <c r="B202" s="24" t="n"/>
@@ -25353,7 +25199,7 @@
     <row r="203">
       <c r="A203" s="24" t="inlineStr">
         <is>
-          <t>JNC6D</t>
+          <t>MCC1D</t>
         </is>
       </c>
       <c r="B203" s="24" t="n"/>
@@ -25381,7 +25227,7 @@
     <row r="204">
       <c r="A204" s="24" t="inlineStr">
         <is>
-          <t>LDCGD</t>
+          <t>MCC2D</t>
         </is>
       </c>
       <c r="B204" s="24" t="n"/>
@@ -25409,7 +25255,7 @@
     <row r="205">
       <c r="A205" s="24" t="inlineStr">
         <is>
-          <t>LIC6D</t>
+          <t>MCC3D</t>
         </is>
       </c>
       <c r="B205" s="24" t="n"/>
@@ -25437,7 +25283,7 @@
     <row r="206">
       <c r="A206" s="24" t="inlineStr">
         <is>
-          <t>LUC5D</t>
+          <t>MIC3D</t>
         </is>
       </c>
       <c r="B206" s="24" t="n"/>
@@ -25465,7 +25311,7 @@
     <row r="207">
       <c r="A207" s="24" t="inlineStr">
         <is>
-          <t>MCC1D</t>
+          <t>MIC4D</t>
         </is>
       </c>
       <c r="B207" s="24" t="n"/>
@@ -25493,7 +25339,7 @@
     <row r="208">
       <c r="A208" s="24" t="inlineStr">
         <is>
-          <t>MCC2D</t>
+          <t>MIC6D</t>
         </is>
       </c>
       <c r="B208" s="24" t="n"/>
@@ -25521,7 +25367,7 @@
     <row r="209">
       <c r="A209" s="24" t="inlineStr">
         <is>
-          <t>MCC3D</t>
+          <t>MR39D</t>
         </is>
       </c>
       <c r="B209" s="24" t="n"/>
@@ -25549,7 +25395,7 @@
     <row r="210">
       <c r="A210" s="24" t="inlineStr">
         <is>
-          <t>MIC3D</t>
+          <t>MSSED</t>
         </is>
       </c>
       <c r="B210" s="24" t="n"/>
@@ -25577,7 +25423,7 @@
     <row r="211">
       <c r="A211" s="24" t="inlineStr">
         <is>
-          <t>MIC4D</t>
+          <t>MSSFD</t>
         </is>
       </c>
       <c r="B211" s="24" t="n"/>
@@ -25605,7 +25451,7 @@
     <row r="212">
       <c r="A212" s="24" t="inlineStr">
         <is>
-          <t>MIC6D</t>
+          <t>MSSGD</t>
         </is>
       </c>
       <c r="B212" s="24" t="n"/>
@@ -25633,7 +25479,7 @@
     <row r="213">
       <c r="A213" s="24" t="inlineStr">
         <is>
-          <t>MR39D</t>
+          <t>MU31D</t>
         </is>
       </c>
       <c r="B213" s="24" t="n"/>
@@ -25661,7 +25507,7 @@
     <row r="214">
       <c r="A214" s="24" t="inlineStr">
         <is>
-          <t>MSSED</t>
+          <t>MU32D</t>
         </is>
       </c>
       <c r="B214" s="24" t="n"/>
@@ -25689,7 +25535,7 @@
     <row r="215">
       <c r="A215" s="24" t="inlineStr">
         <is>
-          <t>MSSFD</t>
+          <t>NBS1D</t>
         </is>
       </c>
       <c r="B215" s="24" t="n"/>
@@ -25717,7 +25563,7 @@
     <row r="216">
       <c r="A216" s="24" t="inlineStr">
         <is>
-          <t>MSSGD</t>
+          <t>NPCDD</t>
         </is>
       </c>
       <c r="B216" s="24" t="n"/>
@@ -25745,7 +25591,7 @@
     <row r="217">
       <c r="A217" s="24" t="inlineStr">
         <is>
-          <t>MU31D</t>
+          <t>OT41D</t>
         </is>
       </c>
       <c r="B217" s="24" t="n"/>
@@ -25773,7 +25619,7 @@
     <row r="218">
       <c r="A218" s="24" t="inlineStr">
         <is>
-          <t>MU32D</t>
+          <t>OZC3D</t>
         </is>
       </c>
       <c r="B218" s="24" t="n"/>
@@ -25801,7 +25647,7 @@
     <row r="219">
       <c r="A219" s="24" t="inlineStr">
         <is>
-          <t>NBS1D</t>
+          <t>PECMD</t>
         </is>
       </c>
       <c r="B219" s="24" t="n"/>
@@ -25829,7 +25675,7 @@
     <row r="220">
       <c r="A220" s="24" t="inlineStr">
         <is>
-          <t>NPCDD</t>
+          <t>PECND</t>
         </is>
       </c>
       <c r="B220" s="24" t="n"/>
@@ -25857,7 +25703,7 @@
     <row r="221">
       <c r="A221" s="24" t="inlineStr">
         <is>
-          <t>OT41D</t>
+          <t>PFC3D</t>
         </is>
       </c>
       <c r="B221" s="24" t="n"/>
@@ -25885,7 +25731,7 @@
     <row r="222">
       <c r="A222" s="24" t="inlineStr">
         <is>
-          <t>OZC3D</t>
+          <t>PN34D</t>
         </is>
       </c>
       <c r="B222" s="24" t="n"/>
@@ -25913,7 +25759,7 @@
     <row r="223">
       <c r="A223" s="24" t="inlineStr">
         <is>
-          <t>PECMD</t>
+          <t>PQCRD</t>
         </is>
       </c>
       <c r="B223" s="24" t="n"/>
@@ -25941,7 +25787,7 @@
     <row r="224">
       <c r="A224" s="24" t="inlineStr">
         <is>
-          <t>PECND</t>
+          <t>PQCTD</t>
         </is>
       </c>
       <c r="B224" s="24" t="n"/>
@@ -25969,7 +25815,7 @@
     <row r="225">
       <c r="A225" s="24" t="inlineStr">
         <is>
-          <t>PFC3D</t>
+          <t>PZCGD</t>
         </is>
       </c>
       <c r="B225" s="24" t="n"/>
@@ -25997,7 +25843,7 @@
     <row r="226">
       <c r="A226" s="24" t="inlineStr">
         <is>
-          <t>PN34D</t>
+          <t>RC1CD</t>
         </is>
       </c>
       <c r="B226" s="24" t="n"/>
@@ -26025,7 +25871,7 @@
     <row r="227">
       <c r="A227" s="24" t="inlineStr">
         <is>
-          <t>PQCRD</t>
+          <t>RC3CD</t>
         </is>
       </c>
       <c r="B227" s="24" t="n"/>
@@ -26053,7 +25899,7 @@
     <row r="228">
       <c r="A228" s="24" t="inlineStr">
         <is>
-          <t>PQCTD</t>
+          <t>RC5CD</t>
         </is>
       </c>
       <c r="B228" s="24" t="n"/>
@@ -26081,7 +25927,7 @@
     <row r="229">
       <c r="A229" s="24" t="inlineStr">
         <is>
-          <t>PZCGD</t>
+          <t>RZ9BD</t>
         </is>
       </c>
       <c r="B229" s="24" t="n"/>
@@ -26109,7 +25955,7 @@
     <row r="230">
       <c r="A230" s="24" t="inlineStr">
         <is>
-          <t>RC1CD</t>
+          <t>RZABD</t>
         </is>
       </c>
       <c r="B230" s="24" t="n"/>
@@ -26137,7 +25983,7 @@
     <row r="231">
       <c r="A231" s="24" t="inlineStr">
         <is>
-          <t>RC3CD</t>
+          <t>SBC1D</t>
         </is>
       </c>
       <c r="B231" s="24" t="n"/>
@@ -26165,7 +26011,7 @@
     <row r="232">
       <c r="A232" s="24" t="inlineStr">
         <is>
-          <t>RC5CD</t>
+          <t>SBC2D</t>
         </is>
       </c>
       <c r="B232" s="24" t="n"/>
@@ -26193,7 +26039,7 @@
     <row r="233">
       <c r="A233" s="24" t="inlineStr">
         <is>
-          <t>RZ9BD</t>
+          <t>SIC1D</t>
         </is>
       </c>
       <c r="B233" s="24" t="n"/>
@@ -26221,7 +26067,7 @@
     <row r="234">
       <c r="A234" s="24" t="inlineStr">
         <is>
-          <t>RZABD</t>
+          <t>SNABD</t>
         </is>
       </c>
       <c r="B234" s="24" t="n"/>
@@ -26249,7 +26095,7 @@
     <row r="235">
       <c r="A235" s="24" t="inlineStr">
         <is>
-          <t>SBC1D</t>
+          <t>SNEAD</t>
         </is>
       </c>
       <c r="B235" s="24" t="n"/>
@@ -26277,7 +26123,7 @@
     <row r="236">
       <c r="A236" s="24" t="inlineStr">
         <is>
-          <t>SBC2D</t>
+          <t>SNEBD</t>
         </is>
       </c>
       <c r="B236" s="24" t="n"/>
@@ -26305,7 +26151,7 @@
     <row r="237">
       <c r="A237" s="24" t="inlineStr">
         <is>
-          <t>SIC1D</t>
+          <t>SNSBD</t>
         </is>
       </c>
       <c r="B237" s="24" t="n"/>
@@ -26333,7 +26179,7 @@
     <row r="238">
       <c r="A238" s="24" t="inlineStr">
         <is>
-          <t>SNABD</t>
+          <t>SNSDD</t>
         </is>
       </c>
       <c r="B238" s="24" t="n"/>
@@ -26361,7 +26207,7 @@
     <row r="239">
       <c r="A239" s="24" t="inlineStr">
         <is>
-          <t>SNEAD</t>
+          <t>STCFD</t>
         </is>
       </c>
       <c r="B239" s="24" t="n"/>
@@ -26389,7 +26235,7 @@
     <row r="240">
       <c r="A240" s="24" t="inlineStr">
         <is>
-          <t>SNEBD</t>
+          <t>SXC4D</t>
         </is>
       </c>
       <c r="B240" s="24" t="n"/>
@@ -26417,7 +26263,7 @@
     <row r="241">
       <c r="A241" s="24" t="inlineStr">
         <is>
-          <t>SNSBD</t>
+          <t>T641D</t>
         </is>
       </c>
       <c r="B241" s="24" t="n"/>
@@ -26445,7 +26291,7 @@
     <row r="242">
       <c r="A242" s="24" t="inlineStr">
         <is>
-          <t>SNSDD</t>
+          <t>T672D</t>
         </is>
       </c>
       <c r="B242" s="24" t="n"/>
@@ -26473,7 +26319,7 @@
     <row r="243">
       <c r="A243" s="24" t="inlineStr">
         <is>
-          <t>STCFD</t>
+          <t>TLCVD</t>
         </is>
       </c>
       <c r="B243" s="24" t="n"/>
@@ -26501,7 +26347,7 @@
     <row r="244">
       <c r="A244" s="24" t="inlineStr">
         <is>
-          <t>SXC4D</t>
+          <t>TLCWD</t>
         </is>
       </c>
       <c r="B244" s="24" t="n"/>
@@ -26529,7 +26375,7 @@
     <row r="245">
       <c r="A245" s="24" t="inlineStr">
         <is>
-          <t>T641D</t>
+          <t>TTCED</t>
         </is>
       </c>
       <c r="B245" s="24" t="n"/>
@@ -26557,7 +26403,7 @@
     <row r="246">
       <c r="A246" s="24" t="inlineStr">
         <is>
-          <t>T672D</t>
+          <t>VBC1D</t>
         </is>
       </c>
       <c r="B246" s="24" t="n"/>
@@ -26585,7 +26431,7 @@
     <row r="247">
       <c r="A247" s="24" t="inlineStr">
         <is>
-          <t>TLCVD</t>
+          <t>VBC2D</t>
         </is>
       </c>
       <c r="B247" s="24" t="n"/>
@@ -26613,7 +26459,7 @@
     <row r="248">
       <c r="A248" s="24" t="inlineStr">
         <is>
-          <t>TLCWD</t>
+          <t>VSCID</t>
         </is>
       </c>
       <c r="B248" s="24" t="n"/>
@@ -26641,7 +26487,7 @@
     <row r="249">
       <c r="A249" s="24" t="inlineStr">
         <is>
-          <t>TTCED</t>
+          <t>VSCPD</t>
         </is>
       </c>
       <c r="B249" s="24" t="n"/>
@@ -26669,7 +26515,7 @@
     <row r="250">
       <c r="A250" s="24" t="inlineStr">
         <is>
-          <t>VBC1D</t>
+          <t>VSCXD</t>
         </is>
       </c>
       <c r="B250" s="24" t="n"/>
@@ -26697,7 +26543,7 @@
     <row r="251">
       <c r="A251" s="24" t="inlineStr">
         <is>
-          <t>VBC2D</t>
+          <t>WBS1D</t>
         </is>
       </c>
       <c r="B251" s="24" t="n"/>
@@ -26725,7 +26571,7 @@
     <row r="252">
       <c r="A252" s="24" t="inlineStr">
         <is>
-          <t>VSCID</t>
+          <t>YFCKD</t>
         </is>
       </c>
       <c r="B252" s="24" t="n"/>
@@ -26753,7 +26599,7 @@
     <row r="253">
       <c r="A253" s="24" t="inlineStr">
         <is>
-          <t>VSCPD</t>
+          <t>ZPC2D</t>
         </is>
       </c>
       <c r="B253" s="24" t="n"/>
@@ -26781,7 +26627,7 @@
     <row r="254">
       <c r="A254" s="24" t="inlineStr">
         <is>
-          <t>VSCXD</t>
+          <t>ZPC3D</t>
         </is>
       </c>
       <c r="B254" s="24" t="n"/>
@@ -26809,7 +26655,7 @@
     <row r="255">
       <c r="A255" s="24" t="inlineStr">
         <is>
-          <t>WBS1D</t>
+          <t>PUC2D</t>
         </is>
       </c>
       <c r="B255" s="24" t="n"/>
@@ -26837,7 +26683,7 @@
     <row r="256">
       <c r="A256" s="24" t="inlineStr">
         <is>
-          <t>YFCKD</t>
+          <t>ICC6D</t>
         </is>
       </c>
       <c r="B256" s="24" t="n"/>
@@ -26865,7 +26711,7 @@
     <row r="257">
       <c r="A257" s="24" t="inlineStr">
         <is>
-          <t>ZPC2D</t>
+          <t>MJC1D</t>
         </is>
       </c>
       <c r="B257" s="24" t="n"/>
@@ -26893,7 +26739,7 @@
     <row r="258">
       <c r="A258" s="24" t="inlineStr">
         <is>
-          <t>ZPC3D</t>
+          <t>BPCTD</t>
         </is>
       </c>
       <c r="B258" s="24" t="n"/>
@@ -26921,7 +26767,7 @@
     <row r="259">
       <c r="A259" s="24" t="inlineStr">
         <is>
-          <t>PUC2D</t>
+          <t>BVCOD</t>
         </is>
       </c>
       <c r="B259" s="24" t="n"/>
@@ -26949,7 +26795,7 @@
     <row r="260">
       <c r="A260" s="24" t="inlineStr">
         <is>
-          <t>ICC6D</t>
+          <t>BYY2D</t>
         </is>
       </c>
       <c r="B260" s="24" t="n"/>
@@ -26977,7 +26823,7 @@
     <row r="261">
       <c r="A261" s="24" t="inlineStr">
         <is>
-          <t>MJC1D</t>
+          <t>HJCLD</t>
         </is>
       </c>
       <c r="B261" s="24" t="n"/>
@@ -27002,6 +26848,62 @@
       <c r="Q261" s="24" t="n"/>
       <c r="R261" s="24" t="n"/>
     </row>
+    <row r="262">
+      <c r="A262" s="24" t="inlineStr">
+        <is>
+          <t>RZBBD</t>
+        </is>
+      </c>
+      <c r="B262" s="24" t="n"/>
+      <c r="C262" s="24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D262" s="24" t="n"/>
+      <c r="E262" s="24" t="n"/>
+      <c r="F262" s="24" t="n"/>
+      <c r="G262" s="24" t="n"/>
+      <c r="H262" s="24" t="n"/>
+      <c r="I262" s="24" t="n"/>
+      <c r="J262" s="24" t="n"/>
+      <c r="K262" s="24" t="n"/>
+      <c r="L262" s="24" t="n"/>
+      <c r="M262" s="24" t="n"/>
+      <c r="N262" s="24" t="n"/>
+      <c r="O262" s="24" t="n"/>
+      <c r="P262" s="24" t="n"/>
+      <c r="Q262" s="24" t="n"/>
+      <c r="R262" s="24" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="24" t="inlineStr">
+        <is>
+          <t>RZBCD</t>
+        </is>
+      </c>
+      <c r="B263" s="24" t="n"/>
+      <c r="C263" s="24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D263" s="24" t="n"/>
+      <c r="E263" s="24" t="n"/>
+      <c r="F263" s="24" t="n"/>
+      <c r="G263" s="24" t="n"/>
+      <c r="H263" s="24" t="n"/>
+      <c r="I263" s="24" t="n"/>
+      <c r="J263" s="24" t="n"/>
+      <c r="K263" s="24" t="n"/>
+      <c r="L263" s="24" t="n"/>
+      <c r="M263" s="24" t="n"/>
+      <c r="N263" s="24" t="n"/>
+      <c r="O263" s="24" t="n"/>
+      <c r="P263" s="24" t="n"/>
+      <c r="Q263" s="24" t="n"/>
+      <c r="R263" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/instruments_master.xlsx
+++ b/data/instruments_master.xlsx
@@ -14399,7 +14399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R263"/>
+  <dimension ref="A1:R265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26904,6 +26904,62 @@
       <c r="Q263" s="24" t="n"/>
       <c r="R263" s="24" t="n"/>
     </row>
+    <row r="264">
+      <c r="A264" s="24" t="inlineStr">
+        <is>
+          <t>BF44D</t>
+        </is>
+      </c>
+      <c r="B264" s="24" t="n"/>
+      <c r="C264" s="24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D264" s="24" t="n"/>
+      <c r="E264" s="24" t="n"/>
+      <c r="F264" s="24" t="n"/>
+      <c r="G264" s="24" t="n"/>
+      <c r="H264" s="24" t="n"/>
+      <c r="I264" s="24" t="n"/>
+      <c r="J264" s="24" t="n"/>
+      <c r="K264" s="24" t="n"/>
+      <c r="L264" s="24" t="n"/>
+      <c r="M264" s="24" t="n"/>
+      <c r="N264" s="24" t="n"/>
+      <c r="O264" s="24" t="n"/>
+      <c r="P264" s="24" t="n"/>
+      <c r="Q264" s="24" t="n"/>
+      <c r="R264" s="24" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="24" t="inlineStr">
+        <is>
+          <t>RZBAD</t>
+        </is>
+      </c>
+      <c r="B265" s="24" t="n"/>
+      <c r="C265" s="24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D265" s="24" t="n"/>
+      <c r="E265" s="24" t="n"/>
+      <c r="F265" s="24" t="n"/>
+      <c r="G265" s="24" t="n"/>
+      <c r="H265" s="24" t="n"/>
+      <c r="I265" s="24" t="n"/>
+      <c r="J265" s="24" t="n"/>
+      <c r="K265" s="24" t="n"/>
+      <c r="L265" s="24" t="n"/>
+      <c r="M265" s="24" t="n"/>
+      <c r="N265" s="24" t="n"/>
+      <c r="O265" s="24" t="n"/>
+      <c r="P265" s="24" t="n"/>
+      <c r="Q265" s="24" t="n"/>
+      <c r="R265" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/instruments_master.xlsx
+++ b/data/instruments_master.xlsx
@@ -3779,7 +3779,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3904,7 +3904,46 @@
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
     </row>
-    <row r="6" ht="18.75" customHeight="1"/>
+    <row r="6" ht="18.75" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>D31L6</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="n">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>D31G6</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>D31M7</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="n">
+        <v>46477</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TZVD8</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="n">
+        <v>47102</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14399,7 +14438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R265"/>
+  <dimension ref="A1:R268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26960,6 +26999,90 @@
       <c r="Q265" s="24" t="n"/>
       <c r="R265" s="24" t="n"/>
     </row>
+    <row r="266">
+      <c r="A266" s="24" t="inlineStr">
+        <is>
+          <t>EAC4D</t>
+        </is>
+      </c>
+      <c r="B266" s="24" t="n"/>
+      <c r="C266" s="24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D266" s="24" t="n"/>
+      <c r="E266" s="24" t="n"/>
+      <c r="F266" s="24" t="n"/>
+      <c r="G266" s="24" t="n"/>
+      <c r="H266" s="24" t="n"/>
+      <c r="I266" s="24" t="n"/>
+      <c r="J266" s="24" t="n"/>
+      <c r="K266" s="24" t="n"/>
+      <c r="L266" s="24" t="n"/>
+      <c r="M266" s="24" t="n"/>
+      <c r="N266" s="24" t="n"/>
+      <c r="O266" s="24" t="n"/>
+      <c r="P266" s="24" t="n"/>
+      <c r="Q266" s="24" t="n"/>
+      <c r="R266" s="24" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="24" t="inlineStr">
+        <is>
+          <t>IRCQD</t>
+        </is>
+      </c>
+      <c r="B267" s="24" t="n"/>
+      <c r="C267" s="24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D267" s="24" t="n"/>
+      <c r="E267" s="24" t="n"/>
+      <c r="F267" s="24" t="n"/>
+      <c r="G267" s="24" t="n"/>
+      <c r="H267" s="24" t="n"/>
+      <c r="I267" s="24" t="n"/>
+      <c r="J267" s="24" t="n"/>
+      <c r="K267" s="24" t="n"/>
+      <c r="L267" s="24" t="n"/>
+      <c r="M267" s="24" t="n"/>
+      <c r="N267" s="24" t="n"/>
+      <c r="O267" s="24" t="n"/>
+      <c r="P267" s="24" t="n"/>
+      <c r="Q267" s="24" t="n"/>
+      <c r="R267" s="24" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="24" t="inlineStr">
+        <is>
+          <t>SBC3D</t>
+        </is>
+      </c>
+      <c r="B268" s="24" t="n"/>
+      <c r="C268" s="24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D268" s="24" t="n"/>
+      <c r="E268" s="24" t="n"/>
+      <c r="F268" s="24" t="n"/>
+      <c r="G268" s="24" t="n"/>
+      <c r="H268" s="24" t="n"/>
+      <c r="I268" s="24" t="n"/>
+      <c r="J268" s="24" t="n"/>
+      <c r="K268" s="24" t="n"/>
+      <c r="L268" s="24" t="n"/>
+      <c r="M268" s="24" t="n"/>
+      <c r="N268" s="24" t="n"/>
+      <c r="O268" s="24" t="n"/>
+      <c r="P268" s="24" t="n"/>
+      <c r="Q268" s="24" t="n"/>
+      <c r="R268" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/instruments_master.xlsx
+++ b/data/instruments_master.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2058,8 +2058,114 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" ht="18.75" customHeight="1"/>
-    <row r="34" ht="18.75" customHeight="1"/>
+    <row r="33" ht="18.75" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AN29</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>AN29</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BONAR</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="n">
+        <v>47452</v>
+      </c>
+      <c r="E33" s="22" t="n">
+        <v>46003</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>30/360</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18.75" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AN29D</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>AN29D</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BONAR</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="n">
+        <v>47452</v>
+      </c>
+      <c r="E34" s="22" t="n">
+        <v>46003</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>30/360</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BPA8D</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BPA8D</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BOPREAL</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="n">
+        <v>47057</v>
+      </c>
+      <c r="E35" s="22" t="n">
+        <v>45832</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>30/360</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2071,7 +2177,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2572,7 +2678,27 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="18.75" customHeight="1"/>
+    <row r="20" ht="18.75" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S15S6</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LECAP</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="n">
+        <v>46171</v>
+      </c>
+      <c r="D20" s="22" t="n">
+        <v>46280</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.0199</v>
+      </c>
+    </row>
     <row r="21" ht="18.75" customHeight="1"/>
     <row r="22" ht="18.75" customHeight="1"/>
     <row r="23" ht="18.75" customHeight="1"/>
@@ -2588,7 +2714,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3765,9 +3891,99 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="18.75" customHeight="1"/>
-    <row r="29" ht="18.75" customHeight="1"/>
-    <row r="30" ht="18.75" customHeight="1"/>
+    <row r="28" ht="18.75" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TXMD8_CER</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BONCER ZC</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="n">
+        <v>46185</v>
+      </c>
+      <c r="D28" s="22" t="n">
+        <v>47102</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>779.88639313</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>BONO DUAL CER-TAMAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18.75" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TXMD9_CER</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BONCER ZC</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="n">
+        <v>46185</v>
+      </c>
+      <c r="D29" s="22" t="n">
+        <v>47466</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>779.88639313</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>BONO DUAL CER-TAMAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18.75" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TXMJ0_CER</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BONCER ZC</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="n">
+        <v>46185</v>
+      </c>
+      <c r="D30" s="22" t="n">
+        <v>47662</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>779.88639313</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>BONO DUAL CER-TAMAR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3955,7 +4171,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -4261,13 +4477,13 @@
       </c>
       <c r="E10" s="12" t="n"/>
       <c r="F10" s="5" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>758.1179560428147</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
@@ -4291,13 +4507,94 @@
       </c>
       <c r="E11" s="12" t="n"/>
       <c r="F11" s="5" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>746.3809193800248</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.05</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TXMD8</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DUAL_CER_TAMAR</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="n">
+        <v>46185</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>47102</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G12" t="n">
+        <v>779.88639313</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TXMD9</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DUAL_CER_TAMAR</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="n">
+        <v>46185</v>
+      </c>
+      <c r="D13" s="22" t="n">
+        <v>47466</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G13" t="n">
+        <v>779.88639313</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TXMJ0</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DUAL_CER_TAMAR</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="n">
+        <v>46185</v>
+      </c>
+      <c r="D14" s="22" t="n">
+        <v>47662</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G14" t="n">
+        <v>779.88639313</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4311,7 +4608,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D535"/>
+  <dimension ref="A1:D555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -8539,7 +8836,7 @@
     <row r="235" ht="18.75" customHeight="1">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>BPB8D</t>
+          <t>AO28D</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -8551,97 +8848,97 @@
         <v>0</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="236" ht="18.75" customHeight="1">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>BPB8D</t>
+          <t>AO28D</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="C236" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="237" ht="18.75" customHeight="1">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>BPB8D</t>
+          <t>AO28D</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>2027-04-30</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C237" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="238" ht="18.75" customHeight="1">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>BPB8D</t>
+          <t>AO28D</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>2027-10-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C238" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="239" ht="18.75" customHeight="1">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>BPB8D</t>
+          <t>AO28D</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>2028-04-30</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="C239" s="8" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="240" ht="18.75" customHeight="1">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>BPB8D</t>
+          <t>AO28D</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>2028-10-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C240" s="8" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="241" ht="18.75" customHeight="1">
@@ -8652,7 +8949,7 @@
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C241" s="8" t="n">
@@ -8670,7 +8967,7 @@
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="C242" s="8" t="n">
@@ -8688,7 +8985,7 @@
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="C243" s="8" t="n">
@@ -8706,7 +9003,7 @@
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2027-01-30</t>
         </is>
       </c>
       <c r="C244" s="8" t="n">
@@ -8724,7 +9021,7 @@
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2027-02-28</t>
         </is>
       </c>
       <c r="C245" s="8" t="n">
@@ -8742,7 +9039,7 @@
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2027-03-28</t>
         </is>
       </c>
       <c r="C246" s="8" t="n">
@@ -8760,7 +9057,7 @@
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2027-04-28</t>
         </is>
       </c>
       <c r="C247" s="8" t="n">
@@ -8778,7 +9075,7 @@
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2027-05-28</t>
         </is>
       </c>
       <c r="C248" s="8" t="n">
@@ -8796,7 +9093,7 @@
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2027-06-28</t>
         </is>
       </c>
       <c r="C249" s="8" t="n">
@@ -8814,7 +9111,7 @@
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>2027-01-30</t>
+          <t>2027-07-28</t>
         </is>
       </c>
       <c r="C250" s="8" t="n">
@@ -8832,7 +9129,7 @@
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>2027-08-28</t>
         </is>
       </c>
       <c r="C251" s="8" t="n">
@@ -8850,7 +9147,7 @@
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>2027-03-28</t>
+          <t>2027-09-28</t>
         </is>
       </c>
       <c r="C252" s="8" t="n">
@@ -8868,7 +9165,7 @@
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>2027-04-28</t>
+          <t>2027-10-28</t>
         </is>
       </c>
       <c r="C253" s="8" t="n">
@@ -8886,7 +9183,7 @@
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>2027-05-28</t>
+          <t>2027-11-28</t>
         </is>
       </c>
       <c r="C254" s="8" t="n">
@@ -8904,7 +9201,7 @@
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>2027-06-28</t>
+          <t>2027-12-28</t>
         </is>
       </c>
       <c r="C255" s="8" t="n">
@@ -8922,7 +9219,7 @@
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>2027-07-28</t>
+          <t>2028-01-28</t>
         </is>
       </c>
       <c r="C256" s="8" t="n">
@@ -8940,7 +9237,7 @@
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>2027-08-28</t>
+          <t>2028-02-28</t>
         </is>
       </c>
       <c r="C257" s="8" t="n">
@@ -8958,7 +9255,7 @@
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>2027-09-28</t>
+          <t>2028-03-28</t>
         </is>
       </c>
       <c r="C258" s="8" t="n">
@@ -8976,7 +9273,7 @@
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>2027-10-28</t>
+          <t>2028-04-28</t>
         </is>
       </c>
       <c r="C259" s="8" t="n">
@@ -8994,7 +9291,7 @@
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>2027-11-28</t>
+          <t>2028-05-28</t>
         </is>
       </c>
       <c r="C260" s="8" t="n">
@@ -9012,7 +9309,7 @@
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>2027-12-28</t>
+          <t>2028-06-28</t>
         </is>
       </c>
       <c r="C261" s="8" t="n">
@@ -9030,7 +9327,7 @@
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>2028-01-28</t>
+          <t>2028-07-28</t>
         </is>
       </c>
       <c r="C262" s="8" t="n">
@@ -9048,7 +9345,7 @@
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>2028-02-28</t>
+          <t>2028-08-28</t>
         </is>
       </c>
       <c r="C263" s="8" t="n">
@@ -9066,7 +9363,7 @@
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>2028-03-28</t>
+          <t>2028-09-28</t>
         </is>
       </c>
       <c r="C264" s="8" t="n">
@@ -9084,7 +9381,7 @@
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>2028-04-28</t>
+          <t>2028-10-28</t>
         </is>
       </c>
       <c r="C265" s="8" t="n">
@@ -9102,11 +9399,11 @@
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>2028-05-28</t>
+          <t>2028-10-31</t>
         </is>
       </c>
       <c r="C266" s="8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D266" s="5" t="n">
         <v>0.5</v>
@@ -9115,109 +9412,109 @@
     <row r="267" ht="18.75" customHeight="1">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>AO28D</t>
+          <t>AE38</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>2028-06-28</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C267" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D267" s="5" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="268" ht="18.75" customHeight="1">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>AO28D</t>
+          <t>AE38</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>2028-07-28</t>
+          <t>2027-01-09</t>
         </is>
       </c>
       <c r="C268" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D268" s="5" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="269" ht="18.75" customHeight="1">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>AO28D</t>
+          <t>AE38</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>2028-08-28</t>
-        </is>
-      </c>
-      <c r="C269" s="8" t="n">
-        <v>0</v>
+          <t>2027-07-09</t>
+        </is>
+      </c>
+      <c r="C269" s="5" t="n">
+        <v>4.5454</v>
       </c>
       <c r="D269" s="5" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="270" ht="18.75" customHeight="1">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>AO28D</t>
+          <t>AE38</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>2028-09-28</t>
-        </is>
-      </c>
-      <c r="C270" s="8" t="n">
-        <v>0</v>
+          <t>2028-01-09</t>
+        </is>
+      </c>
+      <c r="C270" s="5" t="n">
+        <v>4.5454</v>
       </c>
       <c r="D270" s="5" t="n">
-        <v>0.5</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="271" ht="18.75" customHeight="1">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>AO28D</t>
+          <t>AE38</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>2028-10-28</t>
-        </is>
-      </c>
-      <c r="C271" s="8" t="n">
-        <v>0</v>
+          <t>2028-07-09</t>
+        </is>
+      </c>
+      <c r="C271" s="5" t="n">
+        <v>4.5454</v>
       </c>
       <c r="D271" s="5" t="n">
-        <v>0.5</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="272" ht="18.75" customHeight="1">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>AO28D</t>
+          <t>AE38</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>2028-10-31</t>
-        </is>
-      </c>
-      <c r="C272" s="8" t="n">
-        <v>100</v>
+          <t>2029-01-09</t>
+        </is>
+      </c>
+      <c r="C272" s="5" t="n">
+        <v>4.5454</v>
       </c>
       <c r="D272" s="5" t="n">
-        <v>0.5</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="273" ht="18.75" customHeight="1">
@@ -9228,14 +9525,14 @@
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="C273" s="8" t="n">
-        <v>0</v>
+          <t>2029-07-09</t>
+        </is>
+      </c>
+      <c r="C273" s="5" t="n">
+        <v>4.5454</v>
       </c>
       <c r="D273" s="5" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="274" ht="18.75" customHeight="1">
@@ -9246,14 +9543,14 @@
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
-        </is>
-      </c>
-      <c r="C274" s="8" t="n">
-        <v>0</v>
+          <t>2030-01-09</t>
+        </is>
+      </c>
+      <c r="C274" s="5" t="n">
+        <v>4.5454</v>
       </c>
       <c r="D274" s="5" t="n">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="275" ht="18.75" customHeight="1">
@@ -9264,14 +9561,14 @@
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2030-07-09</t>
         </is>
       </c>
       <c r="C275" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D275" s="5" t="n">
-        <v>2.5</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="276" ht="18.75" customHeight="1">
@@ -9282,14 +9579,14 @@
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>2028-01-09</t>
+          <t>2031-01-09</t>
         </is>
       </c>
       <c r="C276" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D276" s="5" t="n">
-        <v>2.39</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="277" ht="18.75" customHeight="1">
@@ -9300,14 +9597,14 @@
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>2028-07-09</t>
+          <t>2031-07-09</t>
         </is>
       </c>
       <c r="C277" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D277" s="5" t="n">
-        <v>2.27</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="278" ht="18.75" customHeight="1">
@@ -9318,14 +9615,14 @@
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>2029-01-09</t>
+          <t>2032-01-09</t>
         </is>
       </c>
       <c r="C278" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D278" s="5" t="n">
-        <v>2.16</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="279" ht="18.75" customHeight="1">
@@ -9336,14 +9633,14 @@
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>2029-07-09</t>
+          <t>2032-07-09</t>
         </is>
       </c>
       <c r="C279" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D279" s="5" t="n">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="280" ht="18.75" customHeight="1">
@@ -9354,14 +9651,14 @@
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>2030-01-09</t>
+          <t>2033-01-09</t>
         </is>
       </c>
       <c r="C280" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D280" s="5" t="n">
-        <v>1.93</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="281" ht="18.75" customHeight="1">
@@ -9372,14 +9669,14 @@
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>2030-07-09</t>
+          <t>2033-07-09</t>
         </is>
       </c>
       <c r="C281" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D281" s="5" t="n">
-        <v>1.82</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="282" ht="18.75" customHeight="1">
@@ -9390,14 +9687,14 @@
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>2031-01-09</t>
+          <t>2034-01-09</t>
         </is>
       </c>
       <c r="C282" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D282" s="5" t="n">
-        <v>1.7</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="283" ht="18.75" customHeight="1">
@@ -9408,14 +9705,14 @@
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>2031-07-09</t>
+          <t>2034-07-09</t>
         </is>
       </c>
       <c r="C283" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D283" s="5" t="n">
-        <v>1.59</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="284" ht="18.75" customHeight="1">
@@ -9426,14 +9723,14 @@
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>2032-01-09</t>
+          <t>2035-01-09</t>
         </is>
       </c>
       <c r="C284" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D284" s="5" t="n">
-        <v>1.48</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="285" ht="18.75" customHeight="1">
@@ -9444,14 +9741,14 @@
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>2032-07-09</t>
+          <t>2035-07-09</t>
         </is>
       </c>
       <c r="C285" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D285" s="5" t="n">
-        <v>1.36</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="286" ht="18.75" customHeight="1">
@@ -9462,14 +9759,14 @@
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>2033-01-09</t>
+          <t>2036-01-09</t>
         </is>
       </c>
       <c r="C286" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D286" s="5" t="n">
-        <v>1.25</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="287" ht="18.75" customHeight="1">
@@ -9480,14 +9777,14 @@
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>2033-07-09</t>
+          <t>2036-07-09</t>
         </is>
       </c>
       <c r="C287" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D287" s="5" t="n">
-        <v>1.14</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="288" ht="18.75" customHeight="1">
@@ -9498,14 +9795,14 @@
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>2034-01-09</t>
+          <t>2037-01-09</t>
         </is>
       </c>
       <c r="C288" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D288" s="5" t="n">
-        <v>1.02</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="289" ht="18.75" customHeight="1">
@@ -9516,14 +9813,14 @@
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>2034-07-09</t>
+          <t>2037-07-09</t>
         </is>
       </c>
       <c r="C289" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D289" s="5" t="n">
-        <v>0.91</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="290" ht="18.75" customHeight="1">
@@ -9534,122 +9831,122 @@
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>2035-01-09</t>
+          <t>2038-01-09</t>
         </is>
       </c>
       <c r="C290" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D290" s="5" t="n">
-        <v>0.8</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="291" ht="18.75" customHeight="1">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>AE38</t>
+          <t>AL29</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>2035-07-09</t>
-        </is>
-      </c>
-      <c r="C291" s="5" t="n">
-        <v>4.5454</v>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C291" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="D291" s="5" t="n">
-        <v>0.68</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="292" ht="18.75" customHeight="1">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>AE38</t>
+          <t>AL29</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>2036-01-09</t>
-        </is>
-      </c>
-      <c r="C292" s="5" t="n">
-        <v>4.5454</v>
+          <t>2027-01-09</t>
+        </is>
+      </c>
+      <c r="C292" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="D292" s="5" t="n">
-        <v>0.57</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="293" ht="18.75" customHeight="1">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>AE38</t>
+          <t>AL29</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>2036-07-09</t>
-        </is>
-      </c>
-      <c r="C293" s="5" t="n">
-        <v>4.5454</v>
+          <t>2027-07-09</t>
+        </is>
+      </c>
+      <c r="C293" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="D293" s="5" t="n">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="294" ht="18.75" customHeight="1">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>AE38</t>
+          <t>AL29</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>2037-01-09</t>
-        </is>
-      </c>
-      <c r="C294" s="5" t="n">
-        <v>4.5454</v>
+          <t>2028-01-09</t>
+        </is>
+      </c>
+      <c r="C294" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="D294" s="5" t="n">
-        <v>0.34</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="295" ht="18.75" customHeight="1">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>AE38</t>
+          <t>AL29</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>2037-07-09</t>
-        </is>
-      </c>
-      <c r="C295" s="5" t="n">
-        <v>4.5454</v>
+          <t>2028-07-09</t>
+        </is>
+      </c>
+      <c r="C295" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="D295" s="5" t="n">
-        <v>0.23</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="296" ht="18.75" customHeight="1">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>AE38</t>
+          <t>AL29</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>2038-01-09</t>
-        </is>
-      </c>
-      <c r="C296" s="5" t="n">
-        <v>4.5454</v>
+          <t>2029-01-09</t>
+        </is>
+      </c>
+      <c r="C296" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="D296" s="5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="297" ht="18.75" customHeight="1">
@@ -9660,122 +9957,122 @@
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2029-07-09</t>
         </is>
       </c>
       <c r="C297" s="8" t="n">
         <v>10</v>
       </c>
       <c r="D297" s="5" t="n">
-        <v>0.35</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="298" ht="18.75" customHeight="1">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>AL29</t>
+          <t>AL30</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C298" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D298" s="5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="299" ht="18.75" customHeight="1">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>AL29</t>
+          <t>AL30</t>
         </is>
       </c>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2027-01-09</t>
         </is>
       </c>
       <c r="C299" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D299" s="5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="300" ht="18.75" customHeight="1">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>AL29</t>
+          <t>AL30</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>2028-01-09</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="C300" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D300" s="5" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="301" ht="18.75" customHeight="1">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>AL29</t>
+          <t>AL30</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>2028-07-09</t>
+          <t>2028-01-09</t>
         </is>
       </c>
       <c r="C301" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D301" s="5" t="n">
-        <v>0.15</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="302" ht="18.75" customHeight="1">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t>AL29</t>
+          <t>AL30</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>2029-01-09</t>
+          <t>2028-07-09</t>
         </is>
       </c>
       <c r="C302" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D302" s="5" t="n">
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="303" ht="18.75" customHeight="1">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t>AL29</t>
+          <t>AL30</t>
         </is>
       </c>
       <c r="B303" s="3" t="inlineStr">
         <is>
-          <t>2029-07-09</t>
+          <t>2029-01-09</t>
         </is>
       </c>
       <c r="C303" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D303" s="5" t="n">
-        <v>0.05</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="304" ht="18.75" customHeight="1">
@@ -9786,14 +10083,14 @@
       </c>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2029-07-09</t>
         </is>
       </c>
       <c r="C304" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D304" s="5" t="n">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="305" ht="18.75" customHeight="1">
@@ -9804,14 +10101,14 @@
       </c>
       <c r="B305" s="3" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2030-01-09</t>
         </is>
       </c>
       <c r="C305" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D305" s="5" t="n">
-        <v>0.24</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="306" ht="18.75" customHeight="1">
@@ -9822,122 +10119,122 @@
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2030-07-09</t>
         </is>
       </c>
       <c r="C306" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D306" s="5" t="n">
-        <v>0.21</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="307" ht="18.75" customHeight="1">
       <c r="A307" s="3" t="inlineStr">
         <is>
-          <t>AL30</t>
+          <t>AL30C</t>
         </is>
       </c>
       <c r="B307" s="3" t="inlineStr">
         <is>
-          <t>2028-01-09</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C307" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D307" s="5" t="n">
-        <v>0.42</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="308" ht="18.75" customHeight="1">
       <c r="A308" s="3" t="inlineStr">
         <is>
-          <t>AL30</t>
+          <t>AL30C</t>
         </is>
       </c>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>2028-07-09</t>
+          <t>2027-01-09</t>
         </is>
       </c>
       <c r="C308" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D308" s="5" t="n">
-        <v>0.35</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="309" ht="18.75" customHeight="1">
       <c r="A309" s="3" t="inlineStr">
         <is>
-          <t>AL30</t>
+          <t>AL30C</t>
         </is>
       </c>
       <c r="B309" s="3" t="inlineStr">
         <is>
-          <t>2029-01-09</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="C309" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D309" s="5" t="n">
-        <v>0.28</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="310" ht="18.75" customHeight="1">
       <c r="A310" s="3" t="inlineStr">
         <is>
-          <t>AL30</t>
+          <t>AL30C</t>
         </is>
       </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>2029-07-09</t>
+          <t>2028-01-09</t>
         </is>
       </c>
       <c r="C310" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D310" s="5" t="n">
-        <v>0.21</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="311" ht="18.75" customHeight="1">
       <c r="A311" s="3" t="inlineStr">
         <is>
-          <t>AL30</t>
+          <t>AL30C</t>
         </is>
       </c>
       <c r="B311" s="3" t="inlineStr">
         <is>
-          <t>2030-01-09</t>
+          <t>2028-07-09</t>
         </is>
       </c>
       <c r="C311" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D311" s="5" t="n">
-        <v>0.14</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="312" ht="18.75" customHeight="1">
       <c r="A312" s="3" t="inlineStr">
         <is>
-          <t>AL30</t>
+          <t>AL30C</t>
         </is>
       </c>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>2030-07-09</t>
+          <t>2029-01-09</t>
         </is>
       </c>
       <c r="C312" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D312" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="313" ht="18.75" customHeight="1">
@@ -9948,14 +10245,14 @@
       </c>
       <c r="B313" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2029-07-09</t>
         </is>
       </c>
       <c r="C313" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D313" s="5" t="n">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="314" ht="18.75" customHeight="1">
@@ -9966,14 +10263,14 @@
       </c>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2030-01-09</t>
         </is>
       </c>
       <c r="C314" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D314" s="5" t="n">
-        <v>0.24</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="315" ht="18.75" customHeight="1">
@@ -9984,122 +10281,122 @@
       </c>
       <c r="B315" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2030-07-09</t>
         </is>
       </c>
       <c r="C315" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D315" s="5" t="n">
-        <v>0.21</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="316" ht="18.75" customHeight="1">
       <c r="A316" s="3" t="inlineStr">
         <is>
-          <t>AL30C</t>
+          <t>AL35</t>
         </is>
       </c>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>2028-01-09</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C316" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D316" s="5" t="n">
-        <v>0.42</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="317" ht="18.75" customHeight="1">
       <c r="A317" s="3" t="inlineStr">
         <is>
-          <t>AL30C</t>
+          <t>AL35</t>
         </is>
       </c>
       <c r="B317" s="3" t="inlineStr">
         <is>
-          <t>2028-07-09</t>
+          <t>2027-01-09</t>
         </is>
       </c>
       <c r="C317" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D317" s="5" t="n">
-        <v>0.35</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="318" ht="18.75" customHeight="1">
       <c r="A318" s="3" t="inlineStr">
         <is>
-          <t>AL30C</t>
+          <t>AL35</t>
         </is>
       </c>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>2029-01-09</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="C318" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D318" s="5" t="n">
-        <v>0.28</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="319" ht="18.75" customHeight="1">
       <c r="A319" s="3" t="inlineStr">
         <is>
-          <t>AL30C</t>
+          <t>AL35</t>
         </is>
       </c>
       <c r="B319" s="3" t="inlineStr">
         <is>
-          <t>2029-07-09</t>
+          <t>2028-01-09</t>
         </is>
       </c>
       <c r="C319" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D319" s="5" t="n">
-        <v>0.21</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="320" ht="18.75" customHeight="1">
       <c r="A320" s="3" t="inlineStr">
         <is>
-          <t>AL30C</t>
+          <t>AL35</t>
         </is>
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>2030-01-09</t>
+          <t>2028-07-09</t>
         </is>
       </c>
       <c r="C320" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D320" s="5" t="n">
-        <v>0.14</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="321" ht="18.75" customHeight="1">
       <c r="A321" s="3" t="inlineStr">
         <is>
-          <t>AL30C</t>
+          <t>AL35</t>
         </is>
       </c>
       <c r="B321" s="3" t="inlineStr">
         <is>
-          <t>2030-07-09</t>
+          <t>2029-01-09</t>
         </is>
       </c>
       <c r="C321" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D321" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="322" ht="18.75" customHeight="1">
@@ -10110,14 +10407,14 @@
       </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2029-07-09</t>
         </is>
       </c>
       <c r="C322" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D322" s="5" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="323" ht="18.75" customHeight="1">
@@ -10128,14 +10425,14 @@
       </c>
       <c r="B323" s="3" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2030-01-09</t>
         </is>
       </c>
       <c r="C323" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D323" s="5" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="324" ht="18.75" customHeight="1">
@@ -10146,14 +10443,14 @@
       </c>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2030-07-09</t>
         </is>
       </c>
       <c r="C324" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D324" s="5" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="325" ht="18.75" customHeight="1">
@@ -10164,14 +10461,14 @@
       </c>
       <c r="B325" s="3" t="inlineStr">
         <is>
-          <t>2028-01-09</t>
+          <t>2031-01-09</t>
         </is>
       </c>
       <c r="C325" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D325" s="5" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="326" ht="18.75" customHeight="1">
@@ -10182,14 +10479,14 @@
       </c>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>2028-07-09</t>
+          <t>2031-07-09</t>
         </is>
       </c>
       <c r="C326" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D326" s="5" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="327" ht="18.75" customHeight="1">
@@ -10200,14 +10497,14 @@
       </c>
       <c r="B327" s="3" t="inlineStr">
         <is>
-          <t>2029-01-09</t>
+          <t>2032-01-09</t>
         </is>
       </c>
       <c r="C327" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D327" s="5" t="n">
-        <v>2.5</v>
+        <v>10</v>
+      </c>
+      <c r="D327" s="8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="328" ht="18.75" customHeight="1">
@@ -10218,14 +10515,14 @@
       </c>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>2029-07-09</t>
+          <t>2032-07-09</t>
         </is>
       </c>
       <c r="C328" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D328" s="5" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="329" ht="18.75" customHeight="1">
@@ -10236,14 +10533,14 @@
       </c>
       <c r="B329" s="3" t="inlineStr">
         <is>
-          <t>2030-01-09</t>
+          <t>2033-01-09</t>
         </is>
       </c>
       <c r="C329" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D329" s="5" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="330" ht="18.75" customHeight="1">
@@ -10254,14 +10551,14 @@
       </c>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>2030-07-09</t>
+          <t>2033-07-09</t>
         </is>
       </c>
       <c r="C330" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D330" s="5" t="n">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="331" ht="18.75" customHeight="1">
@@ -10272,14 +10569,14 @@
       </c>
       <c r="B331" s="3" t="inlineStr">
         <is>
-          <t>2031-01-09</t>
+          <t>2034-01-09</t>
         </is>
       </c>
       <c r="C331" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="D331" s="5" t="n">
-        <v>2.5</v>
+      <c r="D331" s="8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="332" ht="18.75" customHeight="1">
@@ -10290,14 +10587,14 @@
       </c>
       <c r="B332" s="3" t="inlineStr">
         <is>
-          <t>2031-07-09</t>
+          <t>2034-07-09</t>
         </is>
       </c>
       <c r="C332" s="8" t="n">
         <v>10</v>
       </c>
       <c r="D332" s="5" t="n">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="333" ht="18.75" customHeight="1">
@@ -10308,14 +10605,14 @@
       </c>
       <c r="B333" s="3" t="inlineStr">
         <is>
-          <t>2032-01-09</t>
+          <t>2035-01-09</t>
         </is>
       </c>
       <c r="C333" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="D333" s="8" t="n">
-        <v>2</v>
+      <c r="D333" s="5" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="334" ht="18.75" customHeight="1">
@@ -10326,122 +10623,122 @@
       </c>
       <c r="B334" s="3" t="inlineStr">
         <is>
-          <t>2032-07-09</t>
+          <t>2035-07-09</t>
         </is>
       </c>
       <c r="C334" s="8" t="n">
         <v>10</v>
       </c>
       <c r="D334" s="5" t="n">
-        <v>1.75</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="335" ht="18.75" customHeight="1">
       <c r="A335" s="3" t="inlineStr">
         <is>
-          <t>AL35</t>
+          <t>AL41</t>
         </is>
       </c>
       <c r="B335" s="3" t="inlineStr">
         <is>
-          <t>2033-01-09</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C335" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D335" s="5" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="336" ht="18.75" customHeight="1">
       <c r="A336" s="3" t="inlineStr">
         <is>
-          <t>AL35</t>
+          <t>AL41</t>
         </is>
       </c>
       <c r="B336" s="3" t="inlineStr">
         <is>
-          <t>2033-07-09</t>
+          <t>2027-01-09</t>
         </is>
       </c>
       <c r="C336" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D336" s="5" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="337" ht="18.75" customHeight="1">
       <c r="A337" s="3" t="inlineStr">
         <is>
-          <t>AL35</t>
+          <t>AL41</t>
         </is>
       </c>
       <c r="B337" s="3" t="inlineStr">
         <is>
-          <t>2034-01-09</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="C337" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="D337" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="D337" s="5" t="n">
+        <v>1.75</v>
       </c>
     </row>
     <row r="338" ht="18.75" customHeight="1">
       <c r="A338" s="3" t="inlineStr">
         <is>
-          <t>AL35</t>
+          <t>AL41</t>
         </is>
       </c>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>2034-07-09</t>
-        </is>
-      </c>
-      <c r="C338" s="8" t="n">
-        <v>10</v>
+          <t>2028-01-09</t>
+        </is>
+      </c>
+      <c r="C338" s="5" t="n">
+        <v>3.57</v>
       </c>
       <c r="D338" s="5" t="n">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="339" ht="18.75" customHeight="1">
       <c r="A339" s="3" t="inlineStr">
         <is>
-          <t>AL35</t>
+          <t>AL41</t>
         </is>
       </c>
       <c r="B339" s="3" t="inlineStr">
         <is>
-          <t>2035-01-09</t>
-        </is>
-      </c>
-      <c r="C339" s="8" t="n">
-        <v>10</v>
+          <t>2028-07-09</t>
+        </is>
+      </c>
+      <c r="C339" s="5" t="n">
+        <v>3.57</v>
       </c>
       <c r="D339" s="5" t="n">
-        <v>0.5</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="340" ht="18.75" customHeight="1">
       <c r="A340" s="3" t="inlineStr">
         <is>
-          <t>AL35</t>
+          <t>AL41</t>
         </is>
       </c>
       <c r="B340" s="3" t="inlineStr">
         <is>
-          <t>2035-07-09</t>
-        </is>
-      </c>
-      <c r="C340" s="8" t="n">
-        <v>10</v>
+          <t>2029-01-09</t>
+        </is>
+      </c>
+      <c r="C340" s="5" t="n">
+        <v>3.57</v>
       </c>
       <c r="D340" s="5" t="n">
-        <v>0.25</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="341" ht="18.75" customHeight="1">
@@ -10452,14 +10749,14 @@
       </c>
       <c r="B341" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="C341" s="8" t="n">
-        <v>0</v>
+          <t>2029-07-09</t>
+        </is>
+      </c>
+      <c r="C341" s="5" t="n">
+        <v>3.57</v>
       </c>
       <c r="D341" s="5" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="342" ht="18.75" customHeight="1">
@@ -10470,14 +10767,14 @@
       </c>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
-        </is>
-      </c>
-      <c r="C342" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D342" s="5" t="n">
-        <v>1.75</v>
+          <t>2030-01-09</t>
+        </is>
+      </c>
+      <c r="C342" s="5" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="D342" s="8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="343" ht="18.75" customHeight="1">
@@ -10488,14 +10785,14 @@
       </c>
       <c r="B343" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
-        </is>
-      </c>
-      <c r="C343" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D343" s="5" t="n">
-        <v>1.75</v>
+          <t>2030-07-09</t>
+        </is>
+      </c>
+      <c r="C343" s="5" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="D343" s="8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="344" ht="18.75" customHeight="1">
@@ -10506,14 +10803,14 @@
       </c>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>2028-01-09</t>
+          <t>2031-01-09</t>
         </is>
       </c>
       <c r="C344" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D344" s="5" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="345" ht="18.75" customHeight="1">
@@ -10524,14 +10821,14 @@
       </c>
       <c r="B345" s="3" t="inlineStr">
         <is>
-          <t>2028-07-09</t>
+          <t>2031-07-09</t>
         </is>
       </c>
       <c r="C345" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D345" s="5" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="346" ht="18.75" customHeight="1">
@@ -10542,14 +10839,14 @@
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>2029-01-09</t>
+          <t>2032-01-09</t>
         </is>
       </c>
       <c r="C346" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D346" s="5" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="347" ht="18.75" customHeight="1">
@@ -10560,14 +10857,14 @@
       </c>
       <c r="B347" s="3" t="inlineStr">
         <is>
-          <t>2029-07-09</t>
+          <t>2032-07-09</t>
         </is>
       </c>
       <c r="C347" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D347" s="5" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="348" ht="18.75" customHeight="1">
@@ -10578,14 +10875,14 @@
       </c>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>2030-01-09</t>
+          <t>2033-01-09</t>
         </is>
       </c>
       <c r="C348" s="5" t="n">
         <v>3.57</v>
       </c>
-      <c r="D348" s="8" t="n">
-        <v>2</v>
+      <c r="D348" s="5" t="n">
+        <v>1.57</v>
       </c>
     </row>
     <row r="349" ht="18.75" customHeight="1">
@@ -10596,14 +10893,14 @@
       </c>
       <c r="B349" s="3" t="inlineStr">
         <is>
-          <t>2030-07-09</t>
+          <t>2033-07-09</t>
         </is>
       </c>
       <c r="C349" s="5" t="n">
         <v>3.57</v>
       </c>
-      <c r="D349" s="8" t="n">
-        <v>2</v>
+      <c r="D349" s="5" t="n">
+        <v>1.48</v>
       </c>
     </row>
     <row r="350" ht="18.75" customHeight="1">
@@ -10614,14 +10911,14 @@
       </c>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>2031-01-09</t>
+          <t>2034-01-09</t>
         </is>
       </c>
       <c r="C350" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D350" s="5" t="n">
-        <v>1.92</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="351" ht="18.75" customHeight="1">
@@ -10632,14 +10929,14 @@
       </c>
       <c r="B351" s="3" t="inlineStr">
         <is>
-          <t>2031-07-09</t>
+          <t>2034-07-09</t>
         </is>
       </c>
       <c r="C351" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D351" s="5" t="n">
-        <v>1.83</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="352" ht="18.75" customHeight="1">
@@ -10650,14 +10947,14 @@
       </c>
       <c r="B352" s="3" t="inlineStr">
         <is>
-          <t>2032-01-09</t>
+          <t>2035-01-09</t>
         </is>
       </c>
       <c r="C352" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D352" s="5" t="n">
-        <v>1.74</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="353" ht="18.75" customHeight="1">
@@ -10668,14 +10965,14 @@
       </c>
       <c r="B353" s="3" t="inlineStr">
         <is>
-          <t>2032-07-09</t>
+          <t>2035-07-09</t>
         </is>
       </c>
       <c r="C353" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D353" s="5" t="n">
-        <v>1.65</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="354" ht="18.75" customHeight="1">
@@ -10686,14 +10983,14 @@
       </c>
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>2033-01-09</t>
+          <t>2036-01-09</t>
         </is>
       </c>
       <c r="C354" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D354" s="5" t="n">
-        <v>1.57</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="355" ht="18.75" customHeight="1">
@@ -10704,14 +11001,14 @@
       </c>
       <c r="B355" s="3" t="inlineStr">
         <is>
-          <t>2033-07-09</t>
+          <t>2036-07-09</t>
         </is>
       </c>
       <c r="C355" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D355" s="5" t="n">
-        <v>1.48</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="356" ht="18.75" customHeight="1">
@@ -10722,14 +11019,14 @@
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>2034-01-09</t>
+          <t>2037-01-09</t>
         </is>
       </c>
       <c r="C356" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D356" s="5" t="n">
-        <v>1.39</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="357" ht="18.75" customHeight="1">
@@ -10740,14 +11037,14 @@
       </c>
       <c r="B357" s="3" t="inlineStr">
         <is>
-          <t>2034-07-09</t>
+          <t>2037-07-09</t>
         </is>
       </c>
       <c r="C357" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D357" s="5" t="n">
-        <v>1.31</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="358" ht="18.75" customHeight="1">
@@ -10758,14 +11055,14 @@
       </c>
       <c r="B358" s="3" t="inlineStr">
         <is>
-          <t>2035-01-09</t>
+          <t>2038-01-09</t>
         </is>
       </c>
       <c r="C358" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D358" s="5" t="n">
-        <v>1.22</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="359" ht="18.75" customHeight="1">
@@ -10776,14 +11073,14 @@
       </c>
       <c r="B359" s="3" t="inlineStr">
         <is>
-          <t>2035-07-09</t>
+          <t>2038-07-09</t>
         </is>
       </c>
       <c r="C359" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D359" s="5" t="n">
-        <v>1.13</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="360" ht="18.75" customHeight="1">
@@ -10794,14 +11091,14 @@
       </c>
       <c r="B360" s="3" t="inlineStr">
         <is>
-          <t>2036-01-09</t>
+          <t>2039-01-09</t>
         </is>
       </c>
       <c r="C360" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D360" s="5" t="n">
-        <v>1.05</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="361" ht="18.75" customHeight="1">
@@ -10812,14 +11109,14 @@
       </c>
       <c r="B361" s="3" t="inlineStr">
         <is>
-          <t>2036-07-09</t>
+          <t>2039-07-09</t>
         </is>
       </c>
       <c r="C361" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D361" s="5" t="n">
-        <v>0.96</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="362" ht="18.75" customHeight="1">
@@ -10830,14 +11127,14 @@
       </c>
       <c r="B362" s="3" t="inlineStr">
         <is>
-          <t>2037-01-09</t>
+          <t>2040-01-09</t>
         </is>
       </c>
       <c r="C362" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D362" s="5" t="n">
-        <v>0.87</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="363" ht="18.75" customHeight="1">
@@ -10848,14 +11145,14 @@
       </c>
       <c r="B363" s="3" t="inlineStr">
         <is>
-          <t>2037-07-09</t>
+          <t>2040-07-09</t>
         </is>
       </c>
       <c r="C363" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D363" s="5" t="n">
-        <v>0.78</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="364" ht="18.75" customHeight="1">
@@ -10866,14 +11163,14 @@
       </c>
       <c r="B364" s="3" t="inlineStr">
         <is>
-          <t>2038-01-09</t>
+          <t>2041-01-09</t>
         </is>
       </c>
       <c r="C364" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D364" s="5" t="n">
-        <v>0.7</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="365" ht="18.75" customHeight="1">
@@ -10884,122 +11181,122 @@
       </c>
       <c r="B365" s="3" t="inlineStr">
         <is>
-          <t>2038-07-09</t>
+          <t>2041-07-09</t>
         </is>
       </c>
       <c r="C365" s="5" t="n">
-        <v>3.57</v>
+        <v>3.61</v>
       </c>
       <c r="D365" s="5" t="n">
-        <v>0.61</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="366" ht="18.75" customHeight="1">
       <c r="A366" s="3" t="inlineStr">
         <is>
-          <t>AL41</t>
+          <t>GD29</t>
         </is>
       </c>
       <c r="B366" s="3" t="inlineStr">
         <is>
-          <t>2039-01-09</t>
-        </is>
-      </c>
-      <c r="C366" s="5" t="n">
-        <v>3.57</v>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C366" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="D366" s="5" t="n">
-        <v>0.52</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="367" ht="18.75" customHeight="1">
       <c r="A367" s="3" t="inlineStr">
         <is>
-          <t>AL41</t>
+          <t>GD29</t>
         </is>
       </c>
       <c r="B367" s="3" t="inlineStr">
         <is>
-          <t>2039-07-09</t>
-        </is>
-      </c>
-      <c r="C367" s="5" t="n">
-        <v>3.57</v>
+          <t>2027-01-09</t>
+        </is>
+      </c>
+      <c r="C367" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="D367" s="5" t="n">
-        <v>0.44</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="368" ht="18.75" customHeight="1">
       <c r="A368" s="3" t="inlineStr">
         <is>
-          <t>AL41</t>
+          <t>GD29</t>
         </is>
       </c>
       <c r="B368" s="3" t="inlineStr">
         <is>
-          <t>2040-01-09</t>
-        </is>
-      </c>
-      <c r="C368" s="5" t="n">
-        <v>3.57</v>
+          <t>2027-07-09</t>
+        </is>
+      </c>
+      <c r="C368" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="D368" s="5" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="369" ht="18.75" customHeight="1">
       <c r="A369" s="3" t="inlineStr">
         <is>
-          <t>AL41</t>
+          <t>GD29</t>
         </is>
       </c>
       <c r="B369" s="3" t="inlineStr">
         <is>
-          <t>2040-07-09</t>
-        </is>
-      </c>
-      <c r="C369" s="5" t="n">
-        <v>3.57</v>
+          <t>2028-01-09</t>
+        </is>
+      </c>
+      <c r="C369" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="D369" s="5" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="370" ht="18.75" customHeight="1">
       <c r="A370" s="3" t="inlineStr">
         <is>
-          <t>AL41</t>
+          <t>GD29</t>
         </is>
       </c>
       <c r="B370" s="3" t="inlineStr">
         <is>
-          <t>2041-01-09</t>
-        </is>
-      </c>
-      <c r="C370" s="5" t="n">
-        <v>3.57</v>
+          <t>2028-07-09</t>
+        </is>
+      </c>
+      <c r="C370" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="D370" s="5" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="371" ht="18.75" customHeight="1">
       <c r="A371" s="3" t="inlineStr">
         <is>
-          <t>AL41</t>
+          <t>GD29</t>
         </is>
       </c>
       <c r="B371" s="3" t="inlineStr">
         <is>
-          <t>2041-07-09</t>
-        </is>
-      </c>
-      <c r="C371" s="5" t="n">
-        <v>3.61</v>
+          <t>2029-01-09</t>
+        </is>
+      </c>
+      <c r="C371" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="D371" s="5" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="372" ht="18.75" customHeight="1">
@@ -11010,122 +11307,122 @@
       </c>
       <c r="B372" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2029-07-09</t>
         </is>
       </c>
       <c r="C372" s="8" t="n">
         <v>10</v>
       </c>
       <c r="D372" s="5" t="n">
-        <v>0.35</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="373" ht="18.75" customHeight="1">
       <c r="A373" s="3" t="inlineStr">
         <is>
-          <t>GD29</t>
+          <t>GD30</t>
         </is>
       </c>
       <c r="B373" s="3" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C373" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D373" s="5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="374" ht="18.75" customHeight="1">
       <c r="A374" s="3" t="inlineStr">
         <is>
-          <t>GD29</t>
+          <t>GD30</t>
         </is>
       </c>
       <c r="B374" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2027-01-09</t>
         </is>
       </c>
       <c r="C374" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D374" s="5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="375" ht="18.75" customHeight="1">
       <c r="A375" s="3" t="inlineStr">
         <is>
-          <t>GD29</t>
+          <t>GD30</t>
         </is>
       </c>
       <c r="B375" s="3" t="inlineStr">
         <is>
-          <t>2028-01-09</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="C375" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D375" s="5" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="376" ht="18.75" customHeight="1">
       <c r="A376" s="3" t="inlineStr">
         <is>
-          <t>GD29</t>
+          <t>GD30</t>
         </is>
       </c>
       <c r="B376" s="3" t="inlineStr">
         <is>
-          <t>2028-07-09</t>
+          <t>2028-01-09</t>
         </is>
       </c>
       <c r="C376" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D376" s="5" t="n">
-        <v>0.15</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="377" ht="18.75" customHeight="1">
       <c r="A377" s="3" t="inlineStr">
         <is>
-          <t>GD29</t>
+          <t>GD30</t>
         </is>
       </c>
       <c r="B377" s="3" t="inlineStr">
         <is>
-          <t>2029-01-09</t>
+          <t>2028-07-09</t>
         </is>
       </c>
       <c r="C377" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D377" s="5" t="n">
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="378" ht="18.75" customHeight="1">
       <c r="A378" s="3" t="inlineStr">
         <is>
-          <t>GD29</t>
+          <t>GD30</t>
         </is>
       </c>
       <c r="B378" s="3" t="inlineStr">
         <is>
-          <t>2029-07-09</t>
+          <t>2029-01-09</t>
         </is>
       </c>
       <c r="C378" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D378" s="5" t="n">
-        <v>0.05</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="379" ht="18.75" customHeight="1">
@@ -11136,14 +11433,14 @@
       </c>
       <c r="B379" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2029-07-09</t>
         </is>
       </c>
       <c r="C379" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D379" s="5" t="n">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="380" ht="18.75" customHeight="1">
@@ -11154,14 +11451,14 @@
       </c>
       <c r="B380" s="3" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2030-01-09</t>
         </is>
       </c>
       <c r="C380" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D380" s="5" t="n">
-        <v>0.24</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="381" ht="18.75" customHeight="1">
@@ -11172,122 +11469,122 @@
       </c>
       <c r="B381" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2030-07-09</t>
         </is>
       </c>
       <c r="C381" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D381" s="5" t="n">
-        <v>0.21</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="382" ht="18.75" customHeight="1">
       <c r="A382" s="3" t="inlineStr">
         <is>
-          <t>GD30</t>
+          <t>GD30C</t>
         </is>
       </c>
       <c r="B382" s="3" t="inlineStr">
         <is>
-          <t>2028-01-09</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C382" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D382" s="5" t="n">
-        <v>0.42</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="383" ht="18.75" customHeight="1">
       <c r="A383" s="3" t="inlineStr">
         <is>
-          <t>GD30</t>
+          <t>GD30C</t>
         </is>
       </c>
       <c r="B383" s="3" t="inlineStr">
         <is>
-          <t>2028-07-09</t>
+          <t>2027-01-09</t>
         </is>
       </c>
       <c r="C383" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D383" s="5" t="n">
-        <v>0.35</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="384" ht="18.75" customHeight="1">
       <c r="A384" s="3" t="inlineStr">
         <is>
-          <t>GD30</t>
+          <t>GD30C</t>
         </is>
       </c>
       <c r="B384" s="3" t="inlineStr">
         <is>
-          <t>2029-01-09</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="C384" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D384" s="5" t="n">
-        <v>0.28</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="385" ht="18.75" customHeight="1">
       <c r="A385" s="3" t="inlineStr">
         <is>
-          <t>GD30</t>
+          <t>GD30C</t>
         </is>
       </c>
       <c r="B385" s="3" t="inlineStr">
         <is>
-          <t>2029-07-09</t>
+          <t>2028-01-09</t>
         </is>
       </c>
       <c r="C385" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D385" s="5" t="n">
-        <v>0.21</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="386" ht="18.75" customHeight="1">
       <c r="A386" s="3" t="inlineStr">
         <is>
-          <t>GD30</t>
+          <t>GD30C</t>
         </is>
       </c>
       <c r="B386" s="3" t="inlineStr">
         <is>
-          <t>2030-01-09</t>
+          <t>2028-07-09</t>
         </is>
       </c>
       <c r="C386" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D386" s="5" t="n">
-        <v>0.14</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="387" ht="18.75" customHeight="1">
       <c r="A387" s="3" t="inlineStr">
         <is>
-          <t>GD30</t>
+          <t>GD30C</t>
         </is>
       </c>
       <c r="B387" s="3" t="inlineStr">
         <is>
-          <t>2030-07-09</t>
+          <t>2029-01-09</t>
         </is>
       </c>
       <c r="C387" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D387" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="388" ht="18.75" customHeight="1">
@@ -11298,14 +11595,14 @@
       </c>
       <c r="B388" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2029-07-09</t>
         </is>
       </c>
       <c r="C388" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D388" s="5" t="n">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="389" ht="18.75" customHeight="1">
@@ -11316,14 +11613,14 @@
       </c>
       <c r="B389" s="3" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2030-01-09</t>
         </is>
       </c>
       <c r="C389" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D389" s="5" t="n">
-        <v>0.24</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="390" ht="18.75" customHeight="1">
@@ -11334,122 +11631,122 @@
       </c>
       <c r="B390" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2030-07-09</t>
         </is>
       </c>
       <c r="C390" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D390" s="5" t="n">
-        <v>0.21</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="391" ht="18.75" customHeight="1">
       <c r="A391" s="3" t="inlineStr">
         <is>
-          <t>GD30C</t>
+          <t>GD35</t>
         </is>
       </c>
       <c r="B391" s="3" t="inlineStr">
         <is>
-          <t>2028-01-09</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C391" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D391" s="5" t="n">
-        <v>0.42</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="392" ht="18.75" customHeight="1">
       <c r="A392" s="3" t="inlineStr">
         <is>
-          <t>GD30C</t>
+          <t>GD35</t>
         </is>
       </c>
       <c r="B392" s="3" t="inlineStr">
         <is>
-          <t>2028-07-09</t>
+          <t>2027-01-09</t>
         </is>
       </c>
       <c r="C392" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D392" s="5" t="n">
-        <v>0.35</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="393" ht="18.75" customHeight="1">
       <c r="A393" s="3" t="inlineStr">
         <is>
-          <t>GD30C</t>
+          <t>GD35</t>
         </is>
       </c>
       <c r="B393" s="3" t="inlineStr">
         <is>
-          <t>2029-01-09</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="C393" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D393" s="5" t="n">
-        <v>0.28</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="394" ht="18.75" customHeight="1">
       <c r="A394" s="3" t="inlineStr">
         <is>
-          <t>GD30C</t>
+          <t>GD35</t>
         </is>
       </c>
       <c r="B394" s="3" t="inlineStr">
         <is>
-          <t>2029-07-09</t>
+          <t>2028-01-09</t>
         </is>
       </c>
       <c r="C394" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D394" s="5" t="n">
-        <v>0.21</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="395" ht="18.75" customHeight="1">
       <c r="A395" s="3" t="inlineStr">
         <is>
-          <t>GD30C</t>
+          <t>GD35</t>
         </is>
       </c>
       <c r="B395" s="3" t="inlineStr">
         <is>
-          <t>2030-01-09</t>
+          <t>2028-07-09</t>
         </is>
       </c>
       <c r="C395" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D395" s="5" t="n">
-        <v>0.14</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="396" ht="18.75" customHeight="1">
       <c r="A396" s="3" t="inlineStr">
         <is>
-          <t>GD30C</t>
+          <t>GD35</t>
         </is>
       </c>
       <c r="B396" s="3" t="inlineStr">
         <is>
-          <t>2030-07-09</t>
+          <t>2029-01-09</t>
         </is>
       </c>
       <c r="C396" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D396" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="397" ht="18.75" customHeight="1">
@@ -11460,14 +11757,14 @@
       </c>
       <c r="B397" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2029-07-09</t>
         </is>
       </c>
       <c r="C397" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D397" s="5" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="398" ht="18.75" customHeight="1">
@@ -11478,14 +11775,14 @@
       </c>
       <c r="B398" s="3" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2030-01-09</t>
         </is>
       </c>
       <c r="C398" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D398" s="5" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="399" ht="18.75" customHeight="1">
@@ -11496,14 +11793,14 @@
       </c>
       <c r="B399" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2030-07-09</t>
         </is>
       </c>
       <c r="C399" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D399" s="5" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="400" ht="18.75" customHeight="1">
@@ -11514,14 +11811,14 @@
       </c>
       <c r="B400" s="3" t="inlineStr">
         <is>
-          <t>2028-01-09</t>
+          <t>2031-01-09</t>
         </is>
       </c>
       <c r="C400" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D400" s="5" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="401" ht="18.75" customHeight="1">
@@ -11532,14 +11829,14 @@
       </c>
       <c r="B401" s="3" t="inlineStr">
         <is>
-          <t>2028-07-09</t>
+          <t>2031-07-09</t>
         </is>
       </c>
       <c r="C401" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D401" s="5" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="402" ht="18.75" customHeight="1">
@@ -11550,14 +11847,14 @@
       </c>
       <c r="B402" s="3" t="inlineStr">
         <is>
-          <t>2029-01-09</t>
+          <t>2032-01-09</t>
         </is>
       </c>
       <c r="C402" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D402" s="5" t="n">
-        <v>2.5</v>
+        <v>10</v>
+      </c>
+      <c r="D402" s="8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="403" ht="18.75" customHeight="1">
@@ -11568,14 +11865,14 @@
       </c>
       <c r="B403" s="3" t="inlineStr">
         <is>
-          <t>2029-07-09</t>
+          <t>2032-07-09</t>
         </is>
       </c>
       <c r="C403" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D403" s="5" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="404" ht="18.75" customHeight="1">
@@ -11586,14 +11883,14 @@
       </c>
       <c r="B404" s="3" t="inlineStr">
         <is>
-          <t>2030-01-09</t>
+          <t>2033-01-09</t>
         </is>
       </c>
       <c r="C404" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D404" s="5" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="405" ht="18.75" customHeight="1">
@@ -11604,14 +11901,14 @@
       </c>
       <c r="B405" s="3" t="inlineStr">
         <is>
-          <t>2030-07-09</t>
+          <t>2033-07-09</t>
         </is>
       </c>
       <c r="C405" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D405" s="5" t="n">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="406" ht="18.75" customHeight="1">
@@ -11622,14 +11919,14 @@
       </c>
       <c r="B406" s="3" t="inlineStr">
         <is>
-          <t>2031-01-09</t>
+          <t>2034-01-09</t>
         </is>
       </c>
       <c r="C406" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="D406" s="5" t="n">
-        <v>2.5</v>
+      <c r="D406" s="8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="407" ht="18.75" customHeight="1">
@@ -11640,14 +11937,14 @@
       </c>
       <c r="B407" s="3" t="inlineStr">
         <is>
-          <t>2031-07-09</t>
+          <t>2034-07-09</t>
         </is>
       </c>
       <c r="C407" s="8" t="n">
         <v>10</v>
       </c>
       <c r="D407" s="5" t="n">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="408" ht="18.75" customHeight="1">
@@ -11658,14 +11955,14 @@
       </c>
       <c r="B408" s="3" t="inlineStr">
         <is>
-          <t>2032-01-09</t>
+          <t>2035-01-09</t>
         </is>
       </c>
       <c r="C408" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="D408" s="8" t="n">
-        <v>2</v>
+      <c r="D408" s="5" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="409" ht="18.75" customHeight="1">
@@ -11676,122 +11973,122 @@
       </c>
       <c r="B409" s="3" t="inlineStr">
         <is>
-          <t>2032-07-09</t>
+          <t>2035-07-09</t>
         </is>
       </c>
       <c r="C409" s="8" t="n">
         <v>10</v>
       </c>
       <c r="D409" s="5" t="n">
-        <v>1.75</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="410" ht="18.75" customHeight="1">
       <c r="A410" s="3" t="inlineStr">
         <is>
-          <t>GD35</t>
+          <t>GD38</t>
         </is>
       </c>
       <c r="B410" s="3" t="inlineStr">
         <is>
-          <t>2033-01-09</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C410" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D410" s="5" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="411" ht="18.75" customHeight="1">
       <c r="A411" s="3" t="inlineStr">
         <is>
-          <t>GD35</t>
+          <t>GD38</t>
         </is>
       </c>
       <c r="B411" s="3" t="inlineStr">
         <is>
-          <t>2033-07-09</t>
+          <t>2027-01-09</t>
         </is>
       </c>
       <c r="C411" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D411" s="5" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="412" ht="18.75" customHeight="1">
       <c r="A412" s="3" t="inlineStr">
         <is>
-          <t>GD35</t>
+          <t>GD38</t>
         </is>
       </c>
       <c r="B412" s="3" t="inlineStr">
         <is>
-          <t>2034-01-09</t>
-        </is>
-      </c>
-      <c r="C412" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="D412" s="8" t="n">
-        <v>1</v>
+          <t>2027-07-09</t>
+        </is>
+      </c>
+      <c r="C412" s="5" t="n">
+        <v>4.5454</v>
+      </c>
+      <c r="D412" s="5" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="413" ht="18.75" customHeight="1">
       <c r="A413" s="3" t="inlineStr">
         <is>
-          <t>GD35</t>
+          <t>GD38</t>
         </is>
       </c>
       <c r="B413" s="3" t="inlineStr">
         <is>
-          <t>2034-07-09</t>
-        </is>
-      </c>
-      <c r="C413" s="8" t="n">
-        <v>10</v>
+          <t>2028-01-09</t>
+        </is>
+      </c>
+      <c r="C413" s="5" t="n">
+        <v>4.5454</v>
       </c>
       <c r="D413" s="5" t="n">
-        <v>0.75</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="414" ht="18.75" customHeight="1">
       <c r="A414" s="3" t="inlineStr">
         <is>
-          <t>GD35</t>
+          <t>GD38</t>
         </is>
       </c>
       <c r="B414" s="3" t="inlineStr">
         <is>
-          <t>2035-01-09</t>
-        </is>
-      </c>
-      <c r="C414" s="8" t="n">
-        <v>10</v>
+          <t>2028-07-09</t>
+        </is>
+      </c>
+      <c r="C414" s="5" t="n">
+        <v>4.5454</v>
       </c>
       <c r="D414" s="5" t="n">
-        <v>0.5</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="415" ht="18.75" customHeight="1">
       <c r="A415" s="3" t="inlineStr">
         <is>
-          <t>GD35</t>
+          <t>GD38</t>
         </is>
       </c>
       <c r="B415" s="3" t="inlineStr">
         <is>
-          <t>2035-07-09</t>
-        </is>
-      </c>
-      <c r="C415" s="8" t="n">
-        <v>10</v>
+          <t>2029-01-09</t>
+        </is>
+      </c>
+      <c r="C415" s="5" t="n">
+        <v>4.5454</v>
       </c>
       <c r="D415" s="5" t="n">
-        <v>0.25</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="416" ht="18.75" customHeight="1">
@@ -11802,14 +12099,14 @@
       </c>
       <c r="B416" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="C416" s="8" t="n">
-        <v>0</v>
+          <t>2029-07-09</t>
+        </is>
+      </c>
+      <c r="C416" s="5" t="n">
+        <v>4.5454</v>
       </c>
       <c r="D416" s="5" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="417" ht="18.75" customHeight="1">
@@ -11820,14 +12117,14 @@
       </c>
       <c r="B417" s="3" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
-        </is>
-      </c>
-      <c r="C417" s="8" t="n">
-        <v>0</v>
+          <t>2030-01-09</t>
+        </is>
+      </c>
+      <c r="C417" s="5" t="n">
+        <v>4.5454</v>
       </c>
       <c r="D417" s="5" t="n">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="418" ht="18.75" customHeight="1">
@@ -11838,14 +12135,14 @@
       </c>
       <c r="B418" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2030-07-09</t>
         </is>
       </c>
       <c r="C418" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D418" s="5" t="n">
-        <v>2.5</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="419" ht="18.75" customHeight="1">
@@ -11856,14 +12153,14 @@
       </c>
       <c r="B419" s="3" t="inlineStr">
         <is>
-          <t>2028-01-09</t>
+          <t>2031-01-09</t>
         </is>
       </c>
       <c r="C419" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D419" s="5" t="n">
-        <v>2.39</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="420" ht="18.75" customHeight="1">
@@ -11874,14 +12171,14 @@
       </c>
       <c r="B420" s="3" t="inlineStr">
         <is>
-          <t>2028-07-09</t>
+          <t>2031-07-09</t>
         </is>
       </c>
       <c r="C420" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D420" s="5" t="n">
-        <v>2.27</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="421" ht="18.75" customHeight="1">
@@ -11892,14 +12189,14 @@
       </c>
       <c r="B421" s="3" t="inlineStr">
         <is>
-          <t>2029-01-09</t>
+          <t>2032-01-09</t>
         </is>
       </c>
       <c r="C421" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D421" s="5" t="n">
-        <v>2.16</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="422" ht="18.75" customHeight="1">
@@ -11910,14 +12207,14 @@
       </c>
       <c r="B422" s="3" t="inlineStr">
         <is>
-          <t>2029-07-09</t>
+          <t>2032-07-09</t>
         </is>
       </c>
       <c r="C422" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D422" s="5" t="n">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="423" ht="18.75" customHeight="1">
@@ -11928,14 +12225,14 @@
       </c>
       <c r="B423" s="3" t="inlineStr">
         <is>
-          <t>2030-01-09</t>
+          <t>2033-01-09</t>
         </is>
       </c>
       <c r="C423" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D423" s="5" t="n">
-        <v>1.93</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="424" ht="18.75" customHeight="1">
@@ -11946,14 +12243,14 @@
       </c>
       <c r="B424" s="3" t="inlineStr">
         <is>
-          <t>2030-07-09</t>
+          <t>2033-07-09</t>
         </is>
       </c>
       <c r="C424" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D424" s="5" t="n">
-        <v>1.82</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="425" ht="18.75" customHeight="1">
@@ -11964,14 +12261,14 @@
       </c>
       <c r="B425" s="3" t="inlineStr">
         <is>
-          <t>2031-01-09</t>
+          <t>2034-01-09</t>
         </is>
       </c>
       <c r="C425" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D425" s="5" t="n">
-        <v>1.7</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="426" ht="18.75" customHeight="1">
@@ -11982,14 +12279,14 @@
       </c>
       <c r="B426" s="3" t="inlineStr">
         <is>
-          <t>2031-07-09</t>
+          <t>2034-07-09</t>
         </is>
       </c>
       <c r="C426" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D426" s="5" t="n">
-        <v>1.59</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="427" ht="18.75" customHeight="1">
@@ -12000,14 +12297,14 @@
       </c>
       <c r="B427" s="3" t="inlineStr">
         <is>
-          <t>2032-01-09</t>
+          <t>2035-01-09</t>
         </is>
       </c>
       <c r="C427" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D427" s="5" t="n">
-        <v>1.48</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="428" ht="18.75" customHeight="1">
@@ -12018,14 +12315,14 @@
       </c>
       <c r="B428" s="3" t="inlineStr">
         <is>
-          <t>2032-07-09</t>
+          <t>2035-07-09</t>
         </is>
       </c>
       <c r="C428" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D428" s="5" t="n">
-        <v>1.36</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="429" ht="18.75" customHeight="1">
@@ -12036,14 +12333,14 @@
       </c>
       <c r="B429" s="3" t="inlineStr">
         <is>
-          <t>2033-01-09</t>
+          <t>2036-01-09</t>
         </is>
       </c>
       <c r="C429" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D429" s="5" t="n">
-        <v>1.25</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="430" ht="18.75" customHeight="1">
@@ -12054,14 +12351,14 @@
       </c>
       <c r="B430" s="3" t="inlineStr">
         <is>
-          <t>2033-07-09</t>
+          <t>2036-07-09</t>
         </is>
       </c>
       <c r="C430" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D430" s="5" t="n">
-        <v>1.14</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="431" ht="18.75" customHeight="1">
@@ -12072,14 +12369,14 @@
       </c>
       <c r="B431" s="3" t="inlineStr">
         <is>
-          <t>2034-01-09</t>
+          <t>2037-01-09</t>
         </is>
       </c>
       <c r="C431" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D431" s="5" t="n">
-        <v>1.02</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="432" ht="18.75" customHeight="1">
@@ -12090,14 +12387,14 @@
       </c>
       <c r="B432" s="3" t="inlineStr">
         <is>
-          <t>2034-07-09</t>
+          <t>2037-07-09</t>
         </is>
       </c>
       <c r="C432" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D432" s="5" t="n">
-        <v>0.91</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="433" ht="18.75" customHeight="1">
@@ -12108,122 +12405,122 @@
       </c>
       <c r="B433" s="3" t="inlineStr">
         <is>
-          <t>2035-01-09</t>
+          <t>2038-01-09</t>
         </is>
       </c>
       <c r="C433" s="5" t="n">
         <v>4.5454</v>
       </c>
       <c r="D433" s="5" t="n">
-        <v>0.8</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="434" ht="18.75" customHeight="1">
       <c r="A434" s="3" t="inlineStr">
         <is>
-          <t>GD38</t>
+          <t>GD41</t>
         </is>
       </c>
       <c r="B434" s="3" t="inlineStr">
         <is>
-          <t>2035-07-09</t>
-        </is>
-      </c>
-      <c r="C434" s="5" t="n">
-        <v>4.5454</v>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C434" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="D434" s="5" t="n">
-        <v>0.68</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="435" ht="18.75" customHeight="1">
       <c r="A435" s="3" t="inlineStr">
         <is>
-          <t>GD38</t>
+          <t>GD41</t>
         </is>
       </c>
       <c r="B435" s="3" t="inlineStr">
         <is>
-          <t>2036-01-09</t>
-        </is>
-      </c>
-      <c r="C435" s="5" t="n">
-        <v>4.5454</v>
+          <t>2027-01-09</t>
+        </is>
+      </c>
+      <c r="C435" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="D435" s="5" t="n">
-        <v>0.57</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="436" ht="18.75" customHeight="1">
       <c r="A436" s="3" t="inlineStr">
         <is>
-          <t>GD38</t>
+          <t>GD41</t>
         </is>
       </c>
       <c r="B436" s="3" t="inlineStr">
         <is>
-          <t>2036-07-09</t>
-        </is>
-      </c>
-      <c r="C436" s="5" t="n">
-        <v>4.5454</v>
+          <t>2027-07-09</t>
+        </is>
+      </c>
+      <c r="C436" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="D436" s="5" t="n">
-        <v>0.45</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="437" ht="18.75" customHeight="1">
       <c r="A437" s="3" t="inlineStr">
         <is>
-          <t>GD38</t>
+          <t>GD41</t>
         </is>
       </c>
       <c r="B437" s="3" t="inlineStr">
         <is>
-          <t>2037-01-09</t>
+          <t>2028-01-09</t>
         </is>
       </c>
       <c r="C437" s="5" t="n">
-        <v>4.5454</v>
+        <v>3.57</v>
       </c>
       <c r="D437" s="5" t="n">
-        <v>0.34</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="438" ht="18.75" customHeight="1">
       <c r="A438" s="3" t="inlineStr">
         <is>
-          <t>GD38</t>
+          <t>GD41</t>
         </is>
       </c>
       <c r="B438" s="3" t="inlineStr">
         <is>
-          <t>2037-07-09</t>
+          <t>2028-07-09</t>
         </is>
       </c>
       <c r="C438" s="5" t="n">
-        <v>4.5454</v>
+        <v>3.57</v>
       </c>
       <c r="D438" s="5" t="n">
-        <v>0.23</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="439" ht="18.75" customHeight="1">
       <c r="A439" s="3" t="inlineStr">
         <is>
-          <t>GD38</t>
+          <t>GD41</t>
         </is>
       </c>
       <c r="B439" s="3" t="inlineStr">
         <is>
-          <t>2038-01-09</t>
+          <t>2029-01-09</t>
         </is>
       </c>
       <c r="C439" s="5" t="n">
-        <v>4.5454</v>
+        <v>3.57</v>
       </c>
       <c r="D439" s="5" t="n">
-        <v>0.11</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="440" ht="18.75" customHeight="1">
@@ -12234,14 +12531,14 @@
       </c>
       <c r="B440" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="C440" s="8" t="n">
-        <v>0</v>
+          <t>2029-07-09</t>
+        </is>
+      </c>
+      <c r="C440" s="5" t="n">
+        <v>3.57</v>
       </c>
       <c r="D440" s="5" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="441" ht="18.75" customHeight="1">
@@ -12252,14 +12549,14 @@
       </c>
       <c r="B441" s="3" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
-        </is>
-      </c>
-      <c r="C441" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D441" s="5" t="n">
-        <v>1.75</v>
+          <t>2030-01-09</t>
+        </is>
+      </c>
+      <c r="C441" s="5" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="D441" s="8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="442" ht="18.75" customHeight="1">
@@ -12270,14 +12567,14 @@
       </c>
       <c r="B442" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
-        </is>
-      </c>
-      <c r="C442" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D442" s="5" t="n">
-        <v>1.75</v>
+          <t>2030-07-09</t>
+        </is>
+      </c>
+      <c r="C442" s="5" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="D442" s="8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="443" ht="18.75" customHeight="1">
@@ -12288,14 +12585,14 @@
       </c>
       <c r="B443" s="3" t="inlineStr">
         <is>
-          <t>2028-01-09</t>
+          <t>2031-01-09</t>
         </is>
       </c>
       <c r="C443" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D443" s="5" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="444" ht="18.75" customHeight="1">
@@ -12306,14 +12603,14 @@
       </c>
       <c r="B444" s="3" t="inlineStr">
         <is>
-          <t>2028-07-09</t>
+          <t>2031-07-09</t>
         </is>
       </c>
       <c r="C444" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D444" s="5" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="445" ht="18.75" customHeight="1">
@@ -12324,14 +12621,14 @@
       </c>
       <c r="B445" s="3" t="inlineStr">
         <is>
-          <t>2029-01-09</t>
+          <t>2032-01-09</t>
         </is>
       </c>
       <c r="C445" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D445" s="5" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="446" ht="18.75" customHeight="1">
@@ -12342,14 +12639,14 @@
       </c>
       <c r="B446" s="3" t="inlineStr">
         <is>
-          <t>2029-07-09</t>
+          <t>2032-07-09</t>
         </is>
       </c>
       <c r="C446" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D446" s="5" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="447" ht="18.75" customHeight="1">
@@ -12360,14 +12657,14 @@
       </c>
       <c r="B447" s="3" t="inlineStr">
         <is>
-          <t>2030-01-09</t>
+          <t>2033-01-09</t>
         </is>
       </c>
       <c r="C447" s="5" t="n">
         <v>3.57</v>
       </c>
-      <c r="D447" s="8" t="n">
-        <v>2</v>
+      <c r="D447" s="5" t="n">
+        <v>1.57</v>
       </c>
     </row>
     <row r="448" ht="18.75" customHeight="1">
@@ -12378,14 +12675,14 @@
       </c>
       <c r="B448" s="3" t="inlineStr">
         <is>
-          <t>2030-07-09</t>
+          <t>2033-07-09</t>
         </is>
       </c>
       <c r="C448" s="5" t="n">
         <v>3.57</v>
       </c>
-      <c r="D448" s="8" t="n">
-        <v>2</v>
+      <c r="D448" s="5" t="n">
+        <v>1.48</v>
       </c>
     </row>
     <row r="449" ht="18.75" customHeight="1">
@@ -12396,14 +12693,14 @@
       </c>
       <c r="B449" s="3" t="inlineStr">
         <is>
-          <t>2031-01-09</t>
+          <t>2034-01-09</t>
         </is>
       </c>
       <c r="C449" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D449" s="5" t="n">
-        <v>1.92</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="450" ht="18.75" customHeight="1">
@@ -12414,14 +12711,14 @@
       </c>
       <c r="B450" s="3" t="inlineStr">
         <is>
-          <t>2031-07-09</t>
+          <t>2034-07-09</t>
         </is>
       </c>
       <c r="C450" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D450" s="5" t="n">
-        <v>1.83</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="451" ht="18.75" customHeight="1">
@@ -12432,14 +12729,14 @@
       </c>
       <c r="B451" s="3" t="inlineStr">
         <is>
-          <t>2032-01-09</t>
+          <t>2035-01-09</t>
         </is>
       </c>
       <c r="C451" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D451" s="5" t="n">
-        <v>1.74</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="452" ht="18.75" customHeight="1">
@@ -12450,14 +12747,14 @@
       </c>
       <c r="B452" s="3" t="inlineStr">
         <is>
-          <t>2032-07-09</t>
+          <t>2035-07-09</t>
         </is>
       </c>
       <c r="C452" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D452" s="5" t="n">
-        <v>1.65</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="453" ht="18.75" customHeight="1">
@@ -12468,14 +12765,14 @@
       </c>
       <c r="B453" s="3" t="inlineStr">
         <is>
-          <t>2033-01-09</t>
+          <t>2036-01-09</t>
         </is>
       </c>
       <c r="C453" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D453" s="5" t="n">
-        <v>1.57</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="454" ht="18.75" customHeight="1">
@@ -12486,14 +12783,14 @@
       </c>
       <c r="B454" s="3" t="inlineStr">
         <is>
-          <t>2033-07-09</t>
+          <t>2036-07-09</t>
         </is>
       </c>
       <c r="C454" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D454" s="5" t="n">
-        <v>1.48</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="455" ht="18.75" customHeight="1">
@@ -12504,14 +12801,14 @@
       </c>
       <c r="B455" s="3" t="inlineStr">
         <is>
-          <t>2034-01-09</t>
+          <t>2037-01-09</t>
         </is>
       </c>
       <c r="C455" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D455" s="5" t="n">
-        <v>1.39</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="456" ht="18.75" customHeight="1">
@@ -12522,14 +12819,14 @@
       </c>
       <c r="B456" s="3" t="inlineStr">
         <is>
-          <t>2034-07-09</t>
+          <t>2037-07-09</t>
         </is>
       </c>
       <c r="C456" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D456" s="5" t="n">
-        <v>1.31</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="457" ht="18.75" customHeight="1">
@@ -12540,14 +12837,14 @@
       </c>
       <c r="B457" s="3" t="inlineStr">
         <is>
-          <t>2035-01-09</t>
+          <t>2038-01-09</t>
         </is>
       </c>
       <c r="C457" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D457" s="5" t="n">
-        <v>1.22</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="458" ht="18.75" customHeight="1">
@@ -12558,14 +12855,14 @@
       </c>
       <c r="B458" s="3" t="inlineStr">
         <is>
-          <t>2035-07-09</t>
+          <t>2038-07-09</t>
         </is>
       </c>
       <c r="C458" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D458" s="5" t="n">
-        <v>1.13</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="459" ht="18.75" customHeight="1">
@@ -12576,14 +12873,14 @@
       </c>
       <c r="B459" s="3" t="inlineStr">
         <is>
-          <t>2036-01-09</t>
+          <t>2039-01-09</t>
         </is>
       </c>
       <c r="C459" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D459" s="5" t="n">
-        <v>1.05</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="460" ht="18.75" customHeight="1">
@@ -12594,14 +12891,14 @@
       </c>
       <c r="B460" s="3" t="inlineStr">
         <is>
-          <t>2036-07-09</t>
+          <t>2039-07-09</t>
         </is>
       </c>
       <c r="C460" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D460" s="5" t="n">
-        <v>0.96</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="461" ht="18.75" customHeight="1">
@@ -12612,14 +12909,14 @@
       </c>
       <c r="B461" s="3" t="inlineStr">
         <is>
-          <t>2037-01-09</t>
+          <t>2040-01-09</t>
         </is>
       </c>
       <c r="C461" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D461" s="5" t="n">
-        <v>0.87</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="462" ht="18.75" customHeight="1">
@@ -12630,14 +12927,14 @@
       </c>
       <c r="B462" s="3" t="inlineStr">
         <is>
-          <t>2037-07-09</t>
+          <t>2040-07-09</t>
         </is>
       </c>
       <c r="C462" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D462" s="5" t="n">
-        <v>0.78</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="463" ht="18.75" customHeight="1">
@@ -12648,14 +12945,14 @@
       </c>
       <c r="B463" s="3" t="inlineStr">
         <is>
-          <t>2038-01-09</t>
+          <t>2041-01-09</t>
         </is>
       </c>
       <c r="C463" s="5" t="n">
         <v>3.57</v>
       </c>
       <c r="D463" s="5" t="n">
-        <v>0.7</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="464" ht="18.75" customHeight="1">
@@ -12666,122 +12963,122 @@
       </c>
       <c r="B464" s="3" t="inlineStr">
         <is>
-          <t>2038-07-09</t>
+          <t>2041-07-09</t>
         </is>
       </c>
       <c r="C464" s="5" t="n">
-        <v>3.57</v>
+        <v>3.61</v>
       </c>
       <c r="D464" s="5" t="n">
-        <v>0.61</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="465" ht="18.75" customHeight="1">
       <c r="A465" s="3" t="inlineStr">
         <is>
-          <t>GD41</t>
+          <t>GD46</t>
         </is>
       </c>
       <c r="B465" s="3" t="inlineStr">
         <is>
-          <t>2039-01-09</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C465" s="5" t="n">
-        <v>3.57</v>
+        <v>2.27</v>
       </c>
       <c r="D465" s="5" t="n">
-        <v>0.52</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="466" ht="18.75" customHeight="1">
       <c r="A466" s="3" t="inlineStr">
         <is>
-          <t>GD41</t>
+          <t>GD46</t>
         </is>
       </c>
       <c r="B466" s="3" t="inlineStr">
         <is>
-          <t>2039-07-09</t>
+          <t>2027-01-09</t>
         </is>
       </c>
       <c r="C466" s="5" t="n">
-        <v>3.57</v>
+        <v>2.27</v>
       </c>
       <c r="D466" s="5" t="n">
-        <v>0.44</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="467" ht="18.75" customHeight="1">
       <c r="A467" s="3" t="inlineStr">
         <is>
-          <t>GD41</t>
+          <t>GD46</t>
         </is>
       </c>
       <c r="B467" s="3" t="inlineStr">
         <is>
-          <t>2040-01-09</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="C467" s="5" t="n">
-        <v>3.57</v>
+        <v>2.27</v>
       </c>
       <c r="D467" s="5" t="n">
-        <v>0.35</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="468" ht="18.75" customHeight="1">
       <c r="A468" s="3" t="inlineStr">
         <is>
-          <t>GD41</t>
+          <t>GD46</t>
         </is>
       </c>
       <c r="B468" s="3" t="inlineStr">
         <is>
-          <t>2040-07-09</t>
+          <t>2028-01-09</t>
         </is>
       </c>
       <c r="C468" s="5" t="n">
-        <v>3.57</v>
+        <v>2.27</v>
       </c>
       <c r="D468" s="5" t="n">
-        <v>0.26</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="469" ht="18.75" customHeight="1">
       <c r="A469" s="3" t="inlineStr">
         <is>
-          <t>GD41</t>
+          <t>GD46</t>
         </is>
       </c>
       <c r="B469" s="3" t="inlineStr">
         <is>
-          <t>2041-01-09</t>
+          <t>2028-07-09</t>
         </is>
       </c>
       <c r="C469" s="5" t="n">
-        <v>3.57</v>
+        <v>2.27</v>
       </c>
       <c r="D469" s="5" t="n">
-        <v>0.18</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="470" ht="18.75" customHeight="1">
       <c r="A470" s="3" t="inlineStr">
         <is>
-          <t>GD41</t>
+          <t>GD46</t>
         </is>
       </c>
       <c r="B470" s="3" t="inlineStr">
         <is>
-          <t>2041-07-09</t>
+          <t>2029-01-09</t>
         </is>
       </c>
       <c r="C470" s="5" t="n">
-        <v>3.61</v>
+        <v>2.27</v>
       </c>
       <c r="D470" s="5" t="n">
-        <v>0.09</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="471" ht="18.75" customHeight="1">
@@ -12792,14 +13089,14 @@
       </c>
       <c r="B471" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2029-07-09</t>
         </is>
       </c>
       <c r="C471" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D471" s="5" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="472" ht="18.75" customHeight="1">
@@ -12810,14 +13107,14 @@
       </c>
       <c r="B472" s="3" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2030-01-09</t>
         </is>
       </c>
       <c r="C472" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D472" s="5" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="473" ht="18.75" customHeight="1">
@@ -12828,14 +13125,14 @@
       </c>
       <c r="B473" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
+          <t>2030-07-09</t>
         </is>
       </c>
       <c r="C473" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D473" s="5" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="474" ht="18.75" customHeight="1">
@@ -12846,14 +13143,14 @@
       </c>
       <c r="B474" s="3" t="inlineStr">
         <is>
-          <t>2028-01-09</t>
+          <t>2031-01-09</t>
         </is>
       </c>
       <c r="C474" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D474" s="5" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="475" ht="18.75" customHeight="1">
@@ -12864,14 +13161,14 @@
       </c>
       <c r="B475" s="3" t="inlineStr">
         <is>
-          <t>2028-07-09</t>
+          <t>2031-07-09</t>
         </is>
       </c>
       <c r="C475" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D475" s="5" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="476" ht="18.75" customHeight="1">
@@ -12882,14 +13179,14 @@
       </c>
       <c r="B476" s="3" t="inlineStr">
         <is>
-          <t>2029-01-09</t>
+          <t>2032-01-09</t>
         </is>
       </c>
       <c r="C476" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D476" s="5" t="n">
-        <v>2.09</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="477" ht="18.75" customHeight="1">
@@ -12900,14 +13197,14 @@
       </c>
       <c r="B477" s="3" t="inlineStr">
         <is>
-          <t>2029-07-09</t>
+          <t>2032-07-09</t>
         </is>
       </c>
       <c r="C477" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D477" s="5" t="n">
-        <v>1.99</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="478" ht="18.75" customHeight="1">
@@ -12918,14 +13215,14 @@
       </c>
       <c r="B478" s="3" t="inlineStr">
         <is>
-          <t>2030-01-09</t>
+          <t>2033-01-09</t>
         </is>
       </c>
       <c r="C478" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D478" s="5" t="n">
-        <v>1.93</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="479" ht="18.75" customHeight="1">
@@ -12936,14 +13233,14 @@
       </c>
       <c r="B479" s="3" t="inlineStr">
         <is>
-          <t>2030-07-09</t>
+          <t>2033-07-09</t>
         </is>
       </c>
       <c r="C479" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D479" s="5" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="480" ht="18.75" customHeight="1">
@@ -12954,14 +13251,14 @@
       </c>
       <c r="B480" s="3" t="inlineStr">
         <is>
-          <t>2031-01-09</t>
+          <t>2034-01-09</t>
         </is>
       </c>
       <c r="C480" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D480" s="5" t="n">
-        <v>1.82</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="481" ht="18.75" customHeight="1">
@@ -12972,14 +13269,14 @@
       </c>
       <c r="B481" s="3" t="inlineStr">
         <is>
-          <t>2031-07-09</t>
+          <t>2034-07-09</t>
         </is>
       </c>
       <c r="C481" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D481" s="5" t="n">
-        <v>1.76</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="482" ht="18.75" customHeight="1">
@@ -12990,14 +13287,14 @@
       </c>
       <c r="B482" s="3" t="inlineStr">
         <is>
-          <t>2032-01-09</t>
+          <t>2035-01-09</t>
         </is>
       </c>
       <c r="C482" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D482" s="5" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="483" ht="18.75" customHeight="1">
@@ -13008,14 +13305,14 @@
       </c>
       <c r="B483" s="3" t="inlineStr">
         <is>
-          <t>2032-07-09</t>
+          <t>2035-07-09</t>
         </is>
       </c>
       <c r="C483" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D483" s="5" t="n">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="484" ht="18.75" customHeight="1">
@@ -13026,14 +13323,14 @@
       </c>
       <c r="B484" s="3" t="inlineStr">
         <is>
-          <t>2033-01-09</t>
+          <t>2036-01-09</t>
         </is>
       </c>
       <c r="C484" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D484" s="5" t="n">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="485" ht="18.75" customHeight="1">
@@ -13044,14 +13341,14 @@
       </c>
       <c r="B485" s="3" t="inlineStr">
         <is>
-          <t>2033-07-09</t>
+          <t>2036-07-09</t>
         </is>
       </c>
       <c r="C485" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D485" s="5" t="n">
-        <v>1.53</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="486" ht="18.75" customHeight="1">
@@ -13062,14 +13359,14 @@
       </c>
       <c r="B486" s="3" t="inlineStr">
         <is>
-          <t>2034-01-09</t>
+          <t>2037-01-09</t>
         </is>
       </c>
       <c r="C486" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D486" s="5" t="n">
-        <v>1.48</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="487" ht="18.75" customHeight="1">
@@ -13080,14 +13377,14 @@
       </c>
       <c r="B487" s="3" t="inlineStr">
         <is>
-          <t>2034-07-09</t>
+          <t>2037-07-09</t>
         </is>
       </c>
       <c r="C487" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D487" s="5" t="n">
-        <v>1.42</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="488" ht="18.75" customHeight="1">
@@ -13098,14 +13395,14 @@
       </c>
       <c r="B488" s="3" t="inlineStr">
         <is>
-          <t>2035-01-09</t>
+          <t>2038-01-09</t>
         </is>
       </c>
       <c r="C488" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D488" s="5" t="n">
-        <v>1.36</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="489" ht="18.75" customHeight="1">
@@ -13116,14 +13413,14 @@
       </c>
       <c r="B489" s="3" t="inlineStr">
         <is>
-          <t>2035-07-09</t>
+          <t>2038-07-09</t>
         </is>
       </c>
       <c r="C489" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D489" s="5" t="n">
-        <v>1.31</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="490" ht="18.75" customHeight="1">
@@ -13134,14 +13431,14 @@
       </c>
       <c r="B490" s="3" t="inlineStr">
         <is>
-          <t>2036-01-09</t>
+          <t>2039-01-09</t>
         </is>
       </c>
       <c r="C490" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D490" s="5" t="n">
-        <v>1.25</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="491" ht="18.75" customHeight="1">
@@ -13152,14 +13449,14 @@
       </c>
       <c r="B491" s="3" t="inlineStr">
         <is>
-          <t>2036-07-09</t>
+          <t>2039-07-09</t>
         </is>
       </c>
       <c r="C491" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D491" s="5" t="n">
-        <v>1.19</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="492" ht="18.75" customHeight="1">
@@ -13170,14 +13467,14 @@
       </c>
       <c r="B492" s="3" t="inlineStr">
         <is>
-          <t>2037-01-09</t>
+          <t>2040-01-09</t>
         </is>
       </c>
       <c r="C492" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D492" s="5" t="n">
-        <v>1.14</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="493" ht="18.75" customHeight="1">
@@ -13188,14 +13485,14 @@
       </c>
       <c r="B493" s="3" t="inlineStr">
         <is>
-          <t>2037-07-09</t>
+          <t>2040-07-09</t>
         </is>
       </c>
       <c r="C493" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D493" s="5" t="n">
-        <v>1.08</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="494" ht="18.75" customHeight="1">
@@ -13206,14 +13503,14 @@
       </c>
       <c r="B494" s="3" t="inlineStr">
         <is>
-          <t>2038-01-09</t>
+          <t>2041-01-09</t>
         </is>
       </c>
       <c r="C494" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D494" s="5" t="n">
-        <v>1.02</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="495" ht="18.75" customHeight="1">
@@ -13224,14 +13521,14 @@
       </c>
       <c r="B495" s="3" t="inlineStr">
         <is>
-          <t>2038-07-09</t>
+          <t>2041-07-09</t>
         </is>
       </c>
       <c r="C495" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D495" s="5" t="n">
-        <v>0.97</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="496" ht="18.75" customHeight="1">
@@ -13242,14 +13539,14 @@
       </c>
       <c r="B496" s="3" t="inlineStr">
         <is>
-          <t>2039-01-09</t>
+          <t>2042-01-09</t>
         </is>
       </c>
       <c r="C496" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D496" s="5" t="n">
-        <v>0.91</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="497" ht="18.75" customHeight="1">
@@ -13260,14 +13557,14 @@
       </c>
       <c r="B497" s="3" t="inlineStr">
         <is>
-          <t>2039-07-09</t>
+          <t>2042-07-09</t>
         </is>
       </c>
       <c r="C497" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D497" s="5" t="n">
-        <v>0.85</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="498" ht="18.75" customHeight="1">
@@ -13278,14 +13575,14 @@
       </c>
       <c r="B498" s="3" t="inlineStr">
         <is>
-          <t>2040-01-09</t>
+          <t>2043-01-09</t>
         </is>
       </c>
       <c r="C498" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D498" s="5" t="n">
-        <v>0.8</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="499" ht="18.75" customHeight="1">
@@ -13296,14 +13593,14 @@
       </c>
       <c r="B499" s="3" t="inlineStr">
         <is>
-          <t>2040-07-09</t>
+          <t>2043-07-09</t>
         </is>
       </c>
       <c r="C499" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D499" s="5" t="n">
-        <v>0.74</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="500" ht="18.75" customHeight="1">
@@ -13314,14 +13611,14 @@
       </c>
       <c r="B500" s="3" t="inlineStr">
         <is>
-          <t>2041-01-09</t>
+          <t>2044-01-09</t>
         </is>
       </c>
       <c r="C500" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D500" s="5" t="n">
-        <v>0.68</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="501" ht="18.75" customHeight="1">
@@ -13332,14 +13629,14 @@
       </c>
       <c r="B501" s="3" t="inlineStr">
         <is>
-          <t>2041-07-09</t>
+          <t>2044-07-09</t>
         </is>
       </c>
       <c r="C501" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D501" s="5" t="n">
-        <v>0.63</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="502" ht="18.75" customHeight="1">
@@ -13350,14 +13647,14 @@
       </c>
       <c r="B502" s="3" t="inlineStr">
         <is>
-          <t>2042-01-09</t>
+          <t>2045-01-09</t>
         </is>
       </c>
       <c r="C502" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D502" s="5" t="n">
-        <v>0.57</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="503" ht="18.75" customHeight="1">
@@ -13368,14 +13665,14 @@
       </c>
       <c r="B503" s="3" t="inlineStr">
         <is>
-          <t>2042-07-09</t>
+          <t>2045-07-09</t>
         </is>
       </c>
       <c r="C503" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D503" s="5" t="n">
-        <v>0.51</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="504" ht="18.75" customHeight="1">
@@ -13386,14 +13683,14 @@
       </c>
       <c r="B504" s="3" t="inlineStr">
         <is>
-          <t>2043-01-09</t>
+          <t>2046-01-09</t>
         </is>
       </c>
       <c r="C504" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D504" s="5" t="n">
-        <v>0.45</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="505" ht="18.75" customHeight="1">
@@ -13404,122 +13701,122 @@
       </c>
       <c r="B505" s="3" t="inlineStr">
         <is>
-          <t>2043-07-09</t>
+          <t>2046-07-09</t>
         </is>
       </c>
       <c r="C505" s="5" t="n">
         <v>2.27</v>
       </c>
       <c r="D505" s="5" t="n">
-        <v>0.4</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="506" ht="18.75" customHeight="1">
       <c r="A506" s="3" t="inlineStr">
         <is>
-          <t>GD46</t>
+          <t>AO27D</t>
         </is>
       </c>
       <c r="B506" s="3" t="inlineStr">
         <is>
-          <t>2044-01-09</t>
-        </is>
-      </c>
-      <c r="C506" s="5" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="D506" s="5" t="n">
-        <v>0.34</v>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="C506" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D506" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="507" ht="18.75" customHeight="1">
       <c r="A507" s="3" t="inlineStr">
         <is>
-          <t>GD46</t>
+          <t>AO27D</t>
         </is>
       </c>
       <c r="B507" s="3" t="inlineStr">
         <is>
-          <t>2044-07-09</t>
-        </is>
-      </c>
-      <c r="C507" s="5" t="n">
-        <v>2.27</v>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C507" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="D507" s="5" t="n">
-        <v>0.28</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="508" ht="18.75" customHeight="1">
       <c r="A508" s="3" t="inlineStr">
         <is>
-          <t>GD46</t>
+          <t>AO27D</t>
         </is>
       </c>
       <c r="B508" s="3" t="inlineStr">
         <is>
-          <t>2045-01-09</t>
-        </is>
-      </c>
-      <c r="C508" s="5" t="n">
-        <v>2.27</v>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C508" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="D508" s="5" t="n">
-        <v>0.23</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="509" ht="18.75" customHeight="1">
       <c r="A509" s="3" t="inlineStr">
         <is>
-          <t>GD46</t>
+          <t>AO27D</t>
         </is>
       </c>
       <c r="B509" s="3" t="inlineStr">
         <is>
-          <t>2045-07-09</t>
-        </is>
-      </c>
-      <c r="C509" s="5" t="n">
-        <v>2.27</v>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C509" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="D509" s="5" t="n">
-        <v>0.17</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="510" ht="18.75" customHeight="1">
       <c r="A510" s="3" t="inlineStr">
         <is>
-          <t>GD46</t>
+          <t>AO27D</t>
         </is>
       </c>
       <c r="B510" s="3" t="inlineStr">
         <is>
-          <t>2046-01-09</t>
-        </is>
-      </c>
-      <c r="C510" s="5" t="n">
-        <v>2.27</v>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C510" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="D510" s="5" t="n">
-        <v>0.11</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="511" ht="18.75" customHeight="1">
       <c r="A511" s="3" t="inlineStr">
         <is>
-          <t>GD46</t>
+          <t>AO27D</t>
         </is>
       </c>
       <c r="B511" s="3" t="inlineStr">
         <is>
-          <t>2046-07-09</t>
-        </is>
-      </c>
-      <c r="C511" s="5" t="n">
-        <v>2.27</v>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C511" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="D511" s="5" t="n">
-        <v>0.06</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="512" ht="18.75" customHeight="1">
@@ -13530,14 +13827,14 @@
       </c>
       <c r="B512" s="3" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C512" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D512" s="8" t="n">
-        <v>0</v>
+      <c r="D512" s="5" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="513" ht="18.75" customHeight="1">
@@ -13548,14 +13845,14 @@
       </c>
       <c r="B513" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C513" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D513" s="5" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="514" ht="18.75" customHeight="1">
@@ -13566,7 +13863,7 @@
       </c>
       <c r="B514" s="3" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C514" s="8" t="n">
@@ -13584,14 +13881,14 @@
       </c>
       <c r="B515" s="3" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="C515" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D515" s="5" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="516" ht="18.75" customHeight="1">
@@ -13602,14 +13899,14 @@
       </c>
       <c r="B516" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="C516" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D516" s="5" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="517" ht="18.75" customHeight="1">
@@ -13620,14 +13917,14 @@
       </c>
       <c r="B517" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="C517" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D517" s="5" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="518" ht="18.75" customHeight="1">
@@ -13638,14 +13935,14 @@
       </c>
       <c r="B518" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2027-02-26</t>
         </is>
       </c>
       <c r="C518" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D518" s="5" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="519" ht="18.75" customHeight="1">
@@ -13656,14 +13953,14 @@
       </c>
       <c r="B519" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2027-03-31</t>
         </is>
       </c>
       <c r="C519" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D519" s="5" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="520" ht="18.75" customHeight="1">
@@ -13674,7 +13971,7 @@
       </c>
       <c r="B520" s="3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2027-04-30</t>
         </is>
       </c>
       <c r="C520" s="8" t="n">
@@ -13692,7 +13989,7 @@
       </c>
       <c r="B521" s="3" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2027-05-31</t>
         </is>
       </c>
       <c r="C521" s="8" t="n">
@@ -13710,7 +14007,7 @@
       </c>
       <c r="B522" s="3" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2027-06-30</t>
         </is>
       </c>
       <c r="C522" s="8" t="n">
@@ -13728,14 +14025,14 @@
       </c>
       <c r="B523" s="3" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
+          <t>2027-07-30</t>
         </is>
       </c>
       <c r="C523" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D523" s="5" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="524" ht="18.75" customHeight="1">
@@ -13746,14 +14043,14 @@
       </c>
       <c r="B524" s="3" t="inlineStr">
         <is>
-          <t>2027-02-26</t>
+          <t>2027-08-31</t>
         </is>
       </c>
       <c r="C524" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D524" s="5" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="525" ht="18.75" customHeight="1">
@@ -13764,14 +14061,14 @@
       </c>
       <c r="B525" s="3" t="inlineStr">
         <is>
-          <t>2027-03-31</t>
+          <t>2027-09-30</t>
         </is>
       </c>
       <c r="C525" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D525" s="5" t="n">
-        <v>0.58</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="526" ht="18.75" customHeight="1">
@@ -13782,180 +14079,538 @@
       </c>
       <c r="B526" s="3" t="inlineStr">
         <is>
-          <t>2027-04-30</t>
+          <t>2027-10-29</t>
         </is>
       </c>
       <c r="C526" s="8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D526" s="5" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="527" ht="18.75" customHeight="1">
       <c r="A527" s="3" t="inlineStr">
         <is>
-          <t>AO27D</t>
+          <t>BPD7D</t>
         </is>
       </c>
       <c r="B527" s="3" t="inlineStr">
         <is>
-          <t>2027-05-31</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="C527" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D527" s="5" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="528" ht="18.75" customHeight="1">
       <c r="A528" s="3" t="inlineStr">
         <is>
-          <t>AO27D</t>
+          <t>BPD7D</t>
         </is>
       </c>
       <c r="B528" s="3" t="inlineStr">
         <is>
-          <t>2027-06-30</t>
+          <t>2027-04-30</t>
         </is>
       </c>
       <c r="C528" s="8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D528" s="5" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="529" ht="18.75" customHeight="1">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>AO27D</t>
+          <t>BPD7D</t>
         </is>
       </c>
       <c r="B529" s="3" t="inlineStr">
         <is>
-          <t>2027-07-30</t>
+          <t>2027-10-31</t>
         </is>
       </c>
       <c r="C529" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D529" s="5" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="530" ht="18.75" customHeight="1">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>AN29</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="C530" t="n">
         <v>0</v>
       </c>
-      <c r="D529" s="5" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="530" ht="18.75" customHeight="1">
-      <c r="A530" s="3" t="inlineStr">
-        <is>
-          <t>AO27D</t>
-        </is>
-      </c>
-      <c r="B530" s="3" t="inlineStr">
-        <is>
-          <t>2027-08-31</t>
-        </is>
-      </c>
-      <c r="C530" s="8" t="n">
+      <c r="D530" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="531" ht="18.75" customHeight="1">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>AN29</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>2027-05-30</t>
+        </is>
+      </c>
+      <c r="C531" t="n">
         <v>0</v>
       </c>
-      <c r="D530" s="5" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="531" ht="18.75" customHeight="1">
-      <c r="A531" s="3" t="inlineStr">
-        <is>
-          <t>AO27D</t>
-        </is>
-      </c>
-      <c r="B531" s="3" t="inlineStr">
-        <is>
-          <t>2027-09-30</t>
-        </is>
-      </c>
-      <c r="C531" s="8" t="n">
+      <c r="D531" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="532" ht="18.75" customHeight="1">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>AN29</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>2027-11-30</t>
+        </is>
+      </c>
+      <c r="C532" t="n">
         <v>0</v>
       </c>
-      <c r="D531" s="5" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="532" ht="18.75" customHeight="1">
-      <c r="A532" s="3" t="inlineStr">
-        <is>
-          <t>AO27D</t>
-        </is>
-      </c>
-      <c r="B532" s="3" t="inlineStr">
-        <is>
-          <t>2027-10-29</t>
-        </is>
-      </c>
-      <c r="C532" s="8" t="n">
+      <c r="D532" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="533" ht="18.75" customHeight="1">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>AN29</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>2028-05-30</t>
+        </is>
+      </c>
+      <c r="C533" t="n">
+        <v>0</v>
+      </c>
+      <c r="D533" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="534" ht="18.75" customHeight="1">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>AN29</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>2028-11-30</t>
+        </is>
+      </c>
+      <c r="C534" t="n">
+        <v>0</v>
+      </c>
+      <c r="D534" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="535" ht="18.75" customHeight="1">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>AN29</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>2029-05-30</t>
+        </is>
+      </c>
+      <c r="C535" t="n">
+        <v>0</v>
+      </c>
+      <c r="D535" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="536" ht="18.75" customHeight="1">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>AN29</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>2029-11-30</t>
+        </is>
+      </c>
+      <c r="C536" t="n">
         <v>100</v>
       </c>
-      <c r="D532" s="5" t="n">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="533" ht="18.75" customHeight="1">
-      <c r="A533" s="3" t="inlineStr">
-        <is>
-          <t>BPD7D</t>
-        </is>
-      </c>
-      <c r="B533" s="3" t="inlineStr">
+      <c r="D536" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="537" ht="18.75" customHeight="1">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>AN29D</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="C537" t="n">
+        <v>0</v>
+      </c>
+      <c r="D537" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>AN29D</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>2027-05-30</t>
+        </is>
+      </c>
+      <c r="C538" t="n">
+        <v>0</v>
+      </c>
+      <c r="D538" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>AN29D</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>2027-11-30</t>
+        </is>
+      </c>
+      <c r="C539" t="n">
+        <v>0</v>
+      </c>
+      <c r="D539" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>AN29D</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>2028-05-30</t>
+        </is>
+      </c>
+      <c r="C540" t="n">
+        <v>0</v>
+      </c>
+      <c r="D540" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>AN29D</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>2028-11-30</t>
+        </is>
+      </c>
+      <c r="C541" t="n">
+        <v>0</v>
+      </c>
+      <c r="D541" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>AN29D</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>2029-05-30</t>
+        </is>
+      </c>
+      <c r="C542" t="n">
+        <v>0</v>
+      </c>
+      <c r="D542" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>AN29D</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>2029-11-30</t>
+        </is>
+      </c>
+      <c r="C543" t="n">
+        <v>100</v>
+      </c>
+      <c r="D543" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>BPA8D</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C544" t="n">
+        <v>0</v>
+      </c>
+      <c r="D544" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>BPA8D</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
         <is>
           <t>2026-10-31</t>
         </is>
       </c>
-      <c r="C533" s="8" t="n">
+      <c r="C545" t="n">
         <v>0</v>
       </c>
-      <c r="D533" s="5" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="534" ht="18.75" customHeight="1">
-      <c r="A534" s="3" t="inlineStr">
-        <is>
-          <t>BPD7D</t>
-        </is>
-      </c>
-      <c r="B534" s="3" t="inlineStr">
+      <c r="D545" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>BPA8D</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
         <is>
           <t>2027-04-30</t>
         </is>
       </c>
-      <c r="C534" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="D534" s="5" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="535" ht="18.75" customHeight="1">
-      <c r="A535" s="3" t="inlineStr">
-        <is>
-          <t>BPD7D</t>
-        </is>
-      </c>
-      <c r="B535" s="3" t="inlineStr">
+      <c r="C546" t="n">
+        <v>0</v>
+      </c>
+      <c r="D546" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>BPA8D</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
         <is>
           <t>2027-10-31</t>
         </is>
       </c>
-      <c r="C535" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="D535" s="5" t="n">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="536" ht="18.75" customHeight="1"/>
-    <row r="537" ht="18.75" customHeight="1"/>
+      <c r="C547" t="n">
+        <v>0</v>
+      </c>
+      <c r="D547" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>BPA8D</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>2028-04-30</t>
+        </is>
+      </c>
+      <c r="C548" t="n">
+        <v>0</v>
+      </c>
+      <c r="D548" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>BPA8D</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>2028-10-31</t>
+        </is>
+      </c>
+      <c r="C549" t="n">
+        <v>100</v>
+      </c>
+      <c r="D549" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>BPB8D</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C550" t="n">
+        <v>0</v>
+      </c>
+      <c r="D550" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>BPB8D</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="C551" t="n">
+        <v>0</v>
+      </c>
+      <c r="D551" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>BPB8D</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>2027-04-30</t>
+        </is>
+      </c>
+      <c r="C552" t="n">
+        <v>0</v>
+      </c>
+      <c r="D552" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>BPB8D</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>2027-10-31</t>
+        </is>
+      </c>
+      <c r="C553" t="n">
+        <v>0</v>
+      </c>
+      <c r="D553" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>BPB8D</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>2028-04-30</t>
+        </is>
+      </c>
+      <c r="C554" t="n">
+        <v>0</v>
+      </c>
+      <c r="D554" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>BPB8D</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>2028-10-31</t>
+        </is>
+      </c>
+      <c r="C555" t="n">
+        <v>100</v>
+      </c>
+      <c r="D555" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14438,7 +15093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R268"/>
+  <dimension ref="A1:R269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27083,6 +27738,34 @@
       <c r="Q268" s="24" t="n"/>
       <c r="R268" s="24" t="n"/>
     </row>
+    <row r="269">
+      <c r="A269" s="24" t="inlineStr">
+        <is>
+          <t>HBCFD</t>
+        </is>
+      </c>
+      <c r="B269" s="24" t="n"/>
+      <c r="C269" s="24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D269" s="24" t="n"/>
+      <c r="E269" s="24" t="n"/>
+      <c r="F269" s="24" t="n"/>
+      <c r="G269" s="24" t="n"/>
+      <c r="H269" s="24" t="n"/>
+      <c r="I269" s="24" t="n"/>
+      <c r="J269" s="24" t="n"/>
+      <c r="K269" s="24" t="n"/>
+      <c r="L269" s="24" t="n"/>
+      <c r="M269" s="24" t="n"/>
+      <c r="N269" s="24" t="n"/>
+      <c r="O269" s="24" t="n"/>
+      <c r="P269" s="24" t="n"/>
+      <c r="Q269" s="24" t="n"/>
+      <c r="R269" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/instruments_master.xlsx
+++ b/data/instruments_master.xlsx
@@ -22960,7 +22960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R269"/>
+  <dimension ref="A1:R270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37659,6 +37659,34 @@
       <c r="Q269" s="24" t="n"/>
       <c r="R269" s="24" t="n"/>
     </row>
+    <row r="270">
+      <c r="A270" s="24" t="inlineStr">
+        <is>
+          <t>SIC2D</t>
+        </is>
+      </c>
+      <c r="B270" s="24" t="n"/>
+      <c r="C270" s="24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D270" s="24" t="n"/>
+      <c r="E270" s="24" t="n"/>
+      <c r="F270" s="24" t="n"/>
+      <c r="G270" s="24" t="n"/>
+      <c r="H270" s="24" t="n"/>
+      <c r="I270" s="24" t="n"/>
+      <c r="J270" s="24" t="n"/>
+      <c r="K270" s="24" t="n"/>
+      <c r="L270" s="24" t="n"/>
+      <c r="M270" s="24" t="n"/>
+      <c r="N270" s="24" t="n"/>
+      <c r="O270" s="24" t="n"/>
+      <c r="P270" s="24" t="n"/>
+      <c r="Q270" s="24" t="n"/>
+      <c r="R270" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/instruments_master.xlsx
+++ b/data/instruments_master.xlsx
@@ -22960,7 +22960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R270"/>
+  <dimension ref="A1:R271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37687,6 +37687,34 @@
       <c r="Q270" s="24" t="n"/>
       <c r="R270" s="24" t="n"/>
     </row>
+    <row r="271">
+      <c r="A271" s="24" t="inlineStr">
+        <is>
+          <t>MTC2D</t>
+        </is>
+      </c>
+      <c r="B271" s="24" t="n"/>
+      <c r="C271" s="24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D271" s="24" t="n"/>
+      <c r="E271" s="24" t="n"/>
+      <c r="F271" s="24" t="n"/>
+      <c r="G271" s="24" t="n"/>
+      <c r="H271" s="24" t="n"/>
+      <c r="I271" s="24" t="n"/>
+      <c r="J271" s="24" t="n"/>
+      <c r="K271" s="24" t="n"/>
+      <c r="L271" s="24" t="n"/>
+      <c r="M271" s="24" t="n"/>
+      <c r="N271" s="24" t="n"/>
+      <c r="O271" s="24" t="n"/>
+      <c r="P271" s="24" t="n"/>
+      <c r="Q271" s="24" t="n"/>
+      <c r="R271" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/instruments_master.xlsx
+++ b/data/instruments_master.xlsx
@@ -22960,7 +22960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R271"/>
+  <dimension ref="A1:R272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37715,6 +37715,34 @@
       <c r="Q271" s="24" t="n"/>
       <c r="R271" s="24" t="n"/>
     </row>
+    <row r="272">
+      <c r="A272" s="24" t="inlineStr">
+        <is>
+          <t>OZC8D</t>
+        </is>
+      </c>
+      <c r="B272" s="24" t="n"/>
+      <c r="C272" s="24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D272" s="24" t="n"/>
+      <c r="E272" s="24" t="n"/>
+      <c r="F272" s="24" t="n"/>
+      <c r="G272" s="24" t="n"/>
+      <c r="H272" s="24" t="n"/>
+      <c r="I272" s="24" t="n"/>
+      <c r="J272" s="24" t="n"/>
+      <c r="K272" s="24" t="n"/>
+      <c r="L272" s="24" t="n"/>
+      <c r="M272" s="24" t="n"/>
+      <c r="N272" s="24" t="n"/>
+      <c r="O272" s="24" t="n"/>
+      <c r="P272" s="24" t="n"/>
+      <c r="Q272" s="24" t="n"/>
+      <c r="R272" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/instruments_master.xlsx
+++ b/data/instruments_master.xlsx
@@ -22960,7 +22960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R272"/>
+  <dimension ref="A1:R273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37743,6 +37743,34 @@
       <c r="Q272" s="24" t="n"/>
       <c r="R272" s="24" t="n"/>
     </row>
+    <row r="273">
+      <c r="A273" s="24" t="inlineStr">
+        <is>
+          <t>AFCPD</t>
+        </is>
+      </c>
+      <c r="B273" s="24" t="n"/>
+      <c r="C273" s="24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D273" s="24" t="n"/>
+      <c r="E273" s="24" t="n"/>
+      <c r="F273" s="24" t="n"/>
+      <c r="G273" s="24" t="n"/>
+      <c r="H273" s="24" t="n"/>
+      <c r="I273" s="24" t="n"/>
+      <c r="J273" s="24" t="n"/>
+      <c r="K273" s="24" t="n"/>
+      <c r="L273" s="24" t="n"/>
+      <c r="M273" s="24" t="n"/>
+      <c r="N273" s="24" t="n"/>
+      <c r="O273" s="24" t="n"/>
+      <c r="P273" s="24" t="n"/>
+      <c r="Q273" s="24" t="n"/>
+      <c r="R273" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/instruments_master.xlsx
+++ b/data/instruments_master.xlsx
@@ -22960,7 +22960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R273"/>
+  <dimension ref="A1:R279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37771,6 +37771,174 @@
       <c r="Q273" s="24" t="n"/>
       <c r="R273" s="24" t="n"/>
     </row>
+    <row r="274">
+      <c r="A274" s="24" t="inlineStr">
+        <is>
+          <t>JNC7D</t>
+        </is>
+      </c>
+      <c r="B274" s="24" t="n"/>
+      <c r="C274" s="24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D274" s="24" t="n"/>
+      <c r="E274" s="24" t="n"/>
+      <c r="F274" s="24" t="n"/>
+      <c r="G274" s="24" t="n"/>
+      <c r="H274" s="24" t="n"/>
+      <c r="I274" s="24" t="n"/>
+      <c r="J274" s="24" t="n"/>
+      <c r="K274" s="24" t="n"/>
+      <c r="L274" s="24" t="n"/>
+      <c r="M274" s="24" t="n"/>
+      <c r="N274" s="24" t="n"/>
+      <c r="O274" s="24" t="n"/>
+      <c r="P274" s="24" t="n"/>
+      <c r="Q274" s="24" t="n"/>
+      <c r="R274" s="24" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="24" t="inlineStr">
+        <is>
+          <t>MR46D</t>
+        </is>
+      </c>
+      <c r="B275" s="24" t="n"/>
+      <c r="C275" s="24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D275" s="24" t="n"/>
+      <c r="E275" s="24" t="n"/>
+      <c r="F275" s="24" t="n"/>
+      <c r="G275" s="24" t="n"/>
+      <c r="H275" s="24" t="n"/>
+      <c r="I275" s="24" t="n"/>
+      <c r="J275" s="24" t="n"/>
+      <c r="K275" s="24" t="n"/>
+      <c r="L275" s="24" t="n"/>
+      <c r="M275" s="24" t="n"/>
+      <c r="N275" s="24" t="n"/>
+      <c r="O275" s="24" t="n"/>
+      <c r="P275" s="24" t="n"/>
+      <c r="Q275" s="24" t="n"/>
+      <c r="R275" s="24" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="24" t="inlineStr">
+        <is>
+          <t>MR47D</t>
+        </is>
+      </c>
+      <c r="B276" s="24" t="n"/>
+      <c r="C276" s="24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D276" s="24" t="n"/>
+      <c r="E276" s="24" t="n"/>
+      <c r="F276" s="24" t="n"/>
+      <c r="G276" s="24" t="n"/>
+      <c r="H276" s="24" t="n"/>
+      <c r="I276" s="24" t="n"/>
+      <c r="J276" s="24" t="n"/>
+      <c r="K276" s="24" t="n"/>
+      <c r="L276" s="24" t="n"/>
+      <c r="M276" s="24" t="n"/>
+      <c r="N276" s="24" t="n"/>
+      <c r="O276" s="24" t="n"/>
+      <c r="P276" s="24" t="n"/>
+      <c r="Q276" s="24" t="n"/>
+      <c r="R276" s="24" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="24" t="inlineStr">
+        <is>
+          <t>RC6CD</t>
+        </is>
+      </c>
+      <c r="B277" s="24" t="n"/>
+      <c r="C277" s="24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D277" s="24" t="n"/>
+      <c r="E277" s="24" t="n"/>
+      <c r="F277" s="24" t="n"/>
+      <c r="G277" s="24" t="n"/>
+      <c r="H277" s="24" t="n"/>
+      <c r="I277" s="24" t="n"/>
+      <c r="J277" s="24" t="n"/>
+      <c r="K277" s="24" t="n"/>
+      <c r="L277" s="24" t="n"/>
+      <c r="M277" s="24" t="n"/>
+      <c r="N277" s="24" t="n"/>
+      <c r="O277" s="24" t="n"/>
+      <c r="P277" s="24" t="n"/>
+      <c r="Q277" s="24" t="n"/>
+      <c r="R277" s="24" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="24" t="inlineStr">
+        <is>
+          <t>VSCKD</t>
+        </is>
+      </c>
+      <c r="B278" s="24" t="n"/>
+      <c r="C278" s="24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D278" s="24" t="n"/>
+      <c r="E278" s="24" t="n"/>
+      <c r="F278" s="24" t="n"/>
+      <c r="G278" s="24" t="n"/>
+      <c r="H278" s="24" t="n"/>
+      <c r="I278" s="24" t="n"/>
+      <c r="J278" s="24" t="n"/>
+      <c r="K278" s="24" t="n"/>
+      <c r="L278" s="24" t="n"/>
+      <c r="M278" s="24" t="n"/>
+      <c r="N278" s="24" t="n"/>
+      <c r="O278" s="24" t="n"/>
+      <c r="P278" s="24" t="n"/>
+      <c r="Q278" s="24" t="n"/>
+      <c r="R278" s="24" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="24" t="inlineStr">
+        <is>
+          <t>YFCDD</t>
+        </is>
+      </c>
+      <c r="B279" s="24" t="n"/>
+      <c r="C279" s="24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D279" s="24" t="n"/>
+      <c r="E279" s="24" t="n"/>
+      <c r="F279" s="24" t="n"/>
+      <c r="G279" s="24" t="n"/>
+      <c r="H279" s="24" t="n"/>
+      <c r="I279" s="24" t="n"/>
+      <c r="J279" s="24" t="n"/>
+      <c r="K279" s="24" t="n"/>
+      <c r="L279" s="24" t="n"/>
+      <c r="M279" s="24" t="n"/>
+      <c r="N279" s="24" t="n"/>
+      <c r="O279" s="24" t="n"/>
+      <c r="P279" s="24" t="n"/>
+      <c r="Q279" s="24" t="n"/>
+      <c r="R279" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/instruments_master.xlsx
+++ b/data/instruments_master.xlsx
@@ -22960,7 +22960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R273"/>
+  <dimension ref="A1:R278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37771,6 +37771,146 @@
       <c r="Q273" s="24" t="n"/>
       <c r="R273" s="24" t="n"/>
     </row>
+    <row r="274">
+      <c r="A274" s="24" t="inlineStr">
+        <is>
+          <t>CS46D</t>
+        </is>
+      </c>
+      <c r="B274" s="24" t="n"/>
+      <c r="C274" s="24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D274" s="24" t="n"/>
+      <c r="E274" s="24" t="n"/>
+      <c r="F274" s="24" t="n"/>
+      <c r="G274" s="24" t="n"/>
+      <c r="H274" s="24" t="n"/>
+      <c r="I274" s="24" t="n"/>
+      <c r="J274" s="24" t="n"/>
+      <c r="K274" s="24" t="n"/>
+      <c r="L274" s="24" t="n"/>
+      <c r="M274" s="24" t="n"/>
+      <c r="N274" s="24" t="n"/>
+      <c r="O274" s="24" t="n"/>
+      <c r="P274" s="24" t="n"/>
+      <c r="Q274" s="24" t="n"/>
+      <c r="R274" s="24" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="24" t="inlineStr">
+        <is>
+          <t>JNC7D</t>
+        </is>
+      </c>
+      <c r="B275" s="24" t="n"/>
+      <c r="C275" s="24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D275" s="24" t="n"/>
+      <c r="E275" s="24" t="n"/>
+      <c r="F275" s="24" t="n"/>
+      <c r="G275" s="24" t="n"/>
+      <c r="H275" s="24" t="n"/>
+      <c r="I275" s="24" t="n"/>
+      <c r="J275" s="24" t="n"/>
+      <c r="K275" s="24" t="n"/>
+      <c r="L275" s="24" t="n"/>
+      <c r="M275" s="24" t="n"/>
+      <c r="N275" s="24" t="n"/>
+      <c r="O275" s="24" t="n"/>
+      <c r="P275" s="24" t="n"/>
+      <c r="Q275" s="24" t="n"/>
+      <c r="R275" s="24" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="24" t="inlineStr">
+        <is>
+          <t>MR46D</t>
+        </is>
+      </c>
+      <c r="B276" s="24" t="n"/>
+      <c r="C276" s="24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D276" s="24" t="n"/>
+      <c r="E276" s="24" t="n"/>
+      <c r="F276" s="24" t="n"/>
+      <c r="G276" s="24" t="n"/>
+      <c r="H276" s="24" t="n"/>
+      <c r="I276" s="24" t="n"/>
+      <c r="J276" s="24" t="n"/>
+      <c r="K276" s="24" t="n"/>
+      <c r="L276" s="24" t="n"/>
+      <c r="M276" s="24" t="n"/>
+      <c r="N276" s="24" t="n"/>
+      <c r="O276" s="24" t="n"/>
+      <c r="P276" s="24" t="n"/>
+      <c r="Q276" s="24" t="n"/>
+      <c r="R276" s="24" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="24" t="inlineStr">
+        <is>
+          <t>VSCKD</t>
+        </is>
+      </c>
+      <c r="B277" s="24" t="n"/>
+      <c r="C277" s="24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D277" s="24" t="n"/>
+      <c r="E277" s="24" t="n"/>
+      <c r="F277" s="24" t="n"/>
+      <c r="G277" s="24" t="n"/>
+      <c r="H277" s="24" t="n"/>
+      <c r="I277" s="24" t="n"/>
+      <c r="J277" s="24" t="n"/>
+      <c r="K277" s="24" t="n"/>
+      <c r="L277" s="24" t="n"/>
+      <c r="M277" s="24" t="n"/>
+      <c r="N277" s="24" t="n"/>
+      <c r="O277" s="24" t="n"/>
+      <c r="P277" s="24" t="n"/>
+      <c r="Q277" s="24" t="n"/>
+      <c r="R277" s="24" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="24" t="inlineStr">
+        <is>
+          <t>YFCDD</t>
+        </is>
+      </c>
+      <c r="B278" s="24" t="n"/>
+      <c r="C278" s="24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D278" s="24" t="n"/>
+      <c r="E278" s="24" t="n"/>
+      <c r="F278" s="24" t="n"/>
+      <c r="G278" s="24" t="n"/>
+      <c r="H278" s="24" t="n"/>
+      <c r="I278" s="24" t="n"/>
+      <c r="J278" s="24" t="n"/>
+      <c r="K278" s="24" t="n"/>
+      <c r="L278" s="24" t="n"/>
+      <c r="M278" s="24" t="n"/>
+      <c r="N278" s="24" t="n"/>
+      <c r="O278" s="24" t="n"/>
+      <c r="P278" s="24" t="n"/>
+      <c r="Q278" s="24" t="n"/>
+      <c r="R278" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
